--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9A1444-3FB6-404A-ABAF-8ABB3320FB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C930AC5-9942-4EC9-9E8D-48AB61CF5204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10-01" sheetId="14" state="hidden" r:id="rId1"/>
-    <sheet name="31-01" sheetId="37" r:id="rId2"/>
+    <sheet name="01-02" sheetId="37" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="116">
   <si>
     <t>STT</t>
   </si>
@@ -364,9 +364,6 @@
     <t>VÕ ĐẸP</t>
   </si>
   <si>
-    <t>DOANH THU 31/01/2026</t>
-  </si>
-  <si>
     <t>ĐỖ VIẾT BÌNH</t>
   </si>
   <si>
@@ -377,13 +374,22 @@
   </si>
   <si>
     <t>NGUYỄN THANH LIÊM</t>
+  </si>
+  <si>
+    <t>Đi nhậu với bác kim</t>
+  </si>
+  <si>
+    <t>nghỉ</t>
+  </si>
+  <si>
+    <t>DOANH THU 01/02/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,14 +603,8 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFFFF00"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -685,6 +685,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -838,7 +850,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1081,9 +1093,6 @@
     <xf numFmtId="3" fontId="29" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="29" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="29" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1128,6 +1137,40 @@
     <xf numFmtId="3" fontId="27" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="27" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1140,6 +1183,12 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1160,18 +1209,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1739,32 +1776,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="108" t="s">
+      <c r="B3" s="119" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="109"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="21"/>
@@ -2422,20 +2459,20 @@
       <c r="F26" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="110" t="s">
+      <c r="H26" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="110"/>
+      <c r="I26" s="121"/>
       <c r="J26" s="5">
         <f>SUM(H7:H1001)</f>
         <v>28869000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="110" t="s">
+      <c r="H27" s="121" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="110"/>
+      <c r="I27" s="121"/>
       <c r="J27" s="5">
         <f>SUM(I7:I1001)</f>
         <v>17311000</v>
@@ -2573,25 +2610,25 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="118"/>
+      <c r="K3" s="118"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
       <c r="G4" s="58" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I4" s="59"/>
       <c r="J4" s="59"/>
@@ -2638,7 +2675,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="111" t="s">
+      <c r="A7" s="124" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -2651,27 +2688,31 @@
       <c r="E7" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="41"/>
+      <c r="F7" s="41">
+        <v>1250000</v>
+      </c>
       <c r="G7" s="41">
         <f>IF(F7="",0,IF(F7&gt;1700000,F7*O$19,F7*O$18))</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="41"/>
+        <v>750000</v>
+      </c>
+      <c r="H7" s="41">
+        <v>750000</v>
+      </c>
       <c r="I7" s="41">
         <f>G7-H7</f>
         <v>0</v>
       </c>
-      <c r="J7" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K7" s="96"/>
+      <c r="J7" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="95"/>
       <c r="L7" s="46"/>
       <c r="N7" s="50" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="112"/>
+      <c r="A8" s="125"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -2683,27 +2724,31 @@
       <c r="E8" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="41"/>
+      <c r="F8" s="41">
+        <v>610000</v>
+      </c>
       <c r="G8" s="41">
         <f>IF(F8="",0,IF(F8&gt;1700000,F8*O$19,F8*O$18))</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="41"/>
+        <v>366000</v>
+      </c>
+      <c r="H8" s="41">
+        <v>305000</v>
+      </c>
       <c r="I8" s="41">
         <f t="shared" ref="I8:I10" si="0">G8-H8</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K8" s="97"/>
+        <v>61000</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="96"/>
       <c r="L8" s="46"/>
       <c r="N8" s="48" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="112"/>
+      <c r="A9" s="125"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -2731,11 +2776,11 @@
       <c r="J9" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="97"/>
+      <c r="K9" s="96"/>
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="112"/>
+      <c r="A10" s="125"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -2747,62 +2792,72 @@
       <c r="E10" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="F10" s="44"/>
+      <c r="F10" s="44">
+        <v>1000000</v>
+      </c>
       <c r="G10" s="41">
         <f>IF(F10="",0,IF(F10&gt;1700000,F10*O$19,F10*O$18))</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="44"/>
+        <v>600000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>600000</v>
+      </c>
       <c r="I10" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" s="97"/>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="114" t="s">
+      <c r="N10" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="114"/>
-      <c r="P10" s="115">
+      <c r="O10" s="127"/>
+      <c r="P10" s="128">
         <f>SUM(F7:F1006)</f>
-        <v>850000</v>
+        <v>16675000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="112"/>
+      <c r="A11" s="125"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D11" s="43"/>
       <c r="E11" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="F11" s="44"/>
+      <c r="F11" s="44">
+        <v>250000</v>
+      </c>
       <c r="G11" s="41">
         <f>IF(F11="",0,IF(F11&gt;1700000,F11*O$19,F11*O$18))</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="44"/>
+        <v>150000</v>
+      </c>
+      <c r="H11" s="44">
+        <v>150000</v>
+      </c>
       <c r="I11" s="41">
         <f t="shared" ref="I11:I18" si="2">G11-H11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="62"/>
-      <c r="K11" s="97"/>
+      <c r="J11" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="114"/>
-      <c r="O11" s="114"/>
-      <c r="P11" s="115"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="127"/>
+      <c r="P11" s="128"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="112"/>
+      <c r="A12" s="125"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -2825,19 +2880,19 @@
         <v>0</v>
       </c>
       <c r="J12" s="62"/>
-      <c r="K12" s="97"/>
+      <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="116" t="s">
+      <c r="N12" s="129" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="116"/>
-      <c r="P12" s="115">
+      <c r="O12" s="129"/>
+      <c r="P12" s="128">
         <f>SUM(G7:G1006)</f>
-        <v>510000</v>
+        <v>9346000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="112"/>
+      <c r="A13" s="125"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -2860,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="J13" s="62"/>
-      <c r="K13" s="97"/>
+      <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="116"/>
-      <c r="O13" s="116"/>
-      <c r="P13" s="115"/>
+      <c r="N13" s="129"/>
+      <c r="O13" s="129"/>
+      <c r="P13" s="128"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="112"/>
+      <c r="A14" s="125"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -2890,14 +2945,14 @@
         <v>0</v>
       </c>
       <c r="J14" s="62"/>
-      <c r="K14" s="97"/>
+      <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="116"/>
-      <c r="O14" s="116"/>
-      <c r="P14" s="115"/>
+      <c r="N14" s="129"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="128"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="112"/>
+      <c r="A15" s="125"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -2920,19 +2975,19 @@
         <v>0</v>
       </c>
       <c r="J15" s="62"/>
-      <c r="K15" s="97"/>
+      <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="117" t="s">
+      <c r="N15" s="130" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="117"/>
+      <c r="O15" s="130"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
-        <v>510000</v>
+        <v>9285000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="112"/>
+      <c r="A16" s="125"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2955,11 +3010,11 @@
         <v>0</v>
       </c>
       <c r="J16" s="62"/>
-      <c r="K16" s="97"/>
+      <c r="K16" s="96"/>
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="112"/>
+      <c r="A17" s="125"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -2982,11 +3037,11 @@
         <v>0</v>
       </c>
       <c r="J17" s="62"/>
-      <c r="K17" s="97"/>
+      <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="112"/>
+      <c r="A18" s="125"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3009,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="62"/>
-      <c r="K18" s="97"/>
+      <c r="K18" s="96"/>
       <c r="L18" s="46"/>
       <c r="N18" s="64" t="s">
         <v>60</v>
@@ -3022,7 +3077,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="113"/>
+      <c r="A19" s="126"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -3032,7 +3087,7 @@
       <c r="H19" s="63"/>
       <c r="I19" s="61"/>
       <c r="J19" s="55"/>
-      <c r="K19" s="98"/>
+      <c r="K19" s="97"/>
       <c r="L19" s="56"/>
       <c r="N19" s="64" t="s">
         <v>60</v>
@@ -3045,37 +3100,39 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="118" t="s">
+      <c r="A20" s="122" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
         <v>1</v>
       </c>
-      <c r="C20" s="73" t="s">
+      <c r="C20" s="107" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74" t="s">
+      <c r="D20" s="108"/>
+      <c r="E20" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75">
+      <c r="F20" s="109"/>
+      <c r="G20" s="109">
         <f t="shared" ref="G20:G47" si="4">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75">
+      <c r="H20" s="109"/>
+      <c r="I20" s="109">
         <f t="shared" ref="I20:I37" si="5">G20-H20</f>
         <v>0</v>
       </c>
       <c r="J20" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="K20" s="85"/>
+      <c r="K20" s="85" t="s">
+        <v>113</v>
+      </c>
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="119"/>
+      <c r="A21" s="123"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -3087,107 +3144,113 @@
       <c r="E21" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="79"/>
+      <c r="F21" s="79">
+        <v>1470000</v>
+      </c>
       <c r="G21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="79"/>
+        <v>882000</v>
+      </c>
+      <c r="H21" s="79">
+        <v>882000</v>
+      </c>
       <c r="I21" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J21" s="48" t="s">
-        <v>64</v>
+      <c r="J21" s="49" t="s">
+        <v>63</v>
       </c>
       <c r="K21" s="85"/>
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="119"/>
+      <c r="A22" s="123"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="6">B21+1</f>
         <v>3</v>
       </c>
-      <c r="C22" s="73" t="s">
+      <c r="C22" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81" t="s">
+      <c r="D22" s="111"/>
+      <c r="E22" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75">
+      <c r="F22" s="109"/>
+      <c r="G22" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H22" s="79"/>
-      <c r="I22" s="75">
+      <c r="H22" s="115"/>
+      <c r="I22" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J22" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="K22" s="85"/>
+      <c r="K22" s="85" t="s">
+        <v>113</v>
+      </c>
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="119"/>
+      <c r="A23" s="123"/>
       <c r="B23" s="38">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="C23" s="102"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104">
+      <c r="C23" s="101"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H23" s="104"/>
-      <c r="I23" s="104">
+      <c r="H23" s="103"/>
+      <c r="I23" s="103">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J23" s="48" t="s">
-        <v>64</v>
-      </c>
+      <c r="J23" s="62"/>
       <c r="K23" s="84"/>
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="119"/>
+      <c r="A24" s="123"/>
       <c r="B24" s="38">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="C24" s="73" t="s">
+      <c r="C24" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81" t="s">
+      <c r="D24" s="111"/>
+      <c r="E24" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75">
+      <c r="F24" s="109"/>
+      <c r="G24" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H24" s="79"/>
-      <c r="I24" s="75">
+      <c r="H24" s="115"/>
+      <c r="I24" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J24" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="K24" s="84"/>
+      <c r="K24" s="85" t="s">
+        <v>113</v>
+      </c>
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="119"/>
+      <c r="A25" s="123"/>
       <c r="B25" s="38">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -3199,53 +3262,59 @@
       <c r="E25" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="75"/>
+      <c r="F25" s="75">
+        <v>1375000</v>
+      </c>
       <c r="G25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="79"/>
+        <v>825000</v>
+      </c>
+      <c r="H25" s="79">
+        <v>825000</v>
+      </c>
       <c r="I25" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J25" s="48" t="s">
-        <v>64</v>
+      <c r="J25" s="49" t="s">
+        <v>63</v>
       </c>
       <c r="K25" s="84"/>
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="119"/>
+      <c r="A26" s="123"/>
       <c r="B26" s="38">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="C26" s="73" t="s">
+      <c r="C26" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76" t="s">
+      <c r="D26" s="114"/>
+      <c r="E26" s="114" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75">
+      <c r="F26" s="109"/>
+      <c r="G26" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75">
+      <c r="H26" s="109"/>
+      <c r="I26" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J26" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="K26" s="84"/>
+      <c r="K26" s="85" t="s">
+        <v>113</v>
+      </c>
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="119"/>
+      <c r="A27" s="123"/>
       <c r="B27" s="38">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -3257,24 +3326,28 @@
       <c r="E27" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="F27" s="79"/>
+      <c r="F27" s="79">
+        <v>2570000</v>
+      </c>
       <c r="G27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="75"/>
+        <v>1285000</v>
+      </c>
+      <c r="H27" s="75">
+        <v>1285000</v>
+      </c>
       <c r="I27" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J27" s="48" t="s">
-        <v>64</v>
+      <c r="J27" s="49" t="s">
+        <v>63</v>
       </c>
       <c r="K27" s="85"/>
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="119"/>
+      <c r="A28" s="123"/>
       <c r="B28" s="38">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -3286,78 +3359,82 @@
       <c r="E28" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="79"/>
+      <c r="F28" s="79">
+        <v>1930000</v>
+      </c>
       <c r="G28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="79"/>
+        <v>965000</v>
+      </c>
+      <c r="H28" s="79">
+        <v>965000</v>
+      </c>
       <c r="I28" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J28" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K28" s="92"/>
+      <c r="J28" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K28" s="91"/>
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="119"/>
+      <c r="A29" s="123"/>
       <c r="B29" s="38">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="C29" s="105"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="104">
+      <c r="C29" s="104"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H29" s="106"/>
-      <c r="I29" s="104">
+      <c r="H29" s="105"/>
+      <c r="I29" s="103">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J29" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K29" s="120"/>
-      <c r="L29" s="94"/>
-    </row>
-    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="119"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="106"/>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="123"/>
       <c r="B30" s="38">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="C30" s="88" t="s">
+      <c r="C30" s="110" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="81" t="s">
+      <c r="D30" s="108"/>
+      <c r="E30" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="89"/>
-      <c r="G30" s="75">
+      <c r="F30" s="112"/>
+      <c r="G30" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H30" s="90"/>
-      <c r="I30" s="75">
+      <c r="H30" s="113"/>
+      <c r="I30" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J30" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="K30" s="120"/>
+      <c r="K30" s="85" t="s">
+        <v>113</v>
+      </c>
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="119"/>
+      <c r="A31" s="123"/>
       <c r="B31" s="38">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3369,24 +3446,28 @@
       <c r="E31" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="F31" s="89"/>
+      <c r="F31" s="89">
+        <v>2090000</v>
+      </c>
       <c r="G31" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="89"/>
+        <v>1045000</v>
+      </c>
+      <c r="H31" s="89">
+        <v>1045000</v>
+      </c>
       <c r="I31" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J31" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K31" s="120"/>
-      <c r="L31" s="94"/>
+      <c r="J31" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31" s="106"/>
+      <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="119"/>
+      <c r="A32" s="123"/>
       <c r="B32" s="38">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -3398,36 +3479,38 @@
       <c r="E32" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="F32" s="75"/>
+      <c r="F32" s="75">
+        <v>1150000</v>
+      </c>
       <c r="G32" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="75"/>
+        <v>690000</v>
+      </c>
+      <c r="H32" s="75">
+        <v>690000</v>
+      </c>
       <c r="I32" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J32" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K32" s="120"/>
-      <c r="L32" s="94"/>
+      <c r="J32" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K32" s="106"/>
+      <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="119"/>
+      <c r="A33" s="123"/>
       <c r="B33" s="38">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="C33" s="73" t="s">
-        <v>40</v>
-      </c>
+      <c r="C33" s="73"/>
       <c r="D33" s="74"/>
       <c r="E33" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="91"/>
+      <c r="F33" s="90"/>
       <c r="G33" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3437,109 +3520,119 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J33" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K33" s="120"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="106" t="s">
+        <v>114</v>
+      </c>
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="119"/>
+      <c r="A34" s="123"/>
       <c r="B34" s="38">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="C34" s="77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D34" s="87"/>
       <c r="E34" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="F34" s="79"/>
+      <c r="F34" s="79">
+        <v>500000</v>
+      </c>
       <c r="G34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="79"/>
+        <v>300000</v>
+      </c>
+      <c r="H34" s="79">
+        <v>300000</v>
+      </c>
       <c r="I34" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J34" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K34" s="93"/>
+      <c r="J34" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K34" s="92"/>
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="119"/>
+      <c r="A35" s="123"/>
       <c r="B35" s="38">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="C35" s="94" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="94"/>
-      <c r="E35" s="81" t="s">
+      <c r="C35" s="116" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="116"/>
+      <c r="E35" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="F35" s="95"/>
-      <c r="G35" s="75">
+      <c r="F35" s="117"/>
+      <c r="G35" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H35" s="95"/>
-      <c r="I35" s="75">
+      <c r="H35" s="117"/>
+      <c r="I35" s="109">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J35" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="K35" s="121"/>
+      <c r="K35" s="85" t="s">
+        <v>113</v>
+      </c>
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="119"/>
+      <c r="A36" s="123"/>
       <c r="B36" s="38">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="C36" s="94" t="s">
-        <v>112</v>
+      <c r="C36" s="93" t="s">
+        <v>111</v>
       </c>
       <c r="D36" s="57"/>
       <c r="E36" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="95"/>
+      <c r="F36" s="94">
+        <v>1630000</v>
+      </c>
       <c r="G36" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="95"/>
+        <v>978000</v>
+      </c>
+      <c r="H36" s="94">
+        <v>978000</v>
+      </c>
       <c r="I36" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J36" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K36" s="97"/>
+      <c r="J36" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K36" s="96"/>
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="119"/>
+      <c r="A37" s="123"/>
       <c r="B37" s="38">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="C37" s="100"/>
+      <c r="C37" s="99"/>
       <c r="D37" s="43"/>
       <c r="E37" s="43"/>
-      <c r="F37" s="101"/>
+      <c r="F37" s="100"/>
       <c r="G37" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3550,19 +3643,19 @@
         <v>0</v>
       </c>
       <c r="J37" s="83"/>
-      <c r="K37" s="99"/>
+      <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="119"/>
+      <c r="A38" s="123"/>
       <c r="B38" s="38">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="C38" s="100"/>
+      <c r="C38" s="99"/>
       <c r="D38" s="43"/>
       <c r="E38" s="43"/>
-      <c r="F38" s="101"/>
+      <c r="F38" s="100"/>
       <c r="G38" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3573,19 +3666,19 @@
         <v>0</v>
       </c>
       <c r="J38" s="83"/>
-      <c r="K38" s="99"/>
+      <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="119"/>
+      <c r="A39" s="123"/>
       <c r="B39" s="38">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="C39" s="100"/>
+      <c r="C39" s="99"/>
       <c r="D39" s="43"/>
       <c r="E39" s="43"/>
-      <c r="F39" s="101"/>
+      <c r="F39" s="100"/>
       <c r="G39" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3596,19 +3689,19 @@
         <v>0</v>
       </c>
       <c r="J39" s="83"/>
-      <c r="K39" s="99"/>
+      <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="119"/>
+      <c r="A40" s="123"/>
       <c r="B40" s="38">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="C40" s="100"/>
+      <c r="C40" s="99"/>
       <c r="D40" s="43"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="101"/>
+      <c r="F40" s="100"/>
       <c r="G40" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3619,19 +3712,19 @@
         <v>0</v>
       </c>
       <c r="J40" s="83"/>
-      <c r="K40" s="99"/>
+      <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="119"/>
+      <c r="A41" s="123"/>
       <c r="B41" s="38">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="C41" s="100"/>
+      <c r="C41" s="99"/>
       <c r="D41" s="43"/>
       <c r="E41" s="43"/>
-      <c r="F41" s="101"/>
+      <c r="F41" s="100"/>
       <c r="G41" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3642,19 +3735,19 @@
         <v>0</v>
       </c>
       <c r="J41" s="83"/>
-      <c r="K41" s="99"/>
+      <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="119"/>
+      <c r="A42" s="123"/>
       <c r="B42" s="38">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="C42" s="100"/>
+      <c r="C42" s="99"/>
       <c r="D42" s="43"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="101"/>
+      <c r="F42" s="100"/>
       <c r="G42" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3665,19 +3758,19 @@
         <v>0</v>
       </c>
       <c r="J42" s="83"/>
-      <c r="K42" s="99"/>
+      <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="119"/>
+      <c r="A43" s="123"/>
       <c r="B43" s="38">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="C43" s="100"/>
+      <c r="C43" s="99"/>
       <c r="D43" s="43"/>
       <c r="E43" s="43"/>
-      <c r="F43" s="101"/>
+      <c r="F43" s="100"/>
       <c r="G43" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3688,19 +3781,19 @@
         <v>0</v>
       </c>
       <c r="J43" s="83"/>
-      <c r="K43" s="99"/>
+      <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="119"/>
+      <c r="A44" s="123"/>
       <c r="B44" s="38">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="C44" s="100"/>
+      <c r="C44" s="99"/>
       <c r="D44" s="43"/>
       <c r="E44" s="43"/>
-      <c r="F44" s="101"/>
+      <c r="F44" s="100"/>
       <c r="G44" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3711,19 +3804,19 @@
         <v>0</v>
       </c>
       <c r="J44" s="83"/>
-      <c r="K44" s="99"/>
+      <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="119"/>
+      <c r="A45" s="123"/>
       <c r="B45" s="38">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="C45" s="100"/>
+      <c r="C45" s="99"/>
       <c r="D45" s="43"/>
       <c r="E45" s="43"/>
-      <c r="F45" s="101"/>
+      <c r="F45" s="100"/>
       <c r="G45" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3734,19 +3827,19 @@
         <v>0</v>
       </c>
       <c r="J45" s="83"/>
-      <c r="K45" s="99"/>
+      <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="119"/>
+      <c r="A46" s="123"/>
       <c r="B46" s="38">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="C46" s="100"/>
+      <c r="C46" s="99"/>
       <c r="D46" s="43"/>
       <c r="E46" s="43"/>
-      <c r="F46" s="101"/>
+      <c r="F46" s="100"/>
       <c r="G46" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3757,19 +3850,19 @@
         <v>0</v>
       </c>
       <c r="J46" s="83"/>
-      <c r="K46" s="99"/>
+      <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="119"/>
+      <c r="A47" s="123"/>
       <c r="B47" s="38">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="C47" s="100"/>
+      <c r="C47" s="99"/>
       <c r="D47" s="43"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="101"/>
+      <c r="F47" s="100"/>
       <c r="G47" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -3780,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="83"/>
-      <c r="K47" s="99"/>
+      <c r="K47" s="98"/>
       <c r="L47" s="47"/>
     </row>
   </sheetData>

--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C930AC5-9942-4EC9-9E8D-48AB61CF5204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D96A686-3431-437A-9B53-B9741F514FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10-01" sheetId="14" state="hidden" r:id="rId1"/>
     <sheet name="01-02" sheetId="37" r:id="rId2"/>
+    <sheet name="02-02" sheetId="38" r:id="rId3"/>
+    <sheet name="03-02" sheetId="39" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="121">
   <si>
     <t>STT</t>
   </si>
@@ -383,6 +385,21 @@
   </si>
   <si>
     <t>DOANH THU 01/02/2026</t>
+  </si>
+  <si>
+    <t>DOANH THU 02/02/2026</t>
+  </si>
+  <si>
+    <t>Mai thanh toán</t>
+  </si>
+  <si>
+    <t>Nghỉ tất liên</t>
+  </si>
+  <si>
+    <t>nghỉ có việc</t>
+  </si>
+  <si>
+    <t>DOANH THU 03/02/2026</t>
   </si>
 </sst>
 </file>
@@ -604,7 +621,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -696,6 +713,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -850,7 +879,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1170,6 +1199,34 @@
     <xf numFmtId="0" fontId="27" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="27" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1776,32 +1833,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="119" t="s">
+      <c r="B3" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="21"/>
@@ -2459,20 +2516,20 @@
       <c r="F26" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="121" t="s">
+      <c r="H26" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="121"/>
+      <c r="I26" s="131"/>
       <c r="J26" s="5">
         <f>SUM(H7:H1001)</f>
         <v>28869000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="121" t="s">
+      <c r="H27" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="121"/>
+      <c r="I27" s="131"/>
       <c r="J27" s="5">
         <f>SUM(I7:I1001)</f>
         <v>17311000</v>
@@ -2610,18 +2667,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="118" t="s">
+      <c r="B3" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="118"/>
-      <c r="K3" s="118"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -2675,7 +2732,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="124" t="s">
+      <c r="A7" s="134" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -2712,7 +2769,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="125"/>
+      <c r="A8" s="135"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -2748,7 +2805,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="125"/>
+      <c r="A9" s="135"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -2780,7 +2837,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="125"/>
+      <c r="A10" s="135"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -2811,17 +2868,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="127" t="s">
+      <c r="N10" s="137" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="127"/>
-      <c r="P10" s="128">
+      <c r="O10" s="137"/>
+      <c r="P10" s="138">
         <f>SUM(F7:F1006)</f>
         <v>16675000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="125"/>
+      <c r="A11" s="135"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -2852,12 +2909,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="127"/>
-      <c r="O11" s="127"/>
-      <c r="P11" s="128"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="138"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="125"/>
+      <c r="A12" s="135"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -2882,17 +2939,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="129" t="s">
+      <c r="N12" s="139" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="129"/>
-      <c r="P12" s="128">
+      <c r="O12" s="139"/>
+      <c r="P12" s="138">
         <f>SUM(G7:G1006)</f>
         <v>9346000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="125"/>
+      <c r="A13" s="135"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -2917,12 +2974,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="129"/>
-      <c r="O13" s="129"/>
-      <c r="P13" s="128"/>
+      <c r="N13" s="139"/>
+      <c r="O13" s="139"/>
+      <c r="P13" s="138"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="125"/>
+      <c r="A14" s="135"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -2947,12 +3004,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="129"/>
-      <c r="O14" s="129"/>
-      <c r="P14" s="128"/>
+      <c r="N14" s="139"/>
+      <c r="O14" s="139"/>
+      <c r="P14" s="138"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="125"/>
+      <c r="A15" s="135"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -2977,17 +3034,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="130" t="s">
+      <c r="N15" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="130"/>
+      <c r="O15" s="140"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>9285000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="125"/>
+      <c r="A16" s="135"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -3014,7 +3071,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="125"/>
+      <c r="A17" s="135"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -3041,7 +3098,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="125"/>
+      <c r="A18" s="135"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3077,7 +3134,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="126"/>
+      <c r="A19" s="136"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -3100,7 +3157,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="122" t="s">
+      <c r="A20" s="132" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -3132,7 +3189,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="123"/>
+      <c r="A21" s="133"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -3165,7 +3222,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="123"/>
+      <c r="A22" s="133"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="6">B21+1</f>
         <v>3</v>
@@ -3196,7 +3253,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="123"/>
+      <c r="A23" s="133"/>
       <c r="B23" s="38">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -3219,7 +3276,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="123"/>
+      <c r="A24" s="133"/>
       <c r="B24" s="38">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -3250,7 +3307,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="123"/>
+      <c r="A25" s="133"/>
       <c r="B25" s="38">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -3283,7 +3340,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="123"/>
+      <c r="A26" s="133"/>
       <c r="B26" s="38">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -3314,7 +3371,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="123"/>
+      <c r="A27" s="133"/>
       <c r="B27" s="38">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -3347,7 +3404,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="123"/>
+      <c r="A28" s="133"/>
       <c r="B28" s="38">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -3380,7 +3437,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="123"/>
+      <c r="A29" s="133"/>
       <c r="B29" s="38">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -3403,7 +3460,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="123"/>
+      <c r="A30" s="133"/>
       <c r="B30" s="38">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -3434,7 +3491,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="123"/>
+      <c r="A31" s="133"/>
       <c r="B31" s="38">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3467,7 +3524,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="123"/>
+      <c r="A32" s="133"/>
       <c r="B32" s="38">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -3500,7 +3557,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="123"/>
+      <c r="A33" s="133"/>
       <c r="B33" s="38">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -3527,7 +3584,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="123"/>
+      <c r="A34" s="133"/>
       <c r="B34" s="38">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -3560,7 +3617,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="123"/>
+      <c r="A35" s="133"/>
       <c r="B35" s="38">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -3591,7 +3648,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="123"/>
+      <c r="A36" s="133"/>
       <c r="B36" s="38">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -3624,7 +3681,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="123"/>
+      <c r="A37" s="133"/>
       <c r="B37" s="38">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -3647,7 +3704,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="123"/>
+      <c r="A38" s="133"/>
       <c r="B38" s="38">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -3670,7 +3727,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="123"/>
+      <c r="A39" s="133"/>
       <c r="B39" s="38">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -3693,7 +3750,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="123"/>
+      <c r="A40" s="133"/>
       <c r="B40" s="38">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -3716,7 +3773,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="123"/>
+      <c r="A41" s="133"/>
       <c r="B41" s="38">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -3739,7 +3796,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="123"/>
+      <c r="A42" s="133"/>
       <c r="B42" s="38">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -3762,7 +3819,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="123"/>
+      <c r="A43" s="133"/>
       <c r="B43" s="38">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -3785,7 +3842,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="123"/>
+      <c r="A44" s="133"/>
       <c r="B44" s="38">
         <f t="shared" si="6"/>
         <v>25</v>
@@ -3808,7 +3865,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="123"/>
+      <c r="A45" s="133"/>
       <c r="B45" s="38">
         <f t="shared" si="6"/>
         <v>26</v>
@@ -3831,7 +3888,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="123"/>
+      <c r="A46" s="133"/>
       <c r="B46" s="38">
         <f t="shared" si="6"/>
         <v>27</v>
@@ -3854,7 +3911,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="123"/>
+      <c r="A47" s="133"/>
       <c r="B47" s="38">
         <f t="shared" si="6"/>
         <v>28</v>
@@ -3890,4 +3947,2590 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2610A015-4E55-4C5A-A6A9-925DBA45A0C3}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="128" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="134" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="41">
+        <v>1300000</v>
+      </c>
+      <c r="G7" s="41">
+        <f>IF(F7="",0,IF(F7&gt;1700000,F7*O$19,F7*O$18))</f>
+        <v>780000</v>
+      </c>
+      <c r="H7" s="41">
+        <v>780000</v>
+      </c>
+      <c r="I7" s="41">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="95"/>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="135"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41">
+        <v>1235000</v>
+      </c>
+      <c r="G8" s="41">
+        <f>IF(F8="",0,IF(F8&gt;1700000,F8*O$19,F8*O$18))</f>
+        <v>741000</v>
+      </c>
+      <c r="H8" s="41">
+        <v>620000</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="0">G8-H8</f>
+        <v>121000</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="96"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="135"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="1">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="40"/>
+      <c r="E9" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="41">
+        <v>800000</v>
+      </c>
+      <c r="G9" s="41">
+        <f>IF(F9="",0,IF(F9&gt;1700000,F9*O$19,F9*O$18))</f>
+        <v>480000</v>
+      </c>
+      <c r="H9" s="44"/>
+      <c r="I9" s="41">
+        <f t="shared" si="0"/>
+        <v>480000</v>
+      </c>
+      <c r="J9" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="96" t="s">
+        <v>117</v>
+      </c>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="135"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="44">
+        <v>1200000</v>
+      </c>
+      <c r="G10" s="41">
+        <f>IF(F10="",0,IF(F10&gt;1700000,F10*O$19,F10*O$18))</f>
+        <v>720000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>720000</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="96"/>
+      <c r="L10" s="46"/>
+      <c r="N10" s="137" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="137"/>
+      <c r="P10" s="138">
+        <f>SUM(F7:F1006)</f>
+        <v>30573000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="135"/>
+      <c r="B11" s="38">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44">
+        <v>150000</v>
+      </c>
+      <c r="G11" s="41">
+        <f>IF(F11="",0,IF(F11&gt;1700000,F11*O$19,F11*O$18))</f>
+        <v>90000</v>
+      </c>
+      <c r="H11" s="44">
+        <v>90000</v>
+      </c>
+      <c r="I11" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="96"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="138"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="135"/>
+      <c r="B12" s="38">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" ref="G12:G18" si="2">IF(F12="",0,IF(F12&gt;1700000,F12*O$19,F12*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="62"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="139" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="139"/>
+      <c r="P12" s="138">
+        <f>SUM(G7:G1006)</f>
+        <v>16022500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="135"/>
+      <c r="B13" s="38">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="62"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="139"/>
+      <c r="O13" s="139"/>
+      <c r="P13" s="138"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="135"/>
+      <c r="B14" s="38">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="139"/>
+      <c r="O14" s="139"/>
+      <c r="P14" s="138"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="135"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="140" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="140"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>15420500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="135"/>
+      <c r="B16" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="135"/>
+      <c r="B17" s="38">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="135"/>
+      <c r="B18" s="38">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="136"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="132" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="75">
+        <v>2320000</v>
+      </c>
+      <c r="G20" s="75">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>1160000</v>
+      </c>
+      <c r="H20" s="75">
+        <v>1160000</v>
+      </c>
+      <c r="I20" s="75">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K20" s="85"/>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="133"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="79">
+        <v>500000</v>
+      </c>
+      <c r="G21" s="75">
+        <f t="shared" si="3"/>
+        <v>300000</v>
+      </c>
+      <c r="H21" s="79">
+        <v>300000</v>
+      </c>
+      <c r="I21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K21" s="85"/>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="133"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75">
+        <v>2320000</v>
+      </c>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>1160000</v>
+      </c>
+      <c r="H22" s="79">
+        <v>1160000</v>
+      </c>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" s="85"/>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="133"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="73"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="62"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="133"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="75">
+        <v>1700000</v>
+      </c>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>850000</v>
+      </c>
+      <c r="H24" s="79">
+        <v>850000</v>
+      </c>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K24" s="85"/>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="133"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="75">
+        <v>1105000</v>
+      </c>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>663000</v>
+      </c>
+      <c r="H25" s="79">
+        <v>663000</v>
+      </c>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K25" s="84"/>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="133"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="73" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="75">
+        <v>1700000</v>
+      </c>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>850000</v>
+      </c>
+      <c r="H26" s="75">
+        <v>850000</v>
+      </c>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26" s="85"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="133"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="80"/>
+      <c r="E27" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="79">
+        <v>3155000</v>
+      </c>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>1577500</v>
+      </c>
+      <c r="H27" s="75">
+        <v>1577500</v>
+      </c>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K27" s="85"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="133"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="87"/>
+      <c r="E28" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" s="79">
+        <v>2065000</v>
+      </c>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>1032500</v>
+      </c>
+      <c r="H28" s="79">
+        <v>1032000</v>
+      </c>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="J28" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K28" s="91"/>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="133"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="118"/>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="62"/>
+      <c r="K29" s="106"/>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="133"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="74"/>
+      <c r="E30" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="89">
+        <v>1900000</v>
+      </c>
+      <c r="G30" s="75">
+        <f t="shared" si="3"/>
+        <v>950000</v>
+      </c>
+      <c r="H30" s="119">
+        <v>950000</v>
+      </c>
+      <c r="I30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K30" s="85"/>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="133"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="81"/>
+      <c r="E31" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="89">
+        <v>2070000</v>
+      </c>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>1035000</v>
+      </c>
+      <c r="H31" s="89">
+        <v>1035000</v>
+      </c>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31" s="106"/>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="133"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="78"/>
+      <c r="E32" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="75">
+        <v>1070000</v>
+      </c>
+      <c r="G32" s="75">
+        <f t="shared" si="3"/>
+        <v>642000</v>
+      </c>
+      <c r="H32" s="75">
+        <v>642000</v>
+      </c>
+      <c r="I32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K32" s="106"/>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="133"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="73"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="90"/>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="89"/>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="62"/>
+      <c r="K33" s="106"/>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="133"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" s="87"/>
+      <c r="E34" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="79">
+        <v>1910000</v>
+      </c>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>955000</v>
+      </c>
+      <c r="H34" s="79">
+        <v>955000</v>
+      </c>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K34" s="92"/>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="133"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="87"/>
+      <c r="E35" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" s="118">
+        <v>1890000</v>
+      </c>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>945000</v>
+      </c>
+      <c r="H35" s="118">
+        <v>945000</v>
+      </c>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K35" s="85"/>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="133"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="120"/>
+      <c r="E36" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="118">
+        <v>2183000</v>
+      </c>
+      <c r="G36" s="75">
+        <f t="shared" si="3"/>
+        <v>1091500</v>
+      </c>
+      <c r="H36" s="118">
+        <v>1091000</v>
+      </c>
+      <c r="I36" s="75">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="J36" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K36" s="96"/>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="133"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="99"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="100"/>
+      <c r="G37" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="89"/>
+      <c r="I37" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="83"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="133"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="100"/>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="89"/>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="83"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="133"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="100"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="133"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="100"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="133"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="133"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="133"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="133"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="133"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="133"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="133"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF137B8B-2BBD-4D18-BE8C-6301B6B835E6}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="128" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="134" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="41">
+        <v>1100000</v>
+      </c>
+      <c r="G7" s="41">
+        <f>IF(F7="",0,IF(F7&gt;1700000,F7*O$19,F7*O$18))</f>
+        <v>660000</v>
+      </c>
+      <c r="H7" s="41">
+        <v>660000</v>
+      </c>
+      <c r="I7" s="41">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="95"/>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="135"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41">
+        <v>1145000</v>
+      </c>
+      <c r="G8" s="41">
+        <f>IF(F8="",0,IF(F8&gt;1700000,F8*O$19,F8*O$18))</f>
+        <v>687000</v>
+      </c>
+      <c r="H8" s="41">
+        <v>570000</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="0">G8-H8</f>
+        <v>117000</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="96"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="135"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="1">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="122" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125">
+        <f>IF(F9="",0,IF(F9&gt;1700000,F9*O$19,F9*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="126"/>
+      <c r="I9" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="127"/>
+      <c r="K9" s="96" t="s">
+        <v>119</v>
+      </c>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="135"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="44">
+        <v>1000000</v>
+      </c>
+      <c r="G10" s="41">
+        <f>IF(F10="",0,IF(F10&gt;1700000,F10*O$19,F10*O$18))</f>
+        <v>600000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>600000</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="96"/>
+      <c r="L10" s="46"/>
+      <c r="N10" s="137" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="137"/>
+      <c r="P10" s="138">
+        <f>SUM(F7:F1006)</f>
+        <v>3545000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="135"/>
+      <c r="B11" s="38">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44">
+        <v>300000</v>
+      </c>
+      <c r="G11" s="41">
+        <f>IF(F11="",0,IF(F11&gt;1700000,F11*O$19,F11*O$18))</f>
+        <v>180000</v>
+      </c>
+      <c r="H11" s="44">
+        <v>180000</v>
+      </c>
+      <c r="I11" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="96"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="138"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="135"/>
+      <c r="B12" s="38">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" ref="G12:G18" si="2">IF(F12="",0,IF(F12&gt;1700000,F12*O$19,F12*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="62"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="139" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="139"/>
+      <c r="P12" s="138">
+        <f>SUM(G7:G1006)</f>
+        <v>2127000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="135"/>
+      <c r="B13" s="38">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="62"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="139"/>
+      <c r="O13" s="139"/>
+      <c r="P13" s="138"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="135"/>
+      <c r="B14" s="38">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="139"/>
+      <c r="O14" s="139"/>
+      <c r="P14" s="138"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="135"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="140" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="140"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>2010000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="135"/>
+      <c r="B16" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="135"/>
+      <c r="B17" s="38">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="135"/>
+      <c r="B18" s="38">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="136"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="132" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="75"/>
+      <c r="I20" s="75">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="49"/>
+      <c r="K20" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="133"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="79"/>
+      <c r="G21" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="79"/>
+      <c r="I21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="49"/>
+      <c r="K21" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="133"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="79"/>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="49"/>
+      <c r="K22" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="133"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="73"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="62"/>
+      <c r="K23" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="133"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="79"/>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="49"/>
+      <c r="K24" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="133"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="79"/>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="49"/>
+      <c r="K25" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="133"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="73" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="49"/>
+      <c r="K26" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="133"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="80"/>
+      <c r="E27" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="79"/>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="49"/>
+      <c r="K27" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="133"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="87"/>
+      <c r="E28" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" s="79"/>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="79"/>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="49"/>
+      <c r="K28" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="133"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="118"/>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="62"/>
+      <c r="K29" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="133"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="74"/>
+      <c r="E30" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="89"/>
+      <c r="G30" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="119"/>
+      <c r="I30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="49"/>
+      <c r="K30" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="133"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="81"/>
+      <c r="E31" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="89"/>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="89"/>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="49"/>
+      <c r="K31" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="133"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="78"/>
+      <c r="E32" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="49"/>
+      <c r="K32" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="133"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="73"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="90"/>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="89"/>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="62"/>
+      <c r="K33" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="133"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" s="87"/>
+      <c r="E34" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="79"/>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="79"/>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="49"/>
+      <c r="K34" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="133"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="87"/>
+      <c r="E35" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" s="118"/>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="118"/>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="49"/>
+      <c r="K35" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="133"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="120"/>
+      <c r="E36" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="118"/>
+      <c r="G36" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="118"/>
+      <c r="I36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="49"/>
+      <c r="K36" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="133"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="99"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="100"/>
+      <c r="G37" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="89"/>
+      <c r="I37" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="83"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="133"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="100"/>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="89"/>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="83"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="133"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="100"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="133"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="100"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="133"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="133"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="133"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="133"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="133"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="133"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="133"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D96A686-3431-437A-9B53-B9741F514FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CAC15FD-6A0B-4CEF-95CE-BFFEA51AA28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10-01" sheetId="14" state="hidden" r:id="rId1"/>
     <sheet name="01-02" sheetId="37" r:id="rId2"/>
     <sheet name="02-02" sheetId="38" r:id="rId3"/>
     <sheet name="03-02" sheetId="39" r:id="rId4"/>
+    <sheet name="04-02" sheetId="40" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="138">
   <si>
     <t>STT</t>
   </si>
@@ -400,13 +401,64 @@
   </si>
   <si>
     <t>DOANH THU 03/02/2026</t>
+  </si>
+  <si>
+    <t>4189k</t>
+  </si>
+  <si>
+    <t>NGUYỄN TUẤN ANH</t>
+  </si>
+  <si>
+    <t>NGUYỄN HOÀI PHƯƠNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LÊ VĂN TÙNG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LÊ THÀNH LẬP (Hiếu) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRẦN THANH THANH  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGUYỄN QUỐC NAM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRẦN VIẾT HÙNG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VŨ ĐỨC HẠNH </t>
+  </si>
+  <si>
+    <t>TRƯƠNG THANH TÚ</t>
+  </si>
+  <si>
+    <t>2445 nhưng tính 2tr, còn 445 hnay</t>
+  </si>
+  <si>
+    <t>Nhậu say quá ngủ nguyên ngày</t>
+  </si>
+  <si>
+    <t>THUẬN NGÔ</t>
+  </si>
+  <si>
+    <t>ĐINH ĐOÀN</t>
+  </si>
+  <si>
+    <t>đưa dư 140k</t>
+  </si>
+  <si>
+    <t>chuyển dư 214k</t>
+  </si>
+  <si>
+    <t>DOANH THU 04/02/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -617,6 +669,11 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -879,7 +936,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1226,6 +1283,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1833,32 +1917,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="128" t="s">
+      <c r="B2" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="129" t="s">
+      <c r="B3" s="138" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="139"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="139"/>
+      <c r="I3" s="139"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="139"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="21"/>
@@ -2516,20 +2600,20 @@
       <c r="F26" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="131" t="s">
+      <c r="H26" s="140" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="131"/>
+      <c r="I26" s="140"/>
       <c r="J26" s="5">
         <f>SUM(H7:H1001)</f>
         <v>28869000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="131" t="s">
+      <c r="H27" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="131"/>
+      <c r="I27" s="140"/>
       <c r="J27" s="5">
         <f>SUM(I7:I1001)</f>
         <v>17311000</v>
@@ -2667,18 +2751,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="128" t="s">
+      <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="128"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="128"/>
-      <c r="G3" s="128"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="128"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -2732,7 +2816,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="143" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -2769,7 +2853,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="135"/>
+      <c r="A8" s="144"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -2805,7 +2889,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="135"/>
+      <c r="A9" s="144"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -2837,7 +2921,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="135"/>
+      <c r="A10" s="144"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -2868,17 +2952,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="137" t="s">
+      <c r="N10" s="146" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="137"/>
-      <c r="P10" s="138">
+      <c r="O10" s="146"/>
+      <c r="P10" s="147">
         <f>SUM(F7:F1006)</f>
         <v>16675000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="135"/>
+      <c r="A11" s="144"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -2909,12 +2993,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="138"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="147"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="135"/>
+      <c r="A12" s="144"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -2939,17 +3023,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="139" t="s">
+      <c r="N12" s="148" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="139"/>
-      <c r="P12" s="138">
+      <c r="O12" s="148"/>
+      <c r="P12" s="147">
         <f>SUM(G7:G1006)</f>
         <v>9346000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="135"/>
+      <c r="A13" s="144"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -2974,12 +3058,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="139"/>
-      <c r="O13" s="139"/>
-      <c r="P13" s="138"/>
+      <c r="N13" s="148"/>
+      <c r="O13" s="148"/>
+      <c r="P13" s="147"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="135"/>
+      <c r="A14" s="144"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -3004,12 +3088,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="139"/>
-      <c r="O14" s="139"/>
-      <c r="P14" s="138"/>
+      <c r="N14" s="148"/>
+      <c r="O14" s="148"/>
+      <c r="P14" s="147"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="135"/>
+      <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -3034,17 +3118,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="140" t="s">
+      <c r="N15" s="149" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="140"/>
+      <c r="O15" s="149"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>9285000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="135"/>
+      <c r="A16" s="144"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -3071,7 +3155,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="135"/>
+      <c r="A17" s="144"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -3098,7 +3182,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="135"/>
+      <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3134,7 +3218,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="136"/>
+      <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -3157,7 +3241,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="132" t="s">
+      <c r="A20" s="141" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -3189,7 +3273,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="133"/>
+      <c r="A21" s="142"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -3222,7 +3306,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="133"/>
+      <c r="A22" s="142"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="6">B21+1</f>
         <v>3</v>
@@ -3253,7 +3337,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="133"/>
+      <c r="A23" s="142"/>
       <c r="B23" s="38">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -3276,7 +3360,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="133"/>
+      <c r="A24" s="142"/>
       <c r="B24" s="38">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -3307,7 +3391,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="133"/>
+      <c r="A25" s="142"/>
       <c r="B25" s="38">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -3340,7 +3424,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="133"/>
+      <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -3371,7 +3455,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="133"/>
+      <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -3404,7 +3488,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="133"/>
+      <c r="A28" s="142"/>
       <c r="B28" s="38">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -3437,7 +3521,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="133"/>
+      <c r="A29" s="142"/>
       <c r="B29" s="38">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -3460,7 +3544,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="133"/>
+      <c r="A30" s="142"/>
       <c r="B30" s="38">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -3491,7 +3575,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="133"/>
+      <c r="A31" s="142"/>
       <c r="B31" s="38">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3524,7 +3608,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="133"/>
+      <c r="A32" s="142"/>
       <c r="B32" s="38">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -3557,7 +3641,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="133"/>
+      <c r="A33" s="142"/>
       <c r="B33" s="38">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -3584,7 +3668,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="133"/>
+      <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -3617,7 +3701,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="133"/>
+      <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -3648,7 +3732,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="133"/>
+      <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -3681,7 +3765,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="133"/>
+      <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -3704,7 +3788,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="133"/>
+      <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -3727,7 +3811,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="133"/>
+      <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -3750,7 +3834,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="133"/>
+      <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -3773,7 +3857,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="133"/>
+      <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -3796,7 +3880,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="133"/>
+      <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -3819,7 +3903,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="133"/>
+      <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -3842,7 +3926,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="133"/>
+      <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="6"/>
         <v>25</v>
@@ -3865,7 +3949,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="133"/>
+      <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="6"/>
         <v>26</v>
@@ -3888,7 +3972,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="133"/>
+      <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="6"/>
         <v>27</v>
@@ -3911,7 +3995,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="133"/>
+      <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="6"/>
         <v>28</v>
@@ -3976,18 +4060,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="128" t="s">
+      <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="128"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="128"/>
-      <c r="G3" s="128"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="128"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -4041,7 +4125,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="143" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -4078,7 +4162,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="135"/>
+      <c r="A8" s="144"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -4114,7 +4198,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="135"/>
+      <c r="A9" s="144"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -4147,7 +4231,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="135"/>
+      <c r="A10" s="144"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -4178,17 +4262,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="137" t="s">
+      <c r="N10" s="146" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="137"/>
-      <c r="P10" s="138">
+      <c r="O10" s="146"/>
+      <c r="P10" s="147">
         <f>SUM(F7:F1006)</f>
         <v>30573000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="135"/>
+      <c r="A11" s="144"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -4219,12 +4303,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="138"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="147"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="135"/>
+      <c r="A12" s="144"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -4249,17 +4333,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="139" t="s">
+      <c r="N12" s="148" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="139"/>
-      <c r="P12" s="138">
+      <c r="O12" s="148"/>
+      <c r="P12" s="147">
         <f>SUM(G7:G1006)</f>
         <v>16022500</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="135"/>
+      <c r="A13" s="144"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -4284,12 +4368,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="139"/>
-      <c r="O13" s="139"/>
-      <c r="P13" s="138"/>
+      <c r="N13" s="148"/>
+      <c r="O13" s="148"/>
+      <c r="P13" s="147"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="135"/>
+      <c r="A14" s="144"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -4314,12 +4398,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="139"/>
-      <c r="O14" s="139"/>
-      <c r="P14" s="138"/>
+      <c r="N14" s="148"/>
+      <c r="O14" s="148"/>
+      <c r="P14" s="147"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="135"/>
+      <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -4344,17 +4428,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="140" t="s">
+      <c r="N15" s="149" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="140"/>
+      <c r="O15" s="149"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>15420500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="135"/>
+      <c r="A16" s="144"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -4381,7 +4465,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="135"/>
+      <c r="A17" s="144"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -4408,7 +4492,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="135"/>
+      <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -4444,7 +4528,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="136"/>
+      <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -4467,7 +4551,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="132" t="s">
+      <c r="A20" s="141" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -4501,7 +4585,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="133"/>
+      <c r="A21" s="142"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -4534,7 +4618,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="133"/>
+      <c r="A22" s="142"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -4567,7 +4651,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="133"/>
+      <c r="A23" s="142"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -4590,7 +4674,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="133"/>
+      <c r="A24" s="142"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -4623,7 +4707,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="133"/>
+      <c r="A25" s="142"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -4656,7 +4740,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="133"/>
+      <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -4689,7 +4773,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="133"/>
+      <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -4722,7 +4806,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="133"/>
+      <c r="A28" s="142"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -4755,7 +4839,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="133"/>
+      <c r="A29" s="142"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -4778,7 +4862,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="133"/>
+      <c r="A30" s="142"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -4811,7 +4895,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="133"/>
+      <c r="A31" s="142"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -4844,7 +4928,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="133"/>
+      <c r="A32" s="142"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -4877,7 +4961,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="133"/>
+      <c r="A33" s="142"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -4902,7 +4986,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="133"/>
+      <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -4935,7 +5019,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="133"/>
+      <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -4968,7 +5052,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="133"/>
+      <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -5001,7 +5085,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="133"/>
+      <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -5024,7 +5108,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="133"/>
+      <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -5047,7 +5131,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="133"/>
+      <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -5070,7 +5154,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="133"/>
+      <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -5093,7 +5177,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="133"/>
+      <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -5116,7 +5200,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="133"/>
+      <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -5139,7 +5223,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="133"/>
+      <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -5162,7 +5246,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="133"/>
+      <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -5185,7 +5269,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="133"/>
+      <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -5208,7 +5292,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="133"/>
+      <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -5231,7 +5315,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="133"/>
+      <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -5296,18 +5380,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="128" t="s">
+      <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="128"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="128"/>
-      <c r="G3" s="128"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="128"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -5361,7 +5445,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="143" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -5398,7 +5482,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="135"/>
+      <c r="A8" s="144"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -5434,7 +5518,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="135"/>
+      <c r="A9" s="144"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -5463,7 +5547,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="135"/>
+      <c r="A10" s="144"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -5494,17 +5578,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="137" t="s">
+      <c r="N10" s="146" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="137"/>
-      <c r="P10" s="138">
+      <c r="O10" s="146"/>
+      <c r="P10" s="147">
         <f>SUM(F7:F1006)</f>
         <v>3545000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="135"/>
+      <c r="A11" s="144"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -5535,12 +5619,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="138"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="147"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="135"/>
+      <c r="A12" s="144"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -5565,17 +5649,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="139" t="s">
+      <c r="N12" s="148" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="139"/>
-      <c r="P12" s="138">
+      <c r="O12" s="148"/>
+      <c r="P12" s="147">
         <f>SUM(G7:G1006)</f>
         <v>2127000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="135"/>
+      <c r="A13" s="144"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -5600,12 +5684,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="139"/>
-      <c r="O13" s="139"/>
-      <c r="P13" s="138"/>
+      <c r="N13" s="148"/>
+      <c r="O13" s="148"/>
+      <c r="P13" s="147"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="135"/>
+      <c r="A14" s="144"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -5630,12 +5714,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="139"/>
-      <c r="O14" s="139"/>
-      <c r="P14" s="138"/>
+      <c r="N14" s="148"/>
+      <c r="O14" s="148"/>
+      <c r="P14" s="147"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="135"/>
+      <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -5660,17 +5744,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="140" t="s">
+      <c r="N15" s="149" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="140"/>
+      <c r="O15" s="149"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>2010000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="135"/>
+      <c r="A16" s="144"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -5697,7 +5781,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="135"/>
+      <c r="A17" s="144"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -5724,7 +5808,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="135"/>
+      <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -5760,7 +5844,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="136"/>
+      <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -5783,7 +5867,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="132" t="s">
+      <c r="A20" s="141" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -5813,7 +5897,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="133"/>
+      <c r="A21" s="142"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -5842,7 +5926,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="133"/>
+      <c r="A22" s="142"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -5871,7 +5955,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="133"/>
+      <c r="A23" s="142"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -5896,7 +5980,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="133"/>
+      <c r="A24" s="142"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -5925,7 +6009,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="133"/>
+      <c r="A25" s="142"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -5954,7 +6038,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="133"/>
+      <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -5983,7 +6067,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="133"/>
+      <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -6012,7 +6096,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="133"/>
+      <c r="A28" s="142"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -6041,7 +6125,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="133"/>
+      <c r="A29" s="142"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -6066,7 +6150,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="133"/>
+      <c r="A30" s="142"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -6095,7 +6179,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="133"/>
+      <c r="A31" s="142"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -6124,7 +6208,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="133"/>
+      <c r="A32" s="142"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -6153,7 +6237,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="133"/>
+      <c r="A33" s="142"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -6180,7 +6264,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="133"/>
+      <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -6209,7 +6293,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="133"/>
+      <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -6238,7 +6322,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="133"/>
+      <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -6267,7 +6351,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="133"/>
+      <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -6290,7 +6374,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="133"/>
+      <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -6313,7 +6397,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="133"/>
+      <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -6336,7 +6420,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="133"/>
+      <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -6359,7 +6443,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="133"/>
+      <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -6382,7 +6466,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="133"/>
+      <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -6405,7 +6489,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="133"/>
+      <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -6428,7 +6512,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="133"/>
+      <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -6451,7 +6535,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="133"/>
+      <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -6474,7 +6558,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="133"/>
+      <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -6497,7 +6581,1357 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="133"/>
+      <c r="A47" s="142"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C31C35F-5774-4DEE-9905-7B7C61A41D99}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="137" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="143" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="41">
+        <v>1200000</v>
+      </c>
+      <c r="G7" s="41">
+        <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
+        <v>720000</v>
+      </c>
+      <c r="H7" s="41">
+        <v>720000</v>
+      </c>
+      <c r="I7" s="41">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="129"/>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="144"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41">
+        <f t="shared" ref="G8:G18" si="0">IF(F8="",0,IF(F8&gt;1800000,F8*O$19,F8*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="1">G8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="128"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="144"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="2">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="122" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="126"/>
+      <c r="I9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="127"/>
+      <c r="K9" s="130" t="s">
+        <v>114</v>
+      </c>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="144"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="44">
+        <v>1150000</v>
+      </c>
+      <c r="G10" s="41">
+        <f t="shared" si="0"/>
+        <v>690000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>690000</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="130"/>
+      <c r="L10" s="46"/>
+      <c r="N10" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="146"/>
+      <c r="P10" s="147">
+        <f>SUM(F7:F1006)</f>
+        <v>40751000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="144"/>
+      <c r="B11" s="38">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44">
+        <v>200000</v>
+      </c>
+      <c r="G11" s="41">
+        <f t="shared" si="0"/>
+        <v>120000</v>
+      </c>
+      <c r="H11" s="44">
+        <v>120000</v>
+      </c>
+      <c r="I11" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="130"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="147"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="144"/>
+      <c r="B12" s="38">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="62"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="148"/>
+      <c r="P12" s="147">
+        <f>SUM(G7:G1006)</f>
+        <v>20907500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="144"/>
+      <c r="B13" s="38">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="62"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="148"/>
+      <c r="O13" s="148"/>
+      <c r="P13" s="147"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="144"/>
+      <c r="B14" s="38">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="148"/>
+      <c r="O14" s="148"/>
+      <c r="P14" s="147"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="144"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="149" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="149"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>21280000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="144"/>
+      <c r="B16" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="144"/>
+      <c r="B17" s="38">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="144"/>
+      <c r="B18" s="38">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="145"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="141" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="75">
+        <v>2500000</v>
+      </c>
+      <c r="G20" s="75">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>1250000</v>
+      </c>
+      <c r="H20" s="75">
+        <v>1250000</v>
+      </c>
+      <c r="I20" s="75">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K20" s="132"/>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="142"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="133" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="134"/>
+      <c r="E21" s="134" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="115"/>
+      <c r="G21" s="109">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="115"/>
+      <c r="I21" s="109">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="135"/>
+      <c r="K21" s="136" t="s">
+        <v>132</v>
+      </c>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="142"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75">
+        <v>2340000</v>
+      </c>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>1170000</v>
+      </c>
+      <c r="H22" s="79">
+        <v>1170000</v>
+      </c>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" s="132"/>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="142"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="73" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="75">
+        <v>1430000</v>
+      </c>
+      <c r="G23" s="75">
+        <f t="shared" si="3"/>
+        <v>858000</v>
+      </c>
+      <c r="H23" s="75">
+        <v>858000</v>
+      </c>
+      <c r="I23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K23" s="132"/>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="142"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="75">
+        <v>2840000</v>
+      </c>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>1420000</v>
+      </c>
+      <c r="H24" s="79">
+        <v>1420000</v>
+      </c>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K24" s="132"/>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="142"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="75">
+        <v>2170000</v>
+      </c>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>1085000</v>
+      </c>
+      <c r="H25" s="79">
+        <v>1100000</v>
+      </c>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>-15000</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K25" s="132"/>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="142"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="75">
+        <v>2592000</v>
+      </c>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>1296000</v>
+      </c>
+      <c r="H26" s="75">
+        <v>1296000</v>
+      </c>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26" s="132"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="142"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="87"/>
+      <c r="E27" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="79">
+        <v>2888000</v>
+      </c>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>1444000</v>
+      </c>
+      <c r="H27" s="75">
+        <v>1444000</v>
+      </c>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K27" s="132"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="142"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="79">
+        <v>2000000</v>
+      </c>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+      <c r="H28" s="79">
+        <v>1000000</v>
+      </c>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K28" s="132" t="s">
+        <v>131</v>
+      </c>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="142"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="118">
+        <v>4180000</v>
+      </c>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>2090000</v>
+      </c>
+      <c r="H29" s="118">
+        <v>2090000</v>
+      </c>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K29" s="132" t="s">
+        <v>121</v>
+      </c>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="142"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="78"/>
+      <c r="E30" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="89">
+        <v>2070000</v>
+      </c>
+      <c r="G30" s="75">
+        <f t="shared" si="3"/>
+        <v>1035000</v>
+      </c>
+      <c r="H30" s="119">
+        <v>1035000</v>
+      </c>
+      <c r="I30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K30" s="132"/>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="142"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="89">
+        <v>2490000</v>
+      </c>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>1245000</v>
+      </c>
+      <c r="H31" s="89">
+        <v>1245000</v>
+      </c>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31" s="132"/>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="142"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="87"/>
+      <c r="E32" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="75">
+        <v>1340000</v>
+      </c>
+      <c r="G32" s="75">
+        <f t="shared" si="3"/>
+        <v>804000</v>
+      </c>
+      <c r="H32" s="75">
+        <v>804000</v>
+      </c>
+      <c r="I32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K32" s="132"/>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="142"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="87"/>
+      <c r="E33" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="90">
+        <v>2146000</v>
+      </c>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>1073000</v>
+      </c>
+      <c r="H33" s="89">
+        <v>1287000</v>
+      </c>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>-214000</v>
+      </c>
+      <c r="J33" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K33" s="89" t="s">
+        <v>136</v>
+      </c>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="142"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="79">
+        <v>3385000</v>
+      </c>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>1692500</v>
+      </c>
+      <c r="H34" s="79">
+        <v>1831000</v>
+      </c>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>-138500</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K34" s="132" t="s">
+        <v>135</v>
+      </c>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="142"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="93" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="57"/>
+      <c r="E35" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="118">
+        <v>1770000</v>
+      </c>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>885000</v>
+      </c>
+      <c r="H35" s="118">
+        <v>890000</v>
+      </c>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>-5000</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K35" s="132"/>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="142"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="57"/>
+      <c r="E36" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="118">
+        <v>2060000</v>
+      </c>
+      <c r="G36" s="75">
+        <f t="shared" si="3"/>
+        <v>1030000</v>
+      </c>
+      <c r="H36" s="118">
+        <v>1030000</v>
+      </c>
+      <c r="I36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K36" s="132"/>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="142"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="43"/>
+      <c r="E37" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="90"/>
+      <c r="G37" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="89"/>
+      <c r="I37" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="83"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="142"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="43"/>
+      <c r="E38" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="90"/>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="89"/>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="83"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="142"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="100"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="142"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="100"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="142"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="142"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="142"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="142"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="142"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="142"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>

--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CAC15FD-6A0B-4CEF-95CE-BFFEA51AA28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A034745A-13E2-488D-A9EA-DF2793F9BD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="579" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10-01" sheetId="14" state="hidden" r:id="rId1"/>
@@ -18,27 +18,19 @@
     <sheet name="02-02" sheetId="38" r:id="rId3"/>
     <sheet name="03-02" sheetId="39" r:id="rId4"/>
     <sheet name="04-02" sheetId="40" r:id="rId5"/>
+    <sheet name="05-02" sheetId="41" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="139">
   <si>
     <t>STT</t>
   </si>
@@ -452,6 +444,9 @@
   </si>
   <si>
     <t>DOANH THU 04/02/2026</t>
+  </si>
+  <si>
+    <t>DOANH THU 05/02/2026</t>
   </si>
 </sst>
 </file>
@@ -1896,24 +1891,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25421AD-4B15-4CE5-B032-F166D9527995}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A2:P59"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.44140625" style="1" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="21" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" style="1" customWidth="1"/>
-    <col min="14" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="16.85546875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="19.44140625" style="1" customWidth="1"/>
+    <col min="14" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="16.88671875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1930,7 +1925,7 @@
       <c r="J2" s="137"/>
       <c r="K2" s="137"/>
     </row>
-    <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="B3" s="138" t="s">
         <v>85</v>
       </c>
@@ -1947,7 +1942,7 @@
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="21"/>
     </row>
-    <row r="6" spans="2:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="21" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -1988,7 +1983,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>1</v>
       </c>
@@ -2023,7 +2018,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <f t="shared" ref="B8:B23" si="0">B7 +1</f>
         <v>2</v>
@@ -2061,7 +2056,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2095,7 +2090,7 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2129,7 +2124,7 @@
       <c r="L10" s="37"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10 +1</f>
         <v>5</v>
@@ -2165,7 +2160,7 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2199,7 +2194,7 @@
       <c r="L12" s="8"/>
       <c r="M12" s="9"/>
     </row>
-    <row r="13" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2235,7 +2230,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2268,7 +2263,7 @@
       <c r="L14" s="8"/>
       <c r="M14" s="9"/>
     </row>
-    <row r="15" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2302,7 +2297,7 @@
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
     </row>
-    <row r="16" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2336,7 +2331,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2370,7 +2365,7 @@
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
     </row>
-    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2406,7 +2401,7 @@
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
     </row>
-    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2439,7 +2434,7 @@
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
     </row>
-    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="B20" s="3">
         <f t="shared" si="0"/>
@@ -2472,7 +2467,7 @@
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
     </row>
-    <row r="21" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="A21" s="25"/>
       <c r="B21" s="3">
         <f t="shared" si="0"/>
@@ -2505,7 +2500,7 @@
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
     </row>
-    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2539,7 +2534,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="8"/>
     </row>
-    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2573,7 +2568,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="8"/>
     </row>
-    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -2590,7 +2585,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="8"/>
     </row>
-    <row r="26" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="22.8" x14ac:dyDescent="0.4">
       <c r="C26" s="18" t="s">
         <v>60</v>
       </c>
@@ -2609,7 +2604,7 @@
         <v>28869000</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="22.8" x14ac:dyDescent="0.4">
       <c r="H27" s="140" t="s">
         <v>29</v>
       </c>
@@ -2629,17 +2624,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B44" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B45" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B46" s="12" t="s">
         <v>16</v>
       </c>
@@ -2647,67 +2642,67 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B47" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B48" s="12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B49" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B51" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B53" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B55" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B56" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B57" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="58" spans="2:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="31" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:2" ht="14.4" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:K2"/>
@@ -2727,30 +2722,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBEB86F-A8DD-42F9-B2B2-37DBDB0C26B6}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
       <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
@@ -2764,7 +2759,7 @@
       <c r="J3" s="137"/>
       <c r="K3" s="137"/>
     </row>
-    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -3092,7 +3087,7 @@
       <c r="O14" s="148"/>
       <c r="P14" s="147"/>
     </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
@@ -3181,7 +3176,7 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
@@ -3217,7 +3212,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
@@ -3423,7 +3418,7 @@
       <c r="K25" s="84"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="6"/>
@@ -3454,7 +3449,7 @@
       </c>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="6"/>
@@ -3487,7 +3482,7 @@
       <c r="K27" s="85"/>
       <c r="L27" s="76"/>
     </row>
-    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="142"/>
       <c r="B28" s="38">
         <f t="shared" si="6"/>
@@ -3520,7 +3515,7 @@
       <c r="K28" s="91"/>
       <c r="L28" s="76"/>
     </row>
-    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="142"/>
       <c r="B29" s="38">
         <f t="shared" si="6"/>
@@ -3574,7 +3569,7 @@
       </c>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="142"/>
       <c r="B31" s="38">
         <f t="shared" si="6"/>
@@ -3607,7 +3602,7 @@
       <c r="K31" s="106"/>
       <c r="L31" s="93"/>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="142"/>
       <c r="B32" s="38">
         <f t="shared" si="6"/>
@@ -3640,7 +3635,7 @@
       <c r="K32" s="106"/>
       <c r="L32" s="93"/>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="142"/>
       <c r="B33" s="38">
         <f t="shared" si="6"/>
@@ -3667,7 +3662,7 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="6"/>
@@ -3700,7 +3695,7 @@
       <c r="K34" s="92"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="6"/>
@@ -3731,7 +3726,7 @@
       </c>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="6"/>
@@ -3764,7 +3759,7 @@
       <c r="K36" s="96"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="6"/>
@@ -3787,7 +3782,7 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="6"/>
@@ -3810,7 +3805,7 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="6"/>
@@ -3833,7 +3828,7 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="6"/>
@@ -3856,7 +3851,7 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="6"/>
@@ -3879,7 +3874,7 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="6"/>
@@ -3902,7 +3897,7 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="6"/>
@@ -3925,7 +3920,7 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="6"/>
@@ -3948,7 +3943,7 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="6"/>
@@ -3971,7 +3966,7 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="6"/>
@@ -3994,7 +3989,7 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="6"/>
@@ -4036,30 +4031,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2610A015-4E55-4C5A-A6A9-925DBA45A0C3}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
       <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
@@ -4073,7 +4068,7 @@
       <c r="J3" s="137"/>
       <c r="K3" s="137"/>
     </row>
-    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -4402,7 +4397,7 @@
       <c r="O14" s="148"/>
       <c r="P14" s="147"/>
     </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
@@ -4491,7 +4486,7 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
@@ -4527,7 +4522,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
@@ -4739,7 +4734,7 @@
       <c r="K25" s="84"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
@@ -4772,7 +4767,7 @@
       <c r="K26" s="85"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
@@ -4805,7 +4800,7 @@
       <c r="K27" s="85"/>
       <c r="L27" s="76"/>
     </row>
-    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="142"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
@@ -4838,7 +4833,7 @@
       <c r="K28" s="91"/>
       <c r="L28" s="76"/>
     </row>
-    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="142"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
@@ -4894,7 +4889,7 @@
       <c r="K30" s="85"/>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="142"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
@@ -4927,7 +4922,7 @@
       <c r="K31" s="106"/>
       <c r="L31" s="93"/>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="142"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
@@ -4960,7 +4955,7 @@
       <c r="K32" s="106"/>
       <c r="L32" s="93"/>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="142"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
@@ -4985,7 +4980,7 @@
       <c r="K33" s="106"/>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
@@ -5018,7 +5013,7 @@
       <c r="K34" s="92"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
@@ -5051,7 +5046,7 @@
       <c r="K35" s="85"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
@@ -5084,7 +5079,7 @@
       <c r="K36" s="96"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
@@ -5107,7 +5102,7 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
@@ -5130,7 +5125,7 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
@@ -5153,7 +5148,7 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
@@ -5176,7 +5171,7 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
@@ -5199,7 +5194,7 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
@@ -5222,7 +5217,7 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
@@ -5245,7 +5240,7 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
@@ -5268,7 +5263,7 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
@@ -5291,7 +5286,7 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
@@ -5314,7 +5309,7 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
@@ -5356,30 +5351,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF137B8B-2BBD-4D18-BE8C-6301B6B835E6}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
       <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
@@ -5393,7 +5388,7 @@
       <c r="J3" s="137"/>
       <c r="K3" s="137"/>
     </row>
-    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -5718,7 +5713,7 @@
       <c r="O14" s="148"/>
       <c r="P14" s="147"/>
     </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
@@ -5807,7 +5802,7 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
@@ -5843,7 +5838,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
@@ -6037,7 +6032,7 @@
       </c>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
@@ -6066,7 +6061,7 @@
       </c>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
@@ -6263,7 +6258,7 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
@@ -6292,7 +6287,7 @@
       </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
@@ -6321,7 +6316,7 @@
       </c>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
@@ -6350,7 +6345,7 @@
       </c>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
@@ -6373,7 +6368,7 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
@@ -6396,7 +6391,7 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
@@ -6419,7 +6414,7 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
@@ -6442,7 +6437,7 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
@@ -6465,7 +6460,7 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
@@ -6488,7 +6483,7 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
@@ -6511,7 +6506,7 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
@@ -6534,7 +6529,7 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
@@ -6557,7 +6552,7 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
@@ -6580,7 +6575,7 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
@@ -6622,30 +6617,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C31C35F-5774-4DEE-9905-7B7C61A41D99}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
       <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
@@ -6659,7 +6654,7 @@
       <c r="J3" s="137"/>
       <c r="K3" s="137"/>
     </row>
-    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -6976,7 +6971,7 @@
       <c r="O14" s="148"/>
       <c r="P14" s="147"/>
     </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
@@ -7061,7 +7056,7 @@
       <c r="K17" s="130"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
@@ -7095,7 +7090,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
@@ -7313,7 +7308,7 @@
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
@@ -7346,7 +7341,7 @@
       <c r="K26" s="132"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
@@ -7583,7 +7578,7 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
@@ -7618,7 +7613,7 @@
       </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
@@ -7651,7 +7646,7 @@
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
@@ -7684,7 +7679,7 @@
       <c r="K36" s="132"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
@@ -7711,7 +7706,7 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
@@ -7738,7 +7733,7 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
@@ -7763,7 +7758,7 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
@@ -7788,7 +7783,7 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
@@ -7813,7 +7808,7 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
@@ -7838,7 +7833,7 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
@@ -7861,7 +7856,7 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
@@ -7884,7 +7879,7 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
@@ -7907,7 +7902,7 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
@@ -7930,7 +7925,1237 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="142"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA68E37-18F4-45D2-9A8A-CA2CAECC56FB}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+      <c r="B3" s="137" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="143" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41">
+        <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="128"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="144"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41">
+        <v>340000</v>
+      </c>
+      <c r="G8" s="41">
+        <f t="shared" ref="G8:G18" si="0">IF(F8="",0,IF(F8&gt;1800000,F8*O$19,F8*O$18))</f>
+        <v>204000</v>
+      </c>
+      <c r="H8" s="41">
+        <v>170000</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="1">G8-H8</f>
+        <v>34000</v>
+      </c>
+      <c r="J8" s="128"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="144"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="2">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="122" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="126"/>
+      <c r="I9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="62"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="144"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="44"/>
+      <c r="G10" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="44"/>
+      <c r="I10" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="128"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="46"/>
+      <c r="N10" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="146"/>
+      <c r="P10" s="147">
+        <f>SUM(F7:F1006)</f>
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="144"/>
+      <c r="B11" s="38">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="44"/>
+      <c r="I11" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="128"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="147"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="144"/>
+      <c r="B12" s="38">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="62"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="148"/>
+      <c r="P12" s="147">
+        <f>SUM(G7:G1006)</f>
+        <v>204000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="144"/>
+      <c r="B13" s="38">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="62"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="148"/>
+      <c r="O13" s="148"/>
+      <c r="P13" s="147"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="144"/>
+      <c r="B14" s="38">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="148"/>
+      <c r="O14" s="148"/>
+      <c r="P14" s="147"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="144"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="149" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="149"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="144"/>
+      <c r="B16" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="144"/>
+      <c r="B17" s="38">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="144"/>
+      <c r="B18" s="38">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="145"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="141" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="75"/>
+      <c r="I20" s="75">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="49"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="142"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="79"/>
+      <c r="G21" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="79"/>
+      <c r="I21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="128"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="142"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="79"/>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="49"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="142"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="73" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="49"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="142"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="79"/>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="49"/>
+      <c r="K24" s="132"/>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="142"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="79"/>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="49"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="142"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="49"/>
+      <c r="K26" s="132"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="142"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="87"/>
+      <c r="E27" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="79"/>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="49"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="142"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="79"/>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="79"/>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="49"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="142"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="118"/>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="118"/>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="49"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="142"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="78"/>
+      <c r="E30" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="89"/>
+      <c r="G30" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="119"/>
+      <c r="I30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="49"/>
+      <c r="K30" s="132"/>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="142"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="89"/>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="89"/>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="49"/>
+      <c r="K31" s="132"/>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="142"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="87"/>
+      <c r="E32" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="49"/>
+      <c r="K32" s="132"/>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="142"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="87"/>
+      <c r="E33" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="90"/>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="89"/>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="49"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A34" s="142"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="79"/>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="79"/>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="49"/>
+      <c r="K34" s="132"/>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="142"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="93" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="57"/>
+      <c r="E35" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="118"/>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="118"/>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="49"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="142"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="57"/>
+      <c r="E36" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="118"/>
+      <c r="G36" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="118"/>
+      <c r="I36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="49"/>
+      <c r="K36" s="132"/>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="142"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="43"/>
+      <c r="E37" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="90"/>
+      <c r="G37" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="89"/>
+      <c r="I37" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="83"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="142"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="43"/>
+      <c r="E38" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="90"/>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="89"/>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="83"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="142"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="100"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="142"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="100"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="142"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="142"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="142"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="142"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="142"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="142"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>

--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A034745A-13E2-488D-A9EA-DF2793F9BD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888DB4C9-4488-42C1-884F-381DFF7FB81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="579" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="579" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10-01" sheetId="14" state="hidden" r:id="rId1"/>

--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Theo dõi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A034745A-13E2-488D-A9EA-DF2793F9BD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05328CA-F2BC-4DAB-964E-2AA90F4D9141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="579" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10-01" sheetId="14" state="hidden" r:id="rId1"/>
@@ -25,12 +25,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="144">
   <si>
     <t>STT</t>
   </si>
@@ -447,6 +456,21 @@
   </si>
   <si>
     <t>DOANH THU 05/02/2026</t>
+  </si>
+  <si>
+    <t>về quê ăn tết</t>
+  </si>
+  <si>
+    <t>810k</t>
+  </si>
+  <si>
+    <t>hôm qua chuyển dư 214k</t>
+  </si>
+  <si>
+    <t>hôm qua chuyển dư 141k</t>
+  </si>
+  <si>
+    <t>doanh thu 4/2 cộng 5/2</t>
   </si>
 </sst>
 </file>
@@ -931,7 +955,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1345,6 +1369,39 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1891,24 +1948,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25421AD-4B15-4CE5-B032-F166D9527995}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A2:P59"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.42578125" style="1" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="21" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.44140625" style="1" customWidth="1"/>
-    <col min="14" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="16.88671875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="1"/>
+    <col min="13" max="13" width="19.42578125" style="1" customWidth="1"/>
+    <col min="14" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="16.85546875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1925,7 +1982,7 @@
       <c r="J2" s="137"/>
       <c r="K2" s="137"/>
     </row>
-    <row r="3" spans="2:16" ht="30.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="B3" s="138" t="s">
         <v>85</v>
       </c>
@@ -1942,7 +1999,7 @@
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="21"/>
     </row>
-    <row r="6" spans="2:16" ht="21" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:16" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -1983,7 +2040,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>1</v>
       </c>
@@ -2018,7 +2075,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <f t="shared" ref="B8:B23" si="0">B7 +1</f>
         <v>2</v>
@@ -2056,7 +2113,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2090,7 +2147,7 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2124,7 +2181,7 @@
       <c r="L10" s="37"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <f>B10 +1</f>
         <v>5</v>
@@ -2160,7 +2217,7 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2194,7 +2251,7 @@
       <c r="L12" s="8"/>
       <c r="M12" s="9"/>
     </row>
-    <row r="13" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2230,7 +2287,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2263,7 +2320,7 @@
       <c r="L14" s="8"/>
       <c r="M14" s="9"/>
     </row>
-    <row r="15" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2297,7 +2354,7 @@
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
     </row>
-    <row r="16" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2331,7 +2388,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2365,7 +2422,7 @@
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
     </row>
-    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2401,7 +2458,7 @@
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
     </row>
-    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2434,7 +2491,7 @@
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
     </row>
-    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="B20" s="3">
         <f t="shared" si="0"/>
@@ -2467,7 +2524,7 @@
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
     </row>
-    <row r="21" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="25"/>
       <c r="B21" s="3">
         <f t="shared" si="0"/>
@@ -2500,7 +2557,7 @@
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
     </row>
-    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2534,7 +2591,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="8"/>
     </row>
-    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2568,7 +2625,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="8"/>
     </row>
-    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -2585,7 +2642,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="8"/>
     </row>
-    <row r="26" spans="1:13" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
       <c r="C26" s="18" t="s">
         <v>60</v>
       </c>
@@ -2604,7 +2661,7 @@
         <v>28869000</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
       <c r="H27" s="140" t="s">
         <v>29</v>
       </c>
@@ -2624,17 +2681,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B44" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B45" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B46" s="12" t="s">
         <v>16</v>
       </c>
@@ -2642,67 +2699,67 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B47" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B48" s="12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B49" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B51" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B53" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B55" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B56" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B57" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="58" spans="2:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="31" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="2:2" ht="14.4" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:K2"/>
@@ -2722,30 +2779,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBEB86F-A8DD-42F9-B2B2-37DBDB0C26B6}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
@@ -2759,7 +2816,7 @@
       <c r="J3" s="137"/>
       <c r="K3" s="137"/>
     </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -3087,7 +3144,7 @@
       <c r="O14" s="148"/>
       <c r="P14" s="147"/>
     </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
@@ -3176,7 +3233,7 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
@@ -3212,7 +3269,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
@@ -3418,7 +3475,7 @@
       <c r="K25" s="84"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="6"/>
@@ -3449,7 +3506,7 @@
       </c>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="6"/>
@@ -3482,7 +3539,7 @@
       <c r="K27" s="85"/>
       <c r="L27" s="76"/>
     </row>
-    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="142"/>
       <c r="B28" s="38">
         <f t="shared" si="6"/>
@@ -3515,7 +3572,7 @@
       <c r="K28" s="91"/>
       <c r="L28" s="76"/>
     </row>
-    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="142"/>
       <c r="B29" s="38">
         <f t="shared" si="6"/>
@@ -3569,7 +3626,7 @@
       </c>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="142"/>
       <c r="B31" s="38">
         <f t="shared" si="6"/>
@@ -3602,7 +3659,7 @@
       <c r="K31" s="106"/>
       <c r="L31" s="93"/>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="142"/>
       <c r="B32" s="38">
         <f t="shared" si="6"/>
@@ -3635,7 +3692,7 @@
       <c r="K32" s="106"/>
       <c r="L32" s="93"/>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="142"/>
       <c r="B33" s="38">
         <f t="shared" si="6"/>
@@ -3662,7 +3719,7 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="6"/>
@@ -3695,7 +3752,7 @@
       <c r="K34" s="92"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="6"/>
@@ -3726,7 +3783,7 @@
       </c>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="6"/>
@@ -3759,7 +3816,7 @@
       <c r="K36" s="96"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="6"/>
@@ -3782,7 +3839,7 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="6"/>
@@ -3805,7 +3862,7 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="6"/>
@@ -3828,7 +3885,7 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="6"/>
@@ -3851,7 +3908,7 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="6"/>
@@ -3874,7 +3931,7 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="6"/>
@@ -3897,7 +3954,7 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="6"/>
@@ -3920,7 +3977,7 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="6"/>
@@ -3943,7 +4000,7 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="6"/>
@@ -3966,7 +4023,7 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="6"/>
@@ -3989,7 +4046,7 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="6"/>
@@ -4013,6 +4070,7 @@
       <c r="L47" s="47"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="8">
     <mergeCell ref="A20:A47"/>
     <mergeCell ref="A7:A19"/>
@@ -4031,30 +4089,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2610A015-4E55-4C5A-A6A9-925DBA45A0C3}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
@@ -4068,7 +4126,7 @@
       <c r="J3" s="137"/>
       <c r="K3" s="137"/>
     </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -4397,7 +4455,7 @@
       <c r="O14" s="148"/>
       <c r="P14" s="147"/>
     </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
@@ -4486,7 +4544,7 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
@@ -4522,7 +4580,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
@@ -4734,7 +4792,7 @@
       <c r="K25" s="84"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
@@ -4767,7 +4825,7 @@
       <c r="K26" s="85"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
@@ -4800,7 +4858,7 @@
       <c r="K27" s="85"/>
       <c r="L27" s="76"/>
     </row>
-    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="142"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
@@ -4833,7 +4891,7 @@
       <c r="K28" s="91"/>
       <c r="L28" s="76"/>
     </row>
-    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="142"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
@@ -4889,7 +4947,7 @@
       <c r="K30" s="85"/>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="142"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
@@ -4922,7 +4980,7 @@
       <c r="K31" s="106"/>
       <c r="L31" s="93"/>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="142"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
@@ -4955,7 +5013,7 @@
       <c r="K32" s="106"/>
       <c r="L32" s="93"/>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="142"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
@@ -4980,7 +5038,7 @@
       <c r="K33" s="106"/>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
@@ -5013,7 +5071,7 @@
       <c r="K34" s="92"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
@@ -5046,7 +5104,7 @@
       <c r="K35" s="85"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
@@ -5079,7 +5137,7 @@
       <c r="K36" s="96"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
@@ -5102,7 +5160,7 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
@@ -5125,7 +5183,7 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
@@ -5148,7 +5206,7 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
@@ -5171,7 +5229,7 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
@@ -5194,7 +5252,7 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
@@ -5217,7 +5275,7 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
@@ -5240,7 +5298,7 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
@@ -5263,7 +5321,7 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
@@ -5286,7 +5344,7 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
@@ -5309,7 +5367,7 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
@@ -5333,6 +5391,7 @@
       <c r="L47" s="47"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="8">
     <mergeCell ref="A20:A47"/>
     <mergeCell ref="B3:K3"/>
@@ -5351,30 +5410,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF137B8B-2BBD-4D18-BE8C-6301B6B835E6}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
@@ -5388,7 +5447,7 @@
       <c r="J3" s="137"/>
       <c r="K3" s="137"/>
     </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -5713,7 +5772,7 @@
       <c r="O14" s="148"/>
       <c r="P14" s="147"/>
     </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
@@ -5802,7 +5861,7 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
@@ -5838,7 +5897,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
@@ -6032,7 +6091,7 @@
       </c>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
@@ -6061,7 +6120,7 @@
       </c>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
@@ -6258,7 +6317,7 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
@@ -6287,7 +6346,7 @@
       </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
@@ -6316,7 +6375,7 @@
       </c>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
@@ -6345,7 +6404,7 @@
       </c>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
@@ -6368,7 +6427,7 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
@@ -6391,7 +6450,7 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
@@ -6414,7 +6473,7 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
@@ -6437,7 +6496,7 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
@@ -6460,7 +6519,7 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
@@ -6483,7 +6542,7 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
@@ -6506,7 +6565,7 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
@@ -6529,7 +6588,7 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
@@ -6552,7 +6611,7 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
@@ -6575,7 +6634,7 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
@@ -6599,6 +6658,7 @@
       <c r="L47" s="47"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="8">
     <mergeCell ref="A20:A47"/>
     <mergeCell ref="B3:K3"/>
@@ -6617,30 +6677,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C31C35F-5774-4DEE-9905-7B7C61A41D99}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
@@ -6654,7 +6714,7 @@
       <c r="J3" s="137"/>
       <c r="K3" s="137"/>
     </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -6971,7 +7031,7 @@
       <c r="O14" s="148"/>
       <c r="P14" s="147"/>
     </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
@@ -7056,7 +7116,7 @@
       <c r="K17" s="130"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
@@ -7090,7 +7150,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
@@ -7308,7 +7368,7 @@
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
@@ -7341,7 +7401,7 @@
       <c r="K26" s="132"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
@@ -7578,7 +7638,7 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
@@ -7613,7 +7673,7 @@
       </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
@@ -7646,7 +7706,7 @@
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
@@ -7679,7 +7739,7 @@
       <c r="K36" s="132"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
@@ -7706,7 +7766,7 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
@@ -7733,7 +7793,7 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
@@ -7758,7 +7818,7 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
@@ -7783,7 +7843,7 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
@@ -7808,7 +7868,7 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
@@ -7833,7 +7893,7 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
@@ -7856,7 +7916,7 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
@@ -7879,7 +7939,7 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
@@ -7902,7 +7962,7 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
@@ -7925,7 +7985,7 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
@@ -7949,6 +8009,7 @@
       <c r="L47" s="47"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="8">
     <mergeCell ref="A20:A47"/>
     <mergeCell ref="B3:K3"/>
@@ -7967,30 +8028,30 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA68E37-18F4-45D2-9A8A-CA2CAECC56FB}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="B3" s="137" t="s">
         <v>30</v>
       </c>
@@ -8004,7 +8065,7 @@
       <c r="J3" s="137"/>
       <c r="K3" s="137"/>
     </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -8069,17 +8130,23 @@
       <c r="E7" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="41"/>
+      <c r="F7" s="41">
+        <v>1250000</v>
+      </c>
       <c r="G7" s="41">
         <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="41"/>
+        <v>750000</v>
+      </c>
+      <c r="H7" s="41">
+        <v>750000</v>
+      </c>
       <c r="I7" s="41">
         <f>G7-H7</f>
         <v>0</v>
       </c>
-      <c r="J7" s="128"/>
+      <c r="J7" s="50" t="s">
+        <v>25</v>
+      </c>
       <c r="K7" s="129"/>
       <c r="L7" s="46"/>
       <c r="N7" s="50" t="s">
@@ -8113,7 +8180,9 @@
         <f t="shared" ref="I8:I18" si="1">G8-H8</f>
         <v>34000</v>
       </c>
-      <c r="J8" s="128"/>
+      <c r="J8" s="50" t="s">
+        <v>25</v>
+      </c>
       <c r="K8" s="130"/>
       <c r="L8" s="46"/>
       <c r="N8" s="48" t="s">
@@ -8160,17 +8229,23 @@
       <c r="E10" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="F10" s="44"/>
+      <c r="F10" s="44">
+        <v>1000000</v>
+      </c>
       <c r="G10" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="44"/>
+        <v>600000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>600000</v>
+      </c>
       <c r="I10" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="128"/>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
       <c r="N10" s="146" t="s">
@@ -8179,7 +8254,7 @@
       <c r="O10" s="146"/>
       <c r="P10" s="147">
         <f>SUM(F7:F1006)</f>
-        <v>340000</v>
+        <v>32460000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8188,9 +8263,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="C11" s="42" t="s">
-        <v>112</v>
-      </c>
+      <c r="C11" s="42"/>
       <c r="D11" s="43"/>
       <c r="E11" s="60" t="s">
         <v>76</v>
@@ -8244,7 +8317,7 @@
       <c r="O12" s="148"/>
       <c r="P12" s="147">
         <f>SUM(G7:G1006)</f>
-        <v>204000</v>
+        <v>17157000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8307,7 +8380,7 @@
       <c r="O14" s="148"/>
       <c r="P14" s="147"/>
     </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="144"/>
       <c r="B15" s="38">
         <f>B14+1</f>
@@ -8339,7 +8412,7 @@
       <c r="O15" s="149"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
-        <v>170000</v>
+        <v>16778500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8392,7 +8465,7 @@
       <c r="K17" s="130"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="144"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
@@ -8426,7 +8499,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="145"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
@@ -8456,25 +8529,27 @@
       <c r="B20" s="38">
         <v>1</v>
       </c>
-      <c r="C20" s="73" t="s">
+      <c r="C20" s="150" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74" t="s">
+      <c r="D20" s="151"/>
+      <c r="E20" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75">
+      <c r="F20" s="152"/>
+      <c r="G20" s="152">
         <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75">
+      <c r="H20" s="152"/>
+      <c r="I20" s="152">
         <f t="shared" ref="I20:I47" si="4">G20-H20</f>
         <v>0</v>
       </c>
-      <c r="J20" s="49"/>
-      <c r="K20" s="132"/>
+      <c r="J20" s="154"/>
+      <c r="K20" s="132" t="s">
+        <v>139</v>
+      </c>
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8490,17 +8565,23 @@
       <c r="E21" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="79"/>
+      <c r="F21" s="79">
+        <v>2040000</v>
+      </c>
       <c r="G21" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="79"/>
+        <v>1020000</v>
+      </c>
+      <c r="H21" s="79">
+        <v>1020000</v>
+      </c>
       <c r="I21" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J21" s="128"/>
+      <c r="J21" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K21" s="132"/>
       <c r="L21" s="80"/>
     </row>
@@ -8517,18 +8598,26 @@
       <c r="E22" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="75"/>
+      <c r="F22" s="75">
+        <v>1010000</v>
+      </c>
       <c r="G22" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="79"/>
+        <v>606000</v>
+      </c>
+      <c r="H22" s="79">
+        <v>600000</v>
+      </c>
       <c r="I22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="49"/>
-      <c r="K22" s="132"/>
+        <v>6000</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" s="132" t="s">
+        <v>140</v>
+      </c>
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8537,25 +8626,27 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="C23" s="73" t="s">
+      <c r="C23" s="150" t="s">
         <v>126</v>
       </c>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81" t="s">
+      <c r="D23" s="153"/>
+      <c r="E23" s="153" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="49"/>
-      <c r="K23" s="132"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="152">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="152"/>
+      <c r="I23" s="152">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="154"/>
+      <c r="K23" s="132" t="s">
+        <v>139</v>
+      </c>
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8571,17 +8662,23 @@
       <c r="E24" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="F24" s="75"/>
+      <c r="F24" s="75">
+        <v>1450000</v>
+      </c>
       <c r="G24" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="79"/>
+        <v>870000</v>
+      </c>
+      <c r="H24" s="79">
+        <v>870000</v>
+      </c>
       <c r="I24" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J24" s="49"/>
+      <c r="J24" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K24" s="132"/>
       <c r="L24" s="82"/>
     </row>
@@ -8598,21 +8695,27 @@
       <c r="E25" s="76" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="75"/>
+      <c r="F25" s="75">
+        <v>2230000</v>
+      </c>
       <c r="G25" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="79"/>
+        <v>1115000</v>
+      </c>
+      <c r="H25" s="79">
+        <v>1130000</v>
+      </c>
       <c r="I25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="49"/>
+        <v>-15000</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="142"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
@@ -8625,21 +8728,27 @@
       <c r="E26" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="75"/>
+      <c r="F26" s="75">
+        <v>3403000</v>
+      </c>
       <c r="G26" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="75"/>
+        <v>1701500</v>
+      </c>
+      <c r="H26" s="75">
+        <v>1701500</v>
+      </c>
       <c r="I26" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="49"/>
+      <c r="J26" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K26" s="132"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="142"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
@@ -8652,17 +8761,23 @@
       <c r="E27" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="79"/>
+      <c r="F27" s="79">
+        <v>1872000</v>
+      </c>
       <c r="G27" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="75"/>
+        <v>936000</v>
+      </c>
+      <c r="H27" s="75">
+        <v>936000</v>
+      </c>
       <c r="I27" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="49"/>
+      <c r="J27" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K27" s="132"/>
       <c r="L27" s="76"/>
     </row>
@@ -8679,17 +8794,23 @@
       <c r="E28" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="79"/>
+      <c r="F28" s="79">
+        <v>1765000</v>
+      </c>
       <c r="G28" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="79"/>
+        <v>882500</v>
+      </c>
+      <c r="H28" s="79">
+        <v>882000</v>
+      </c>
       <c r="I28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="49"/>
+        <v>500</v>
+      </c>
+      <c r="J28" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K28" s="132"/>
       <c r="L28" s="76"/>
     </row>
@@ -8706,17 +8827,23 @@
       <c r="E29" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="118"/>
+      <c r="F29" s="118">
+        <v>2380000</v>
+      </c>
       <c r="G29" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="118"/>
+        <v>1190000</v>
+      </c>
+      <c r="H29" s="118">
+        <v>1190000</v>
+      </c>
       <c r="I29" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J29" s="49"/>
+      <c r="J29" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K29" s="132"/>
       <c r="L29" s="93"/>
     </row>
@@ -8733,17 +8860,23 @@
       <c r="E30" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="89"/>
+      <c r="F30" s="89">
+        <v>1470000</v>
+      </c>
       <c r="G30" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="119"/>
+        <v>882000</v>
+      </c>
+      <c r="H30" s="119">
+        <v>882000</v>
+      </c>
       <c r="I30" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="49"/>
+      <c r="J30" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K30" s="132"/>
       <c r="L30" s="80"/>
     </row>
@@ -8760,17 +8893,23 @@
       <c r="E31" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="F31" s="89"/>
+      <c r="F31" s="89">
+        <v>2180000</v>
+      </c>
       <c r="G31" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="89"/>
+        <v>1090000</v>
+      </c>
+      <c r="H31" s="89">
+        <v>1090000</v>
+      </c>
       <c r="I31" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J31" s="49"/>
+      <c r="J31" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K31" s="132"/>
       <c r="L31" s="93"/>
     </row>
@@ -8787,17 +8926,23 @@
       <c r="E32" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="F32" s="75"/>
+      <c r="F32" s="75">
+        <v>840000</v>
+      </c>
       <c r="G32" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="75"/>
+        <v>504000</v>
+      </c>
+      <c r="H32" s="75">
+        <v>504000</v>
+      </c>
       <c r="I32" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J32" s="49"/>
+      <c r="J32" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K32" s="132"/>
       <c r="L32" s="93"/>
     </row>
@@ -8814,21 +8959,29 @@
       <c r="E33" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="F33" s="90"/>
+      <c r="F33" s="90">
+        <v>3550000</v>
+      </c>
       <c r="G33" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="89"/>
+        <v>1775000</v>
+      </c>
+      <c r="H33" s="89">
+        <v>1561000</v>
+      </c>
       <c r="I33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="49"/>
-      <c r="K33" s="89"/>
+        <v>214000</v>
+      </c>
+      <c r="J33" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K33" s="89" t="s">
+        <v>141</v>
+      </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="142"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
@@ -8841,21 +8994,29 @@
       <c r="E34" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="79"/>
+      <c r="F34" s="79">
+        <v>940000</v>
+      </c>
       <c r="G34" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="79"/>
+        <v>564000</v>
+      </c>
+      <c r="H34" s="79">
+        <v>425000</v>
+      </c>
       <c r="I34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="49"/>
-      <c r="K34" s="132"/>
+        <v>139000</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K34" s="132" t="s">
+        <v>142</v>
+      </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="142"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
@@ -8868,21 +9029,27 @@
       <c r="E35" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="F35" s="118"/>
+      <c r="F35" s="118">
+        <v>1870000</v>
+      </c>
       <c r="G35" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="118"/>
+        <v>935000</v>
+      </c>
+      <c r="H35" s="118">
+        <v>935000</v>
+      </c>
       <c r="I35" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J35" s="49"/>
+      <c r="J35" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="142"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
@@ -8895,48 +9062,52 @@
       <c r="E36" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="F36" s="118"/>
+      <c r="F36" s="118">
+        <v>1900000</v>
+      </c>
       <c r="G36" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="118"/>
+        <v>950000</v>
+      </c>
+      <c r="H36" s="118">
+        <v>950000</v>
+      </c>
       <c r="I36" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J36" s="49"/>
+      <c r="J36" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K36" s="132"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="142"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="C37" s="99" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" s="43"/>
-      <c r="E37" s="86" t="s">
+      <c r="C37" s="155"/>
+      <c r="D37" s="156"/>
+      <c r="E37" s="157" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="90"/>
-      <c r="G37" s="75">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="89"/>
-      <c r="I37" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="83"/>
+      <c r="F37" s="158"/>
+      <c r="G37" s="152">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="159"/>
+      <c r="I37" s="152">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="160"/>
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="142"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
@@ -8949,21 +9120,29 @@
       <c r="E38" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="F38" s="90"/>
+      <c r="F38" s="90">
+        <v>970000</v>
+      </c>
       <c r="G38" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="89"/>
+        <v>582000</v>
+      </c>
+      <c r="H38" s="89">
+        <v>582000</v>
+      </c>
       <c r="I38" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J38" s="83"/>
-      <c r="K38" s="98"/>
+      <c r="J38" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K38" s="98" t="s">
+        <v>143</v>
+      </c>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="142"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
@@ -8988,7 +9167,7 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="142"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
@@ -9013,7 +9192,7 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="142"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
@@ -9038,7 +9217,7 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="142"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
@@ -9063,7 +9242,7 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="142"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
@@ -9086,7 +9265,7 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="142"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
@@ -9109,7 +9288,7 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="142"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
@@ -9132,7 +9311,7 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="142"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
@@ -9155,7 +9334,7 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="142"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>

--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888DB4C9-4488-42C1-884F-381DFF7FB81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FD4655-5DE0-40E8-8D28-F2A27BFD1D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="579" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05328CA-F2BC-4DAB-964E-2AA90F4D9141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18819EFA-CBA9-464C-9D0E-1EA77DF95DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10-01" sheetId="14" state="hidden" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="03-02" sheetId="39" r:id="rId4"/>
     <sheet name="04-02" sheetId="40" r:id="rId5"/>
     <sheet name="05-02" sheetId="41" r:id="rId6"/>
+    <sheet name="06-02" sheetId="42" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="149">
   <si>
     <t>STT</t>
   </si>
@@ -471,13 +472,28 @@
   </si>
   <si>
     <t>doanh thu 4/2 cộng 5/2</t>
+  </si>
+  <si>
+    <t>DOANH THU 06/02/2026</t>
+  </si>
+  <si>
+    <t>nghỉ nhà có việc</t>
+  </si>
+  <si>
+    <t>nghỉ luôn</t>
+  </si>
+  <si>
+    <t>1150, bỏ cuốc 150 và 50 mới nhất vì đã cộng vô doanh thu hôm ngày 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50k đèn xi nhan </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -692,6 +708,12 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -955,7 +977,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1331,6 +1353,39 @@
     <xf numFmtId="0" fontId="29" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1370,37 +1425,25 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="27" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="29" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1969,32 +2012,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="148"/>
+      <c r="J2" s="148"/>
+      <c r="K2" s="148"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="138" t="s">
+      <c r="B3" s="149" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="150"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="21"/>
@@ -2652,20 +2695,20 @@
       <c r="F26" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="140" t="s">
+      <c r="H26" s="151" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="140"/>
+      <c r="I26" s="151"/>
       <c r="J26" s="5">
         <f>SUM(H7:H1001)</f>
         <v>28869000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="140" t="s">
+      <c r="H27" s="151" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="140"/>
+      <c r="I27" s="151"/>
       <c r="J27" s="5">
         <f>SUM(I7:I1001)</f>
         <v>17311000</v>
@@ -2803,18 +2846,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="148"/>
+      <c r="K3" s="148"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -2868,7 +2911,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="143" t="s">
+      <c r="A7" s="154" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -2905,7 +2948,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="144"/>
+      <c r="A8" s="155"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -2941,7 +2984,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
+      <c r="A9" s="155"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -2973,7 +3016,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="144"/>
+      <c r="A10" s="155"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -3004,17 +3047,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="146" t="s">
+      <c r="N10" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="146"/>
-      <c r="P10" s="147">
+      <c r="O10" s="157"/>
+      <c r="P10" s="158">
         <f>SUM(F7:F1006)</f>
         <v>16675000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="144"/>
+      <c r="A11" s="155"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -3045,12 +3088,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="146"/>
-      <c r="P11" s="147"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="158"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="144"/>
+      <c r="A12" s="155"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -3075,17 +3118,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="148" t="s">
+      <c r="N12" s="159" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="148"/>
-      <c r="P12" s="147">
+      <c r="O12" s="159"/>
+      <c r="P12" s="158">
         <f>SUM(G7:G1006)</f>
         <v>9346000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144"/>
+      <c r="A13" s="155"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -3110,12 +3153,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="148"/>
-      <c r="O13" s="148"/>
-      <c r="P13" s="147"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="159"/>
+      <c r="P13" s="158"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="144"/>
+      <c r="A14" s="155"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -3140,12 +3183,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="148"/>
-      <c r="O14" s="148"/>
-      <c r="P14" s="147"/>
+      <c r="N14" s="159"/>
+      <c r="O14" s="159"/>
+      <c r="P14" s="158"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="144"/>
+      <c r="A15" s="155"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -3170,17 +3213,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="149" t="s">
+      <c r="N15" s="160" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="149"/>
+      <c r="O15" s="160"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>9285000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="144"/>
+      <c r="A16" s="155"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -3207,7 +3250,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="144"/>
+      <c r="A17" s="155"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -3234,7 +3277,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="144"/>
+      <c r="A18" s="155"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3270,7 +3313,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="145"/>
+      <c r="A19" s="156"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -3293,7 +3336,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="141" t="s">
+      <c r="A20" s="152" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -3325,7 +3368,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="142"/>
+      <c r="A21" s="153"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -3358,7 +3401,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="142"/>
+      <c r="A22" s="153"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="6">B21+1</f>
         <v>3</v>
@@ -3389,7 +3432,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="142"/>
+      <c r="A23" s="153"/>
       <c r="B23" s="38">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -3412,7 +3455,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="142"/>
+      <c r="A24" s="153"/>
       <c r="B24" s="38">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -3443,7 +3486,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="142"/>
+      <c r="A25" s="153"/>
       <c r="B25" s="38">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -3476,7 +3519,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="142"/>
+      <c r="A26" s="153"/>
       <c r="B26" s="38">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -3507,7 +3550,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="142"/>
+      <c r="A27" s="153"/>
       <c r="B27" s="38">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -3540,7 +3583,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="142"/>
+      <c r="A28" s="153"/>
       <c r="B28" s="38">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -3573,7 +3616,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="142"/>
+      <c r="A29" s="153"/>
       <c r="B29" s="38">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -3596,7 +3639,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="142"/>
+      <c r="A30" s="153"/>
       <c r="B30" s="38">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -3627,7 +3670,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="142"/>
+      <c r="A31" s="153"/>
       <c r="B31" s="38">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3660,7 +3703,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="142"/>
+      <c r="A32" s="153"/>
       <c r="B32" s="38">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -3693,7 +3736,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="142"/>
+      <c r="A33" s="153"/>
       <c r="B33" s="38">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -3720,7 +3763,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="142"/>
+      <c r="A34" s="153"/>
       <c r="B34" s="38">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -3753,7 +3796,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="142"/>
+      <c r="A35" s="153"/>
       <c r="B35" s="38">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -3784,7 +3827,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="142"/>
+      <c r="A36" s="153"/>
       <c r="B36" s="38">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -3817,7 +3860,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="142"/>
+      <c r="A37" s="153"/>
       <c r="B37" s="38">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -3840,7 +3883,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="142"/>
+      <c r="A38" s="153"/>
       <c r="B38" s="38">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -3863,7 +3906,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="142"/>
+      <c r="A39" s="153"/>
       <c r="B39" s="38">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -3886,7 +3929,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="142"/>
+      <c r="A40" s="153"/>
       <c r="B40" s="38">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -3909,7 +3952,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="142"/>
+      <c r="A41" s="153"/>
       <c r="B41" s="38">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -3932,7 +3975,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="142"/>
+      <c r="A42" s="153"/>
       <c r="B42" s="38">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -3955,7 +3998,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="142"/>
+      <c r="A43" s="153"/>
       <c r="B43" s="38">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -3978,7 +4021,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="142"/>
+      <c r="A44" s="153"/>
       <c r="B44" s="38">
         <f t="shared" si="6"/>
         <v>25</v>
@@ -4001,7 +4044,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="142"/>
+      <c r="A45" s="153"/>
       <c r="B45" s="38">
         <f t="shared" si="6"/>
         <v>26</v>
@@ -4024,7 +4067,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="142"/>
+      <c r="A46" s="153"/>
       <c r="B46" s="38">
         <f t="shared" si="6"/>
         <v>27</v>
@@ -4047,7 +4090,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="142"/>
+      <c r="A47" s="153"/>
       <c r="B47" s="38">
         <f t="shared" si="6"/>
         <v>28</v>
@@ -4113,18 +4156,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="148"/>
+      <c r="K3" s="148"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -4178,7 +4221,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="143" t="s">
+      <c r="A7" s="154" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -4215,7 +4258,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="144"/>
+      <c r="A8" s="155"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -4251,7 +4294,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
+      <c r="A9" s="155"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -4284,7 +4327,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="144"/>
+      <c r="A10" s="155"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -4315,17 +4358,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="146" t="s">
+      <c r="N10" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="146"/>
-      <c r="P10" s="147">
+      <c r="O10" s="157"/>
+      <c r="P10" s="158">
         <f>SUM(F7:F1006)</f>
         <v>30573000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="144"/>
+      <c r="A11" s="155"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -4356,12 +4399,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="146"/>
-      <c r="P11" s="147"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="158"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="144"/>
+      <c r="A12" s="155"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -4386,17 +4429,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="148" t="s">
+      <c r="N12" s="159" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="148"/>
-      <c r="P12" s="147">
+      <c r="O12" s="159"/>
+      <c r="P12" s="158">
         <f>SUM(G7:G1006)</f>
         <v>16022500</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144"/>
+      <c r="A13" s="155"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -4421,12 +4464,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="148"/>
-      <c r="O13" s="148"/>
-      <c r="P13" s="147"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="159"/>
+      <c r="P13" s="158"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="144"/>
+      <c r="A14" s="155"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -4451,12 +4494,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="148"/>
-      <c r="O14" s="148"/>
-      <c r="P14" s="147"/>
+      <c r="N14" s="159"/>
+      <c r="O14" s="159"/>
+      <c r="P14" s="158"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="144"/>
+      <c r="A15" s="155"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -4481,17 +4524,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="149" t="s">
+      <c r="N15" s="160" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="149"/>
+      <c r="O15" s="160"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>15420500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="144"/>
+      <c r="A16" s="155"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -4518,7 +4561,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="144"/>
+      <c r="A17" s="155"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -4545,7 +4588,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="144"/>
+      <c r="A18" s="155"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -4581,7 +4624,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="145"/>
+      <c r="A19" s="156"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -4604,7 +4647,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="141" t="s">
+      <c r="A20" s="152" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -4638,7 +4681,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="142"/>
+      <c r="A21" s="153"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -4671,7 +4714,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="142"/>
+      <c r="A22" s="153"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -4704,7 +4747,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="142"/>
+      <c r="A23" s="153"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -4727,7 +4770,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="142"/>
+      <c r="A24" s="153"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -4760,7 +4803,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="142"/>
+      <c r="A25" s="153"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -4793,7 +4836,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="142"/>
+      <c r="A26" s="153"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -4826,7 +4869,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="142"/>
+      <c r="A27" s="153"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -4859,7 +4902,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="142"/>
+      <c r="A28" s="153"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -4892,7 +4935,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="142"/>
+      <c r="A29" s="153"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -4915,7 +4958,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="142"/>
+      <c r="A30" s="153"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -4948,7 +4991,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="142"/>
+      <c r="A31" s="153"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -4981,7 +5024,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="142"/>
+      <c r="A32" s="153"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -5014,7 +5057,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="142"/>
+      <c r="A33" s="153"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -5039,7 +5082,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="142"/>
+      <c r="A34" s="153"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -5072,7 +5115,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="142"/>
+      <c r="A35" s="153"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -5105,7 +5148,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="142"/>
+      <c r="A36" s="153"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -5138,7 +5181,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="142"/>
+      <c r="A37" s="153"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -5161,7 +5204,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="142"/>
+      <c r="A38" s="153"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -5184,7 +5227,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="142"/>
+      <c r="A39" s="153"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -5207,7 +5250,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="142"/>
+      <c r="A40" s="153"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -5230,7 +5273,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="142"/>
+      <c r="A41" s="153"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -5253,7 +5296,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="142"/>
+      <c r="A42" s="153"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -5276,7 +5319,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="142"/>
+      <c r="A43" s="153"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -5299,7 +5342,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="142"/>
+      <c r="A44" s="153"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -5322,7 +5365,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="142"/>
+      <c r="A45" s="153"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -5345,7 +5388,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="142"/>
+      <c r="A46" s="153"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -5368,7 +5411,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="142"/>
+      <c r="A47" s="153"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -5434,18 +5477,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="148"/>
+      <c r="K3" s="148"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -5499,7 +5542,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="143" t="s">
+      <c r="A7" s="154" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -5536,7 +5579,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="144"/>
+      <c r="A8" s="155"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -5572,7 +5615,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
+      <c r="A9" s="155"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -5601,7 +5644,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="144"/>
+      <c r="A10" s="155"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -5632,17 +5675,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="146" t="s">
+      <c r="N10" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="146"/>
-      <c r="P10" s="147">
+      <c r="O10" s="157"/>
+      <c r="P10" s="158">
         <f>SUM(F7:F1006)</f>
         <v>3545000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="144"/>
+      <c r="A11" s="155"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -5673,12 +5716,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="146"/>
-      <c r="P11" s="147"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="158"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="144"/>
+      <c r="A12" s="155"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -5703,17 +5746,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="148" t="s">
+      <c r="N12" s="159" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="148"/>
-      <c r="P12" s="147">
+      <c r="O12" s="159"/>
+      <c r="P12" s="158">
         <f>SUM(G7:G1006)</f>
         <v>2127000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144"/>
+      <c r="A13" s="155"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -5738,12 +5781,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="148"/>
-      <c r="O13" s="148"/>
-      <c r="P13" s="147"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="159"/>
+      <c r="P13" s="158"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="144"/>
+      <c r="A14" s="155"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -5768,12 +5811,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="148"/>
-      <c r="O14" s="148"/>
-      <c r="P14" s="147"/>
+      <c r="N14" s="159"/>
+      <c r="O14" s="159"/>
+      <c r="P14" s="158"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="144"/>
+      <c r="A15" s="155"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -5798,17 +5841,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="149" t="s">
+      <c r="N15" s="160" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="149"/>
+      <c r="O15" s="160"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>2010000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="144"/>
+      <c r="A16" s="155"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -5835,7 +5878,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="144"/>
+      <c r="A17" s="155"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -5862,7 +5905,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="144"/>
+      <c r="A18" s="155"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -5898,7 +5941,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="145"/>
+      <c r="A19" s="156"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -5921,7 +5964,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="141" t="s">
+      <c r="A20" s="152" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -5951,7 +5994,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="142"/>
+      <c r="A21" s="153"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -5980,7 +6023,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="142"/>
+      <c r="A22" s="153"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -6009,7 +6052,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="142"/>
+      <c r="A23" s="153"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -6034,7 +6077,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="142"/>
+      <c r="A24" s="153"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -6063,7 +6106,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="142"/>
+      <c r="A25" s="153"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -6092,7 +6135,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="142"/>
+      <c r="A26" s="153"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -6121,7 +6164,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="142"/>
+      <c r="A27" s="153"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -6150,7 +6193,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="142"/>
+      <c r="A28" s="153"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -6179,7 +6222,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="142"/>
+      <c r="A29" s="153"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -6204,7 +6247,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="142"/>
+      <c r="A30" s="153"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -6233,7 +6276,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="142"/>
+      <c r="A31" s="153"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -6262,7 +6305,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="142"/>
+      <c r="A32" s="153"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -6291,7 +6334,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="142"/>
+      <c r="A33" s="153"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -6318,7 +6361,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="142"/>
+      <c r="A34" s="153"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -6347,7 +6390,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="142"/>
+      <c r="A35" s="153"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -6376,7 +6419,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="142"/>
+      <c r="A36" s="153"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -6405,7 +6448,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="142"/>
+      <c r="A37" s="153"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -6428,7 +6471,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="142"/>
+      <c r="A38" s="153"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -6451,7 +6494,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="142"/>
+      <c r="A39" s="153"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -6474,7 +6517,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="142"/>
+      <c r="A40" s="153"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -6497,7 +6540,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="142"/>
+      <c r="A41" s="153"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -6520,7 +6563,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="142"/>
+      <c r="A42" s="153"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -6543,7 +6586,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="142"/>
+      <c r="A43" s="153"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -6566,7 +6609,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="142"/>
+      <c r="A44" s="153"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -6589,7 +6632,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="142"/>
+      <c r="A45" s="153"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -6612,7 +6655,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="142"/>
+      <c r="A46" s="153"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -6635,7 +6678,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="142"/>
+      <c r="A47" s="153"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -6701,18 +6744,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="148"/>
+      <c r="K3" s="148"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -6766,7 +6809,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="143" t="s">
+      <c r="A7" s="154" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -6803,7 +6846,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="144"/>
+      <c r="A8" s="155"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -6831,7 +6874,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
+      <c r="A9" s="155"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -6860,7 +6903,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="144"/>
+      <c r="A10" s="155"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -6891,17 +6934,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="146" t="s">
+      <c r="N10" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="146"/>
-      <c r="P10" s="147">
+      <c r="O10" s="157"/>
+      <c r="P10" s="158">
         <f>SUM(F7:F1006)</f>
         <v>40751000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="144"/>
+      <c r="A11" s="155"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -6932,12 +6975,12 @@
       </c>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="146"/>
-      <c r="P11" s="147"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="158"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="144"/>
+      <c r="A12" s="155"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -6962,17 +7005,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="148" t="s">
+      <c r="N12" s="159" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="148"/>
-      <c r="P12" s="147">
+      <c r="O12" s="159"/>
+      <c r="P12" s="158">
         <f>SUM(G7:G1006)</f>
         <v>20907500</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144"/>
+      <c r="A13" s="155"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -6997,12 +7040,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="148"/>
-      <c r="O13" s="148"/>
-      <c r="P13" s="147"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="159"/>
+      <c r="P13" s="158"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="144"/>
+      <c r="A14" s="155"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7027,12 +7070,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="148"/>
-      <c r="O14" s="148"/>
-      <c r="P14" s="147"/>
+      <c r="N14" s="159"/>
+      <c r="O14" s="159"/>
+      <c r="P14" s="158"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="144"/>
+      <c r="A15" s="155"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -7057,17 +7100,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="149" t="s">
+      <c r="N15" s="160" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="149"/>
+      <c r="O15" s="160"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>21280000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="144"/>
+      <c r="A16" s="155"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -7092,7 +7135,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="144"/>
+      <c r="A17" s="155"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -7117,7 +7160,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="144"/>
+      <c r="A18" s="155"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -7151,7 +7194,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="145"/>
+      <c r="A19" s="156"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -7174,7 +7217,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="141" t="s">
+      <c r="A20" s="152" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -7208,7 +7251,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="142"/>
+      <c r="A21" s="153"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -7237,7 +7280,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="142"/>
+      <c r="A22" s="153"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -7270,7 +7313,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="142"/>
+      <c r="A23" s="153"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -7303,7 +7346,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="142"/>
+      <c r="A24" s="153"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -7336,7 +7379,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="142"/>
+      <c r="A25" s="153"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -7369,7 +7412,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="142"/>
+      <c r="A26" s="153"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -7402,7 +7445,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="142"/>
+      <c r="A27" s="153"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -7435,7 +7478,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="142"/>
+      <c r="A28" s="153"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -7470,7 +7513,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="142"/>
+      <c r="A29" s="153"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -7505,7 +7548,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="142"/>
+      <c r="A30" s="153"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -7538,7 +7581,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="142"/>
+      <c r="A31" s="153"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -7571,7 +7614,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="142"/>
+      <c r="A32" s="153"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -7604,7 +7647,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="142"/>
+      <c r="A33" s="153"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -7639,7 +7682,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="142"/>
+      <c r="A34" s="153"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -7674,7 +7717,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="142"/>
+      <c r="A35" s="153"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -7707,7 +7750,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="142"/>
+      <c r="A36" s="153"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -7740,7 +7783,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="142"/>
+      <c r="A37" s="153"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -7767,7 +7810,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="142"/>
+      <c r="A38" s="153"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -7794,7 +7837,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="142"/>
+      <c r="A39" s="153"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -7819,7 +7862,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="142"/>
+      <c r="A40" s="153"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -7844,7 +7887,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="142"/>
+      <c r="A41" s="153"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -7869,7 +7912,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="142"/>
+      <c r="A42" s="153"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -7894,7 +7937,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="142"/>
+      <c r="A43" s="153"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -7917,7 +7960,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="142"/>
+      <c r="A44" s="153"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -7940,7 +7983,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="142"/>
+      <c r="A45" s="153"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -7963,7 +8006,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="142"/>
+      <c r="A46" s="153"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -7986,7 +8029,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="142"/>
+      <c r="A47" s="153"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -8052,18 +8095,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="148"/>
+      <c r="K3" s="148"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -8117,7 +8160,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="143" t="s">
+      <c r="A7" s="154" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -8154,7 +8197,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="144"/>
+      <c r="A8" s="155"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -8190,7 +8233,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
+      <c r="A9" s="155"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -8217,7 +8260,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="144"/>
+      <c r="A10" s="155"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -8248,17 +8291,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="146" t="s">
+      <c r="N10" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="146"/>
-      <c r="P10" s="147">
+      <c r="O10" s="157"/>
+      <c r="P10" s="158">
         <f>SUM(F7:F1006)</f>
         <v>32460000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="144"/>
+      <c r="A11" s="155"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -8281,12 +8324,12 @@
       <c r="J11" s="128"/>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="146"/>
-      <c r="P11" s="147"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="158"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="144"/>
+      <c r="A12" s="155"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -8311,17 +8354,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="148" t="s">
+      <c r="N12" s="159" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="148"/>
-      <c r="P12" s="147">
+      <c r="O12" s="159"/>
+      <c r="P12" s="158">
         <f>SUM(G7:G1006)</f>
         <v>17157000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144"/>
+      <c r="A13" s="155"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -8346,12 +8389,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="148"/>
-      <c r="O13" s="148"/>
-      <c r="P13" s="147"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="159"/>
+      <c r="P13" s="158"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="144"/>
+      <c r="A14" s="155"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -8376,12 +8419,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="148"/>
-      <c r="O14" s="148"/>
-      <c r="P14" s="147"/>
+      <c r="N14" s="159"/>
+      <c r="O14" s="159"/>
+      <c r="P14" s="158"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="144"/>
+      <c r="A15" s="155"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -8406,17 +8449,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="149" t="s">
+      <c r="N15" s="160" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="149"/>
+      <c r="O15" s="160"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>16778500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="144"/>
+      <c r="A16" s="155"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -8441,7 +8484,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="144"/>
+      <c r="A17" s="155"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -8466,7 +8509,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="144"/>
+      <c r="A18" s="155"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -8500,7 +8543,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="145"/>
+      <c r="A19" s="156"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -8523,37 +8566,37 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="141" t="s">
+      <c r="A20" s="152" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
         <v>1</v>
       </c>
-      <c r="C20" s="150" t="s">
+      <c r="C20" s="137" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="151"/>
-      <c r="E20" s="151" t="s">
+      <c r="D20" s="138"/>
+      <c r="E20" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="152"/>
-      <c r="G20" s="152">
+      <c r="F20" s="139"/>
+      <c r="G20" s="139">
         <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="152"/>
-      <c r="I20" s="152">
+      <c r="H20" s="139"/>
+      <c r="I20" s="139">
         <f t="shared" ref="I20:I47" si="4">G20-H20</f>
         <v>0</v>
       </c>
-      <c r="J20" s="154"/>
+      <c r="J20" s="141"/>
       <c r="K20" s="132" t="s">
         <v>139</v>
       </c>
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="142"/>
+      <c r="A21" s="153"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -8586,7 +8629,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="142"/>
+      <c r="A22" s="153"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -8621,36 +8664,36 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="142"/>
+      <c r="A23" s="153"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="C23" s="150" t="s">
+      <c r="C23" s="137" t="s">
         <v>126</v>
       </c>
-      <c r="D23" s="153"/>
-      <c r="E23" s="153" t="s">
+      <c r="D23" s="140"/>
+      <c r="E23" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="152"/>
-      <c r="G23" s="152">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="152"/>
-      <c r="I23" s="152">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="154"/>
+      <c r="F23" s="139"/>
+      <c r="G23" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="139"/>
+      <c r="I23" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="141"/>
       <c r="K23" s="132" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="142"/>
+      <c r="A24" s="153"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -8683,7 +8726,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="142"/>
+      <c r="A25" s="153"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -8716,7 +8759,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="142"/>
+      <c r="A26" s="153"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -8749,7 +8792,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="142"/>
+      <c r="A27" s="153"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -8782,7 +8825,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="142"/>
+      <c r="A28" s="153"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -8815,7 +8858,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="142"/>
+      <c r="A29" s="153"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -8848,7 +8891,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="142"/>
+      <c r="A30" s="153"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -8881,7 +8924,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="142"/>
+      <c r="A31" s="153"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -8914,7 +8957,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="142"/>
+      <c r="A32" s="153"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -8947,7 +8990,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="142"/>
+      <c r="A33" s="153"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -8982,7 +9025,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="142"/>
+      <c r="A34" s="153"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -9017,7 +9060,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="142"/>
+      <c r="A35" s="153"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -9050,7 +9093,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="142"/>
+      <c r="A36" s="153"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -9083,32 +9126,32 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="142"/>
+      <c r="A37" s="153"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="C37" s="155"/>
-      <c r="D37" s="156"/>
-      <c r="E37" s="157" t="s">
+      <c r="C37" s="142"/>
+      <c r="D37" s="143"/>
+      <c r="E37" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="158"/>
-      <c r="G37" s="152">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="159"/>
-      <c r="I37" s="152">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="160"/>
+      <c r="F37" s="145"/>
+      <c r="G37" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="146"/>
+      <c r="I37" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="147"/>
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="142"/>
+      <c r="A38" s="153"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -9143,7 +9186,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="142"/>
+      <c r="A39" s="153"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -9168,7 +9211,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="142"/>
+      <c r="A40" s="153"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -9193,7 +9236,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="142"/>
+      <c r="A41" s="153"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -9218,7 +9261,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="142"/>
+      <c r="A42" s="153"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -9243,7 +9286,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="142"/>
+      <c r="A43" s="153"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -9266,7 +9309,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="142"/>
+      <c r="A44" s="153"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -9289,7 +9332,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="142"/>
+      <c r="A45" s="153"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -9312,7 +9355,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="142"/>
+      <c r="A46" s="153"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -9335,7 +9378,1349 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="142"/>
+      <c r="A47" s="153"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DDB050C-EFA5-4BA1-89FF-2BF72F913523}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="148" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="148"/>
+      <c r="K3" s="148"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="154" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="41">
+        <v>1800000</v>
+      </c>
+      <c r="G7" s="41">
+        <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
+        <v>1080000</v>
+      </c>
+      <c r="H7" s="41">
+        <v>900000</v>
+      </c>
+      <c r="I7" s="41">
+        <f>G7-H7</f>
+        <v>180000</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="129"/>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="155"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41">
+        <v>770000</v>
+      </c>
+      <c r="G8" s="41">
+        <f t="shared" ref="G8:G18" si="0">IF(F8="",0,IF(F8&gt;1800000,F8*O$19,F8*O$18))</f>
+        <v>462000</v>
+      </c>
+      <c r="H8" s="41">
+        <v>385000</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="1">G8-H8</f>
+        <v>77000</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="130"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="155"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="2">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="122" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="126"/>
+      <c r="I9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="127"/>
+      <c r="K9" s="167" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="155"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="44">
+        <v>1050000</v>
+      </c>
+      <c r="G10" s="41">
+        <f t="shared" si="0"/>
+        <v>630000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>630000</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="130"/>
+      <c r="L10" s="46"/>
+      <c r="N10" s="157" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="157"/>
+      <c r="P10" s="158">
+        <f>SUM(F7:F1006)</f>
+        <v>35340000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="155"/>
+      <c r="B11" s="38">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="44"/>
+      <c r="I11" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="128"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="158"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="155"/>
+      <c r="B12" s="38">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="62"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="159" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="159"/>
+      <c r="P12" s="158">
+        <f>SUM(G7:G1006)</f>
+        <v>18504400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="155"/>
+      <c r="B13" s="38">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="62"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="159"/>
+      <c r="P13" s="158"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="155"/>
+      <c r="B14" s="38">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="159"/>
+      <c r="O14" s="159"/>
+      <c r="P14" s="158"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="155"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="160" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="160"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>18210000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="155"/>
+      <c r="B16" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="155"/>
+      <c r="B17" s="38">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="155"/>
+      <c r="B18" s="38">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="156"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="152" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="128"/>
+      <c r="K20" s="132" t="s">
+        <v>139</v>
+      </c>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="153"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="79">
+        <v>2250000</v>
+      </c>
+      <c r="G21" s="75">
+        <f t="shared" si="3"/>
+        <v>1125000</v>
+      </c>
+      <c r="H21" s="79">
+        <v>1125000</v>
+      </c>
+      <c r="I21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K21" s="132"/>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="153"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75">
+        <v>1150000</v>
+      </c>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>690000</v>
+      </c>
+      <c r="H22" s="79">
+        <v>700000</v>
+      </c>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>-10000</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" s="161" t="s">
+        <v>147</v>
+      </c>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="153"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="101"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="103"/>
+      <c r="I23" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="128"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="153"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="75">
+        <v>1716000</v>
+      </c>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>858000</v>
+      </c>
+      <c r="H24" s="79">
+        <v>858000</v>
+      </c>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K24" s="132"/>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="153"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="75">
+        <v>1760000</v>
+      </c>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+      <c r="H25" s="79">
+        <v>880000</v>
+      </c>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K25" s="132"/>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="153"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="75">
+        <v>2895000</v>
+      </c>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>1447500</v>
+      </c>
+      <c r="H26" s="75">
+        <v>1447500</v>
+      </c>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26" s="132"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="153"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="87"/>
+      <c r="E27" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="79">
+        <v>2768000</v>
+      </c>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>1384000</v>
+      </c>
+      <c r="H27" s="75">
+        <v>1384000</v>
+      </c>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K27" s="132"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="153"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="79">
+        <v>1998000</v>
+      </c>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>999000</v>
+      </c>
+      <c r="H28" s="79">
+        <v>1000000</v>
+      </c>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>-1000</v>
+      </c>
+      <c r="J28" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K28" s="132"/>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="153"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="118">
+        <v>3070000</v>
+      </c>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>1535000</v>
+      </c>
+      <c r="H29" s="118">
+        <v>1535000</v>
+      </c>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K29" s="132"/>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="153"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="78"/>
+      <c r="E30" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="89">
+        <v>1250000</v>
+      </c>
+      <c r="G30" s="75">
+        <f t="shared" si="3"/>
+        <v>750000</v>
+      </c>
+      <c r="H30" s="119">
+        <v>750000</v>
+      </c>
+      <c r="I30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K30" s="132"/>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="153"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="89">
+        <v>2855000</v>
+      </c>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>1427500</v>
+      </c>
+      <c r="H31" s="89">
+        <v>1377500</v>
+      </c>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31" s="132" t="s">
+        <v>148</v>
+      </c>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="153"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="87"/>
+      <c r="E32" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="75">
+        <v>840000</v>
+      </c>
+      <c r="G32" s="75">
+        <f t="shared" si="3"/>
+        <v>504000</v>
+      </c>
+      <c r="H32" s="75">
+        <v>504000</v>
+      </c>
+      <c r="I32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K32" s="132"/>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="153"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="87"/>
+      <c r="E33" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="90">
+        <v>2194000</v>
+      </c>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>1097000</v>
+      </c>
+      <c r="H33" s="89">
+        <v>1097000</v>
+      </c>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K33" s="89"/>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="153"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="79">
+        <v>1720000</v>
+      </c>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>860000</v>
+      </c>
+      <c r="H34" s="79">
+        <v>860000</v>
+      </c>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K34" s="132"/>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="153"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="120"/>
+      <c r="E35" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="118">
+        <v>1870000</v>
+      </c>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>935000</v>
+      </c>
+      <c r="H35" s="118">
+        <v>935000</v>
+      </c>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K35" s="132"/>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="153"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="87" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="120"/>
+      <c r="E36" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="118">
+        <v>1900000</v>
+      </c>
+      <c r="G36" s="75">
+        <f t="shared" si="3"/>
+        <v>950000</v>
+      </c>
+      <c r="H36" s="118">
+        <v>950000</v>
+      </c>
+      <c r="I36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K36" s="132"/>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="153"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="162"/>
+      <c r="D37" s="163"/>
+      <c r="E37" s="164" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="165"/>
+      <c r="G37" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="166"/>
+      <c r="I37" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="83"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="153"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="43"/>
+      <c r="E38" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="90">
+        <v>1484000</v>
+      </c>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>890400</v>
+      </c>
+      <c r="H38" s="89">
+        <v>892000</v>
+      </c>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>-1600</v>
+      </c>
+      <c r="J38" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K38" s="98"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="153"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="90"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="153"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="90"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="153"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="153"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="153"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="153"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="153"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="153"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="153"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>

--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18819EFA-CBA9-464C-9D0E-1EA77DF95DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5662BB34-0092-486F-8D0E-CBDA1794A885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="579" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10-01" sheetId="14" state="hidden" r:id="rId1"/>
@@ -1386,6 +1386,27 @@
     <xf numFmtId="0" fontId="30" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1424,27 +1445,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1991,58 +1991,58 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25421AD-4B15-4CE5-B032-F166D9527995}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A2:P59"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.44140625" style="1" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="21" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" style="1" customWidth="1"/>
-    <col min="14" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="16.85546875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="19.44140625" style="1" customWidth="1"/>
+    <col min="14" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="16.88671875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="155" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="148"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
-      <c r="G2" s="148"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148"/>
-    </row>
-    <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="149" t="s">
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+    </row>
+    <row r="3" spans="2:16" ht="30.6" x14ac:dyDescent="0.25">
+      <c r="B3" s="156" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="150"/>
-      <c r="D3" s="150"/>
-      <c r="E3" s="150"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150"/>
-      <c r="K3" s="150"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="157"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="21"/>
     </row>
-    <row r="6" spans="2:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="21" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>1</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <f t="shared" ref="B8:B23" si="0">B7 +1</f>
         <v>2</v>
@@ -2156,7 +2156,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2190,7 +2190,7 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2224,7 +2224,7 @@
       <c r="L10" s="37"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10 +1</f>
         <v>5</v>
@@ -2260,7 +2260,7 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2294,7 +2294,7 @@
       <c r="L12" s="8"/>
       <c r="M12" s="9"/>
     </row>
-    <row r="13" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2330,7 +2330,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2363,7 +2363,7 @@
       <c r="L14" s="8"/>
       <c r="M14" s="9"/>
     </row>
-    <row r="15" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2397,7 +2397,7 @@
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
     </row>
-    <row r="16" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2431,7 +2431,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2465,7 +2465,7 @@
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
     </row>
-    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2501,7 +2501,7 @@
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
     </row>
-    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2534,7 +2534,7 @@
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
     </row>
-    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="B20" s="3">
         <f t="shared" si="0"/>
@@ -2567,7 +2567,7 @@
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
     </row>
-    <row r="21" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="A21" s="25"/>
       <c r="B21" s="3">
         <f t="shared" si="0"/>
@@ -2600,7 +2600,7 @@
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
     </row>
-    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2634,7 +2634,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="8"/>
     </row>
-    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2668,7 +2668,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="8"/>
     </row>
-    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -2685,7 +2685,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="8"/>
     </row>
-    <row r="26" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="22.8" x14ac:dyDescent="0.4">
       <c r="C26" s="18" t="s">
         <v>60</v>
       </c>
@@ -2695,20 +2695,20 @@
       <c r="F26" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="151" t="s">
+      <c r="H26" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="151"/>
+      <c r="I26" s="158"/>
       <c r="J26" s="5">
         <f>SUM(H7:H1001)</f>
         <v>28869000</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="151" t="s">
+    <row r="27" spans="1:13" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="H27" s="158" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="151"/>
+      <c r="I27" s="158"/>
       <c r="J27" s="5">
         <f>SUM(I7:I1001)</f>
         <v>17311000</v>
@@ -2724,17 +2724,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B44" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B45" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B46" s="12" t="s">
         <v>16</v>
       </c>
@@ -2742,67 +2742,67 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B47" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B48" s="12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B49" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B51" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B53" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B55" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B56" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
       <c r="B57" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="58" spans="2:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="31" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:2" ht="14.4" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:K2"/>
@@ -2822,44 +2822,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBEB86F-A8DD-42F9-B2B2-37DBDB0C26B6}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="148" t="s">
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+      <c r="B3" s="155" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="148"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="148"/>
-      <c r="K3" s="148"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -2911,7 +2911,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="161" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -2948,7 +2948,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="155"/>
+      <c r="A8" s="162"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -2984,7 +2984,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="155"/>
+      <c r="A9" s="162"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -3016,7 +3016,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="155"/>
+      <c r="A10" s="162"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -3047,17 +3047,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="157" t="s">
+      <c r="N10" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="157"/>
-      <c r="P10" s="158">
+      <c r="O10" s="164"/>
+      <c r="P10" s="165">
         <f>SUM(F7:F1006)</f>
         <v>16675000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="155"/>
+      <c r="A11" s="162"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -3088,12 +3088,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="158"/>
+      <c r="N11" s="164"/>
+      <c r="O11" s="164"/>
+      <c r="P11" s="165"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="155"/>
+      <c r="A12" s="162"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -3118,17 +3118,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="159" t="s">
+      <c r="N12" s="166" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="159"/>
-      <c r="P12" s="158">
+      <c r="O12" s="166"/>
+      <c r="P12" s="165">
         <f>SUM(G7:G1006)</f>
         <v>9346000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="155"/>
+      <c r="A13" s="162"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -3153,12 +3153,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="159"/>
-      <c r="O13" s="159"/>
-      <c r="P13" s="158"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="166"/>
+      <c r="P13" s="165"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="155"/>
+      <c r="A14" s="162"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -3183,12 +3183,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="159"/>
-      <c r="O14" s="159"/>
-      <c r="P14" s="158"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="155"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="166"/>
+      <c r="P14" s="165"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="162"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -3213,17 +3213,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="160" t="s">
+      <c r="N15" s="167" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="160"/>
+      <c r="O15" s="167"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>9285000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="155"/>
+      <c r="A16" s="162"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -3250,7 +3250,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="155"/>
+      <c r="A17" s="162"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -3276,8 +3276,8 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="155"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="162"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3312,8 +3312,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="156"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="163"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -3336,7 +3336,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="152" t="s">
+      <c r="A20" s="159" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -3368,7 +3368,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="153"/>
+      <c r="A21" s="160"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -3401,7 +3401,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="153"/>
+      <c r="A22" s="160"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="6">B21+1</f>
         <v>3</v>
@@ -3432,7 +3432,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="153"/>
+      <c r="A23" s="160"/>
       <c r="B23" s="38">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -3455,7 +3455,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="153"/>
+      <c r="A24" s="160"/>
       <c r="B24" s="38">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -3486,7 +3486,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="153"/>
+      <c r="A25" s="160"/>
       <c r="B25" s="38">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -3518,8 +3518,8 @@
       <c r="K25" s="84"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="153"/>
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="160"/>
       <c r="B26" s="38">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -3549,8 +3549,8 @@
       </c>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="153"/>
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="160"/>
       <c r="B27" s="38">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -3582,8 +3582,8 @@
       <c r="K27" s="85"/>
       <c r="L27" s="76"/>
     </row>
-    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="153"/>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="160"/>
       <c r="B28" s="38">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -3615,8 +3615,8 @@
       <c r="K28" s="91"/>
       <c r="L28" s="76"/>
     </row>
-    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="153"/>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="160"/>
       <c r="B29" s="38">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -3639,7 +3639,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="153"/>
+      <c r="A30" s="160"/>
       <c r="B30" s="38">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -3669,8 +3669,8 @@
       </c>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="153"/>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="160"/>
       <c r="B31" s="38">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3702,8 +3702,8 @@
       <c r="K31" s="106"/>
       <c r="L31" s="93"/>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="153"/>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="160"/>
       <c r="B32" s="38">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -3735,8 +3735,8 @@
       <c r="K32" s="106"/>
       <c r="L32" s="93"/>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="153"/>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="160"/>
       <c r="B33" s="38">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -3762,8 +3762,8 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="153"/>
+    <row r="34" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A34" s="160"/>
       <c r="B34" s="38">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -3795,8 +3795,8 @@
       <c r="K34" s="92"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="153"/>
+    <row r="35" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A35" s="160"/>
       <c r="B35" s="38">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -3826,8 +3826,8 @@
       </c>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="153"/>
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="160"/>
       <c r="B36" s="38">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -3859,8 +3859,8 @@
       <c r="K36" s="96"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="153"/>
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="160"/>
       <c r="B37" s="38">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -3882,8 +3882,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="153"/>
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="160"/>
       <c r="B38" s="38">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -3905,8 +3905,8 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="153"/>
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="160"/>
       <c r="B39" s="38">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -3928,8 +3928,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="153"/>
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="160"/>
       <c r="B40" s="38">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -3951,8 +3951,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="153"/>
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="160"/>
       <c r="B41" s="38">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -3974,8 +3974,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="153"/>
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="160"/>
       <c r="B42" s="38">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -3997,8 +3997,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="153"/>
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="160"/>
       <c r="B43" s="38">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -4020,8 +4020,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="153"/>
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="160"/>
       <c r="B44" s="38">
         <f t="shared" si="6"/>
         <v>25</v>
@@ -4043,8 +4043,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="153"/>
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="160"/>
       <c r="B45" s="38">
         <f t="shared" si="6"/>
         <v>26</v>
@@ -4066,8 +4066,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="153"/>
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="160"/>
       <c r="B46" s="38">
         <f t="shared" si="6"/>
         <v>27</v>
@@ -4089,8 +4089,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="153"/>
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="160"/>
       <c r="B47" s="38">
         <f t="shared" si="6"/>
         <v>28</v>
@@ -4132,44 +4132,44 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2610A015-4E55-4C5A-A6A9-925DBA45A0C3}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="148" t="s">
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+      <c r="B3" s="155" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="148"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="148"/>
-      <c r="K3" s="148"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -4221,7 +4221,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="161" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -4258,7 +4258,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="155"/>
+      <c r="A8" s="162"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -4294,7 +4294,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="155"/>
+      <c r="A9" s="162"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -4327,7 +4327,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="155"/>
+      <c r="A10" s="162"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -4358,17 +4358,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="157" t="s">
+      <c r="N10" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="157"/>
-      <c r="P10" s="158">
+      <c r="O10" s="164"/>
+      <c r="P10" s="165">
         <f>SUM(F7:F1006)</f>
         <v>30573000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="155"/>
+      <c r="A11" s="162"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="158"/>
+      <c r="N11" s="164"/>
+      <c r="O11" s="164"/>
+      <c r="P11" s="165"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="155"/>
+      <c r="A12" s="162"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -4429,17 +4429,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="159" t="s">
+      <c r="N12" s="166" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="159"/>
-      <c r="P12" s="158">
+      <c r="O12" s="166"/>
+      <c r="P12" s="165">
         <f>SUM(G7:G1006)</f>
         <v>16022500</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="155"/>
+      <c r="A13" s="162"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -4464,12 +4464,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="159"/>
-      <c r="O13" s="159"/>
-      <c r="P13" s="158"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="166"/>
+      <c r="P13" s="165"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="155"/>
+      <c r="A14" s="162"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -4494,12 +4494,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="159"/>
-      <c r="O14" s="159"/>
-      <c r="P14" s="158"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="155"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="166"/>
+      <c r="P14" s="165"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="162"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -4524,17 +4524,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="160" t="s">
+      <c r="N15" s="167" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="160"/>
+      <c r="O15" s="167"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>15420500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="155"/>
+      <c r="A16" s="162"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -4561,7 +4561,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="155"/>
+      <c r="A17" s="162"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -4587,8 +4587,8 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="155"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="162"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -4623,8 +4623,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="156"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="163"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -4647,7 +4647,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="152" t="s">
+      <c r="A20" s="159" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -4681,7 +4681,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="153"/>
+      <c r="A21" s="160"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -4714,7 +4714,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="153"/>
+      <c r="A22" s="160"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -4747,7 +4747,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="153"/>
+      <c r="A23" s="160"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -4770,7 +4770,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="153"/>
+      <c r="A24" s="160"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -4803,7 +4803,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="153"/>
+      <c r="A25" s="160"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -4835,8 +4835,8 @@
       <c r="K25" s="84"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="153"/>
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="160"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -4868,8 +4868,8 @@
       <c r="K26" s="85"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="153"/>
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="160"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -4901,8 +4901,8 @@
       <c r="K27" s="85"/>
       <c r="L27" s="76"/>
     </row>
-    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="153"/>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="160"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -4934,8 +4934,8 @@
       <c r="K28" s="91"/>
       <c r="L28" s="76"/>
     </row>
-    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="153"/>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="160"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -4958,7 +4958,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="153"/>
+      <c r="A30" s="160"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -4990,8 +4990,8 @@
       <c r="K30" s="85"/>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="153"/>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="160"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -5023,8 +5023,8 @@
       <c r="K31" s="106"/>
       <c r="L31" s="93"/>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="153"/>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="160"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -5056,8 +5056,8 @@
       <c r="K32" s="106"/>
       <c r="L32" s="93"/>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="153"/>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="160"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -5081,8 +5081,8 @@
       <c r="K33" s="106"/>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="153"/>
+    <row r="34" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A34" s="160"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -5114,8 +5114,8 @@
       <c r="K34" s="92"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="153"/>
+    <row r="35" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A35" s="160"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -5147,8 +5147,8 @@
       <c r="K35" s="85"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="153"/>
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="160"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -5180,8 +5180,8 @@
       <c r="K36" s="96"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="153"/>
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="160"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -5203,8 +5203,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="153"/>
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="160"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -5226,8 +5226,8 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="153"/>
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="160"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -5249,8 +5249,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="153"/>
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="160"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -5272,8 +5272,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="153"/>
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="160"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -5295,8 +5295,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="153"/>
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="160"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -5318,8 +5318,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="153"/>
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="160"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -5341,8 +5341,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="153"/>
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="160"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -5364,8 +5364,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="153"/>
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="160"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -5387,8 +5387,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="153"/>
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="160"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -5410,8 +5410,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="153"/>
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="160"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -5453,44 +5453,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF137B8B-2BBD-4D18-BE8C-6301B6B835E6}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="148" t="s">
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+      <c r="B3" s="155" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="148"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="148"/>
-      <c r="K3" s="148"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -5542,7 +5542,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="161" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -5579,7 +5579,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="155"/>
+      <c r="A8" s="162"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -5615,7 +5615,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="155"/>
+      <c r="A9" s="162"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -5644,7 +5644,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="155"/>
+      <c r="A10" s="162"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -5675,17 +5675,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="157" t="s">
+      <c r="N10" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="157"/>
-      <c r="P10" s="158">
+      <c r="O10" s="164"/>
+      <c r="P10" s="165">
         <f>SUM(F7:F1006)</f>
         <v>3545000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="155"/>
+      <c r="A11" s="162"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -5716,12 +5716,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="158"/>
+      <c r="N11" s="164"/>
+      <c r="O11" s="164"/>
+      <c r="P11" s="165"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="155"/>
+      <c r="A12" s="162"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -5746,17 +5746,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="159" t="s">
+      <c r="N12" s="166" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="159"/>
-      <c r="P12" s="158">
+      <c r="O12" s="166"/>
+      <c r="P12" s="165">
         <f>SUM(G7:G1006)</f>
         <v>2127000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="155"/>
+      <c r="A13" s="162"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -5781,12 +5781,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="159"/>
-      <c r="O13" s="159"/>
-      <c r="P13" s="158"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="166"/>
+      <c r="P13" s="165"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="155"/>
+      <c r="A14" s="162"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -5811,12 +5811,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="159"/>
-      <c r="O14" s="159"/>
-      <c r="P14" s="158"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="155"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="166"/>
+      <c r="P14" s="165"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="162"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -5841,17 +5841,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="160" t="s">
+      <c r="N15" s="167" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="160"/>
+      <c r="O15" s="167"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>2010000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="155"/>
+      <c r="A16" s="162"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -5878,7 +5878,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="155"/>
+      <c r="A17" s="162"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -5904,8 +5904,8 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="155"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="162"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -5940,8 +5940,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="156"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="163"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -5964,7 +5964,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="152" t="s">
+      <c r="A20" s="159" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -5994,7 +5994,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="153"/>
+      <c r="A21" s="160"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -6023,7 +6023,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="153"/>
+      <c r="A22" s="160"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -6052,7 +6052,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="153"/>
+      <c r="A23" s="160"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -6077,7 +6077,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="153"/>
+      <c r="A24" s="160"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -6106,7 +6106,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="153"/>
+      <c r="A25" s="160"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -6134,8 +6134,8 @@
       </c>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="153"/>
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="160"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -6163,8 +6163,8 @@
       </c>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="153"/>
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="160"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -6193,7 +6193,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="153"/>
+      <c r="A28" s="160"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -6222,7 +6222,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="153"/>
+      <c r="A29" s="160"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -6247,7 +6247,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="153"/>
+      <c r="A30" s="160"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -6276,7 +6276,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="153"/>
+      <c r="A31" s="160"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -6305,7 +6305,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="153"/>
+      <c r="A32" s="160"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -6334,7 +6334,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="153"/>
+      <c r="A33" s="160"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -6360,8 +6360,8 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="153"/>
+    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A34" s="160"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -6389,8 +6389,8 @@
       </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="153"/>
+    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="160"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -6418,8 +6418,8 @@
       </c>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="153"/>
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="160"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -6447,8 +6447,8 @@
       </c>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="153"/>
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="160"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -6470,8 +6470,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="153"/>
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="160"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -6493,8 +6493,8 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="153"/>
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="160"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -6516,8 +6516,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="153"/>
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="160"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -6539,8 +6539,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="153"/>
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="160"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -6562,8 +6562,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="153"/>
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="160"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -6585,8 +6585,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="153"/>
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="160"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -6608,8 +6608,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="153"/>
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="160"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -6631,8 +6631,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="153"/>
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="160"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -6654,8 +6654,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="153"/>
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="160"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -6677,8 +6677,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="153"/>
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="160"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -6720,44 +6720,44 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C31C35F-5774-4DEE-9905-7B7C61A41D99}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="148" t="s">
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+      <c r="B3" s="155" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="148"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="148"/>
-      <c r="K3" s="148"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -6809,7 +6809,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="161" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -6846,7 +6846,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="155"/>
+      <c r="A8" s="162"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -6874,7 +6874,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="155"/>
+      <c r="A9" s="162"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -6903,7 +6903,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="155"/>
+      <c r="A10" s="162"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -6934,17 +6934,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="157" t="s">
+      <c r="N10" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="157"/>
-      <c r="P10" s="158">
+      <c r="O10" s="164"/>
+      <c r="P10" s="165">
         <f>SUM(F7:F1006)</f>
         <v>40751000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="155"/>
+      <c r="A11" s="162"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="158"/>
+      <c r="N11" s="164"/>
+      <c r="O11" s="164"/>
+      <c r="P11" s="165"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="155"/>
+      <c r="A12" s="162"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -7005,17 +7005,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="159" t="s">
+      <c r="N12" s="166" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="159"/>
-      <c r="P12" s="158">
+      <c r="O12" s="166"/>
+      <c r="P12" s="165">
         <f>SUM(G7:G1006)</f>
         <v>20907500</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="155"/>
+      <c r="A13" s="162"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -7040,12 +7040,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="159"/>
-      <c r="O13" s="159"/>
-      <c r="P13" s="158"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="166"/>
+      <c r="P13" s="165"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="155"/>
+      <c r="A14" s="162"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7070,12 +7070,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="159"/>
-      <c r="O14" s="159"/>
-      <c r="P14" s="158"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="155"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="166"/>
+      <c r="P14" s="165"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="162"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -7100,17 +7100,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="160" t="s">
+      <c r="N15" s="167" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="160"/>
+      <c r="O15" s="167"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>21280000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="155"/>
+      <c r="A16" s="162"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -7135,7 +7135,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="155"/>
+      <c r="A17" s="162"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -7159,8 +7159,8 @@
       <c r="K17" s="130"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="155"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="162"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -7193,8 +7193,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="156"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="163"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -7217,7 +7217,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="152" t="s">
+      <c r="A20" s="159" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -7251,7 +7251,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="153"/>
+      <c r="A21" s="160"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -7280,7 +7280,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="153"/>
+      <c r="A22" s="160"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -7313,7 +7313,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="153"/>
+      <c r="A23" s="160"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -7346,7 +7346,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="153"/>
+      <c r="A24" s="160"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -7379,7 +7379,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="153"/>
+      <c r="A25" s="160"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -7411,8 +7411,8 @@
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="153"/>
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="160"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -7444,8 +7444,8 @@
       <c r="K26" s="132"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="153"/>
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="160"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -7478,7 +7478,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="153"/>
+      <c r="A28" s="160"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -7513,7 +7513,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="153"/>
+      <c r="A29" s="160"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -7548,7 +7548,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="153"/>
+      <c r="A30" s="160"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -7581,7 +7581,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="153"/>
+      <c r="A31" s="160"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -7614,7 +7614,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="153"/>
+      <c r="A32" s="160"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -7647,7 +7647,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="153"/>
+      <c r="A33" s="160"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -7681,8 +7681,8 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="153"/>
+    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A34" s="160"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -7716,8 +7716,8 @@
       </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="153"/>
+    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="160"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -7749,8 +7749,8 @@
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="153"/>
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="160"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -7782,8 +7782,8 @@
       <c r="K36" s="132"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="153"/>
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="160"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -7809,8 +7809,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="153"/>
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="160"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -7836,8 +7836,8 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="153"/>
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="160"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -7861,8 +7861,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="153"/>
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="160"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -7886,8 +7886,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="153"/>
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="160"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -7911,8 +7911,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="153"/>
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="160"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -7936,8 +7936,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="153"/>
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="160"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -7959,8 +7959,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="153"/>
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="160"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -7982,8 +7982,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="153"/>
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="160"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -8005,8 +8005,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="153"/>
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="160"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -8028,8 +8028,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="153"/>
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="160"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -8071,44 +8071,44 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA68E37-18F4-45D2-9A8A-CA2CAECC56FB}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="148" t="s">
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+      <c r="B3" s="155" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="148"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="148"/>
-      <c r="K3" s="148"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -8160,7 +8160,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="161" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -8197,7 +8197,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="155"/>
+      <c r="A8" s="162"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -8233,7 +8233,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="155"/>
+      <c r="A9" s="162"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -8260,7 +8260,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="155"/>
+      <c r="A10" s="162"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -8291,17 +8291,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="157" t="s">
+      <c r="N10" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="157"/>
-      <c r="P10" s="158">
+      <c r="O10" s="164"/>
+      <c r="P10" s="165">
         <f>SUM(F7:F1006)</f>
         <v>32460000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="155"/>
+      <c r="A11" s="162"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -8324,12 +8324,12 @@
       <c r="J11" s="128"/>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="158"/>
+      <c r="N11" s="164"/>
+      <c r="O11" s="164"/>
+      <c r="P11" s="165"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="155"/>
+      <c r="A12" s="162"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -8354,17 +8354,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="159" t="s">
+      <c r="N12" s="166" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="159"/>
-      <c r="P12" s="158">
+      <c r="O12" s="166"/>
+      <c r="P12" s="165">
         <f>SUM(G7:G1006)</f>
         <v>17157000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="155"/>
+      <c r="A13" s="162"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -8389,12 +8389,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="159"/>
-      <c r="O13" s="159"/>
-      <c r="P13" s="158"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="166"/>
+      <c r="P13" s="165"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="155"/>
+      <c r="A14" s="162"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -8419,12 +8419,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="159"/>
-      <c r="O14" s="159"/>
-      <c r="P14" s="158"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="155"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="166"/>
+      <c r="P14" s="165"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="162"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -8449,17 +8449,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="160" t="s">
+      <c r="N15" s="167" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="160"/>
+      <c r="O15" s="167"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>16778500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="155"/>
+      <c r="A16" s="162"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -8484,7 +8484,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="155"/>
+      <c r="A17" s="162"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -8508,8 +8508,8 @@
       <c r="K17" s="130"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="155"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="162"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -8542,8 +8542,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="156"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="163"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -8566,7 +8566,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="152" t="s">
+      <c r="A20" s="159" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -8596,7 +8596,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="153"/>
+      <c r="A21" s="160"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -8629,7 +8629,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="153"/>
+      <c r="A22" s="160"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -8664,7 +8664,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="153"/>
+      <c r="A23" s="160"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -8693,7 +8693,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="153"/>
+      <c r="A24" s="160"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -8726,7 +8726,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="153"/>
+      <c r="A25" s="160"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -8758,8 +8758,8 @@
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="153"/>
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="160"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -8791,8 +8791,8 @@
       <c r="K26" s="132"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="153"/>
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="160"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -8825,7 +8825,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="153"/>
+      <c r="A28" s="160"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -8858,7 +8858,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="153"/>
+      <c r="A29" s="160"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -8891,7 +8891,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="153"/>
+      <c r="A30" s="160"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -8924,7 +8924,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="153"/>
+      <c r="A31" s="160"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -8957,7 +8957,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="153"/>
+      <c r="A32" s="160"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -8990,7 +8990,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="153"/>
+      <c r="A33" s="160"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -9024,8 +9024,8 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="153"/>
+    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A34" s="160"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -9059,8 +9059,8 @@
       </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="153"/>
+    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="160"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -9092,8 +9092,8 @@
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="153"/>
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="160"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -9125,8 +9125,8 @@
       <c r="K36" s="132"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="153"/>
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="160"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -9150,8 +9150,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="153"/>
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="160"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -9185,8 +9185,8 @@
       </c>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="153"/>
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="160"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -9210,8 +9210,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="153"/>
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="160"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -9235,8 +9235,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="153"/>
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="160"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -9260,8 +9260,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="153"/>
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="160"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -9285,8 +9285,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="153"/>
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="160"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -9308,8 +9308,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="153"/>
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="160"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -9331,8 +9331,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="153"/>
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="160"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -9354,8 +9354,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="153"/>
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="160"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -9377,8 +9377,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="153"/>
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="160"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -9419,44 +9419,44 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DDB050C-EFA5-4BA1-89FF-2BF72F913523}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="148" t="s">
+    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
+      <c r="B3" s="155" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="148"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="148"/>
-      <c r="K3" s="148"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -9508,7 +9508,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="161" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -9545,7 +9545,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="155"/>
+      <c r="A8" s="162"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -9581,7 +9581,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="155"/>
+      <c r="A9" s="162"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -9604,13 +9604,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="127"/>
-      <c r="K9" s="167" t="s">
+      <c r="K9" s="154" t="s">
         <v>145</v>
       </c>
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="155"/>
+      <c r="A10" s="162"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -9641,17 +9641,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="157" t="s">
+      <c r="N10" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="157"/>
-      <c r="P10" s="158">
+      <c r="O10" s="164"/>
+      <c r="P10" s="165">
         <f>SUM(F7:F1006)</f>
         <v>35340000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="155"/>
+      <c r="A11" s="162"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -9674,12 +9674,12 @@
       <c r="J11" s="128"/>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="158"/>
+      <c r="N11" s="164"/>
+      <c r="O11" s="164"/>
+      <c r="P11" s="165"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="155"/>
+      <c r="A12" s="162"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -9704,17 +9704,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="159" t="s">
+      <c r="N12" s="166" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="159"/>
-      <c r="P12" s="158">
+      <c r="O12" s="166"/>
+      <c r="P12" s="165">
         <f>SUM(G7:G1006)</f>
         <v>18504400</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="155"/>
+      <c r="A13" s="162"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -9739,12 +9739,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="159"/>
-      <c r="O13" s="159"/>
-      <c r="P13" s="158"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="166"/>
+      <c r="P13" s="165"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="155"/>
+      <c r="A14" s="162"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -9769,12 +9769,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="159"/>
-      <c r="O14" s="159"/>
-      <c r="P14" s="158"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="155"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="166"/>
+      <c r="P14" s="165"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="162"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -9799,17 +9799,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="160" t="s">
+      <c r="N15" s="167" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="160"/>
+      <c r="O15" s="167"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>18210000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="155"/>
+      <c r="A16" s="162"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -9834,7 +9834,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="155"/>
+      <c r="A17" s="162"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -9858,8 +9858,8 @@
       <c r="K17" s="130"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="155"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="162"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -9892,8 +9892,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="156"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="163"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -9916,7 +9916,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="152" t="s">
+      <c r="A20" s="159" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -9946,7 +9946,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="153"/>
+      <c r="A21" s="160"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -9979,7 +9979,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="153"/>
+      <c r="A22" s="160"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -10008,13 +10008,13 @@
       <c r="J22" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="K22" s="161" t="s">
+      <c r="K22" s="148" t="s">
         <v>147</v>
       </c>
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="153"/>
+      <c r="A23" s="160"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -10039,7 +10039,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="153"/>
+      <c r="A24" s="160"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -10072,7 +10072,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="153"/>
+      <c r="A25" s="160"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -10104,8 +10104,8 @@
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="153"/>
+    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="160"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -10137,8 +10137,8 @@
       <c r="K26" s="132"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="153"/>
+    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="160"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -10171,7 +10171,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="153"/>
+      <c r="A28" s="160"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -10204,7 +10204,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="153"/>
+      <c r="A29" s="160"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -10237,7 +10237,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="153"/>
+      <c r="A30" s="160"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -10270,7 +10270,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="153"/>
+      <c r="A31" s="160"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -10305,7 +10305,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="153"/>
+      <c r="A32" s="160"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -10338,7 +10338,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="153"/>
+      <c r="A33" s="160"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -10370,8 +10370,8 @@
       <c r="K33" s="89"/>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="153"/>
+    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A34" s="160"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -10403,8 +10403,8 @@
       <c r="K34" s="132"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="153"/>
+    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="160"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -10436,8 +10436,8 @@
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="153"/>
+    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="160"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -10469,23 +10469,23 @@
       <c r="K36" s="132"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="153"/>
+    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="160"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="C37" s="162"/>
-      <c r="D37" s="163"/>
-      <c r="E37" s="164" t="s">
+      <c r="C37" s="149"/>
+      <c r="D37" s="150"/>
+      <c r="E37" s="151" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="165"/>
+      <c r="F37" s="152"/>
       <c r="G37" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H37" s="166"/>
+      <c r="H37" s="153"/>
       <c r="I37" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -10494,8 +10494,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="153"/>
+    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="160"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -10527,8 +10527,8 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="153"/>
+    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="160"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -10552,8 +10552,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="153"/>
+    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="160"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -10577,8 +10577,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="153"/>
+    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="160"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -10602,8 +10602,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="153"/>
+    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="160"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -10627,8 +10627,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="153"/>
+    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="160"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -10650,8 +10650,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="153"/>
+    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="160"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -10673,8 +10673,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="153"/>
+    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="160"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -10696,8 +10696,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="153"/>
+    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="160"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -10719,8 +10719,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="153"/>
+    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="160"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>

--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MINH HAI DRIVER\MinhHaiDriver2\Theo dõi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5662BB34-0092-486F-8D0E-CBDA1794A885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924336F6-BB63-4DF0-B102-2E2CBE591715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="579" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10-01" sheetId="14" state="hidden" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="04-02" sheetId="40" r:id="rId5"/>
     <sheet name="05-02" sheetId="41" r:id="rId6"/>
     <sheet name="06-02" sheetId="42" r:id="rId7"/>
+    <sheet name="07-02" sheetId="43" r:id="rId8"/>
+    <sheet name="08-02" sheetId="44" r:id="rId9"/>
+    <sheet name="09-02" sheetId="45" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="159">
   <si>
     <t>STT</t>
   </si>
@@ -487,13 +490,43 @@
   </si>
   <si>
     <t xml:space="preserve">50k đèn xi nhan </t>
+  </si>
+  <si>
+    <t>DOANH THU 07/02/2026</t>
+  </si>
+  <si>
+    <t>nghỉ, chạy lấy xe đi vòng vòng rồi về</t>
+  </si>
+  <si>
+    <t>đi du lịch hòn thơm</t>
+  </si>
+  <si>
+    <t>đi nghỉ tết</t>
+  </si>
+  <si>
+    <t>chuyển dư 245 và làm chuôi cắm 100</t>
+  </si>
+  <si>
+    <t>QUỐC PHONG</t>
+  </si>
+  <si>
+    <t>DOANH THU 08/02/2026</t>
+  </si>
+  <si>
+    <t>đi phà chưa chuyển khoản</t>
+  </si>
+  <si>
+    <t>trừ vào tiền cọc xe</t>
+  </si>
+  <si>
+    <t>DOANH THU 09/02/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -715,6 +748,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -977,7 +1017,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1405,6 +1445,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1991,58 +2044,58 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25421AD-4B15-4CE5-B032-F166D9527995}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A2:P59"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.42578125" style="1" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="21" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.44140625" style="1" customWidth="1"/>
-    <col min="14" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="16.88671875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="1"/>
+    <col min="13" max="13" width="19.42578125" style="1" customWidth="1"/>
+    <col min="14" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="16.85546875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="160" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
-    </row>
-    <row r="3" spans="2:16" ht="30.6" x14ac:dyDescent="0.25">
-      <c r="B3" s="156" t="s">
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+    </row>
+    <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="161" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157"/>
-      <c r="J3" s="157"/>
-      <c r="K3" s="157"/>
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="21"/>
     </row>
-    <row r="6" spans="2:16" ht="21" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:16" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -2083,7 +2136,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>1</v>
       </c>
@@ -2118,7 +2171,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <f t="shared" ref="B8:B23" si="0">B7 +1</f>
         <v>2</v>
@@ -2156,7 +2209,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2190,7 +2243,7 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2224,7 +2277,7 @@
       <c r="L10" s="37"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="2:16" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <f>B10 +1</f>
         <v>5</v>
@@ -2260,7 +2313,7 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2294,7 +2347,7 @@
       <c r="L12" s="8"/>
       <c r="M12" s="9"/>
     </row>
-    <row r="13" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2330,7 +2383,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2363,7 +2416,7 @@
       <c r="L14" s="8"/>
       <c r="M14" s="9"/>
     </row>
-    <row r="15" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2397,7 +2450,7 @@
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
     </row>
-    <row r="16" spans="2:16" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2431,7 +2484,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2465,7 +2518,7 @@
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
     </row>
-    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2501,7 +2554,7 @@
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
     </row>
-    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2534,7 +2587,7 @@
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
     </row>
-    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="B20" s="3">
         <f t="shared" si="0"/>
@@ -2567,7 +2620,7 @@
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
     </row>
-    <row r="21" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="25"/>
       <c r="B21" s="3">
         <f t="shared" si="0"/>
@@ -2600,7 +2653,7 @@
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
     </row>
-    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2634,7 +2687,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="8"/>
     </row>
-    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2668,7 +2721,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="8"/>
     </row>
-    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -2685,7 +2738,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="8"/>
     </row>
-    <row r="26" spans="1:13" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
       <c r="C26" s="18" t="s">
         <v>60</v>
       </c>
@@ -2695,20 +2748,20 @@
       <c r="F26" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="158" t="s">
+      <c r="H26" s="163" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="158"/>
+      <c r="I26" s="163"/>
       <c r="J26" s="5">
         <f>SUM(H7:H1001)</f>
         <v>28869000</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="H27" s="158" t="s">
+    <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="H27" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="158"/>
+      <c r="I27" s="163"/>
       <c r="J27" s="5">
         <f>SUM(I7:I1001)</f>
         <v>17311000</v>
@@ -2724,17 +2777,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B44" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B45" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B46" s="12" t="s">
         <v>16</v>
       </c>
@@ -2742,67 +2795,67 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B47" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="2:4" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B48" s="12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B49" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B51" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B53" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B55" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B56" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B57" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="58" spans="2:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="31" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="2:2" ht="14.4" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:K2"/>
@@ -2819,47 +2872,1361 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98BF2736-7444-48AB-AC37-B03361E9F460}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="160" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="166" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="41">
+        <v>1000000</v>
+      </c>
+      <c r="G7" s="41">
+        <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
+        <v>600000</v>
+      </c>
+      <c r="H7" s="41">
+        <v>600000</v>
+      </c>
+      <c r="I7" s="41">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="129" t="s">
+        <v>157</v>
+      </c>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="167"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41">
+        <v>1220000</v>
+      </c>
+      <c r="G8" s="41">
+        <f t="shared" ref="G8:G18" si="0">IF(F8="",0,IF(F8&gt;1800000,F8*O$19,F8*O$18))</f>
+        <v>732000</v>
+      </c>
+      <c r="H8" s="41">
+        <v>610000</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="1">G8-H8</f>
+        <v>122000</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="130"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="167"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="2">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="122"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="126"/>
+      <c r="I9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="159"/>
+      <c r="K9" s="154"/>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="167"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="44">
+        <v>1400000</v>
+      </c>
+      <c r="G10" s="41">
+        <f t="shared" si="0"/>
+        <v>840000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>840000</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="130"/>
+      <c r="L10" s="46"/>
+      <c r="N10" s="169" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="169"/>
+      <c r="P10" s="170">
+        <f>SUM(F7:F1006)</f>
+        <v>33741000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="167"/>
+      <c r="B11" s="38">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="44"/>
+      <c r="I11" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="155"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="170"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="167"/>
+      <c r="B12" s="38">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="155"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="171" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="171"/>
+      <c r="P12" s="170">
+        <f>SUM(G7:G1006)</f>
+        <v>17932800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="167"/>
+      <c r="B13" s="38">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="155"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="170"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="167"/>
+      <c r="B14" s="38">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="170"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="167"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="172" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="172"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>16981000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="167"/>
+      <c r="B16" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="167"/>
+      <c r="B17" s="38">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="167"/>
+      <c r="B18" s="38">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="168"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="164" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="139"/>
+      <c r="I20" s="75">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="128"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="165"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="79">
+        <v>1320000</v>
+      </c>
+      <c r="G21" s="75">
+        <f t="shared" si="3"/>
+        <v>792000</v>
+      </c>
+      <c r="H21" s="79">
+        <v>660000</v>
+      </c>
+      <c r="I21" s="75">
+        <f t="shared" si="4"/>
+        <v>132000</v>
+      </c>
+      <c r="J21" s="62"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="165"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75">
+        <v>1500000</v>
+      </c>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>900000</v>
+      </c>
+      <c r="H22" s="79">
+        <v>900000</v>
+      </c>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" s="158">
+        <v>1500</v>
+      </c>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="165"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="73" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="75">
+        <v>920000</v>
+      </c>
+      <c r="G23" s="75">
+        <f t="shared" si="3"/>
+        <v>552000</v>
+      </c>
+      <c r="H23" s="75">
+        <v>552000</v>
+      </c>
+      <c r="I23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K23" s="132"/>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="165"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="75">
+        <v>2900000</v>
+      </c>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>1450000</v>
+      </c>
+      <c r="H24" s="79">
+        <v>1450000</v>
+      </c>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="128"/>
+      <c r="K24" s="132"/>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="165"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="75">
+        <v>1770000</v>
+      </c>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>885000</v>
+      </c>
+      <c r="H25" s="79">
+        <v>885000</v>
+      </c>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="128"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="165"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="75">
+        <v>2730000</v>
+      </c>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>1365000</v>
+      </c>
+      <c r="H26" s="75">
+        <v>1365000</v>
+      </c>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26" s="132"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="165"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="87"/>
+      <c r="E27" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="79">
+        <v>1363000</v>
+      </c>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>817800</v>
+      </c>
+      <c r="H27" s="75">
+        <v>816000</v>
+      </c>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>1800</v>
+      </c>
+      <c r="J27" s="128"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="165"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="79">
+        <v>740000</v>
+      </c>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>444000</v>
+      </c>
+      <c r="H28" s="79">
+        <v>444000</v>
+      </c>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="128"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="165"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="118">
+        <v>3360000</v>
+      </c>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>1680000</v>
+      </c>
+      <c r="H29" s="118">
+        <v>1680000</v>
+      </c>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="128"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="165"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="78"/>
+      <c r="E30" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="89">
+        <v>1160000</v>
+      </c>
+      <c r="G30" s="75">
+        <f t="shared" si="3"/>
+        <v>696000</v>
+      </c>
+      <c r="H30" s="119"/>
+      <c r="I30" s="75">
+        <f t="shared" si="4"/>
+        <v>696000</v>
+      </c>
+      <c r="J30" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="K30" s="132" t="s">
+        <v>156</v>
+      </c>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="165"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="89">
+        <v>2060000</v>
+      </c>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>1030000</v>
+      </c>
+      <c r="H31" s="89">
+        <v>1030000</v>
+      </c>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="128"/>
+      <c r="K31" s="132"/>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="165"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="156" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="157"/>
+      <c r="E32" s="140" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="139"/>
+      <c r="G32" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="139"/>
+      <c r="I32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="128"/>
+      <c r="K32" s="132"/>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="165"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="87"/>
+      <c r="E33" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="90">
+        <v>1768000</v>
+      </c>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>884000</v>
+      </c>
+      <c r="H33" s="89">
+        <v>884000</v>
+      </c>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="128"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="165"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="79">
+        <v>2030000</v>
+      </c>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>1015000</v>
+      </c>
+      <c r="H34" s="79">
+        <v>1015000</v>
+      </c>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="128"/>
+      <c r="K34" s="132"/>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="165"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="120"/>
+      <c r="E35" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="118">
+        <v>2100000</v>
+      </c>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>1050000</v>
+      </c>
+      <c r="H35" s="118">
+        <v>1050000</v>
+      </c>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="128"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="165"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="87" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="120"/>
+      <c r="E36" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="118">
+        <v>2000000</v>
+      </c>
+      <c r="G36" s="75">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+      <c r="H36" s="118">
+        <v>1000000</v>
+      </c>
+      <c r="I36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="128"/>
+      <c r="K36" s="132"/>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="165"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="142"/>
+      <c r="D37" s="143"/>
+      <c r="E37" s="144" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="145"/>
+      <c r="G37" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="146"/>
+      <c r="I37" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="83"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="165"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="43"/>
+      <c r="E38" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="90">
+        <v>2400000</v>
+      </c>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>1200000</v>
+      </c>
+      <c r="H38" s="89">
+        <v>1200000</v>
+      </c>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="128"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="165"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="90"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="165"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="90"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="165"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="165"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="165"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="165"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="165"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="165"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="165"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBEB86F-A8DD-42F9-B2B2-37DBDB0C26B6}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
-      <c r="B3" s="155" t="s">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="160" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="155"/>
-      <c r="K3" s="155"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -2911,7 +4278,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="161" t="s">
+      <c r="A7" s="166" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -2948,7 +4315,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162"/>
+      <c r="A8" s="167"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -2984,7 +4351,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162"/>
+      <c r="A9" s="167"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -3016,7 +4383,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="162"/>
+      <c r="A10" s="167"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -3047,17 +4414,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="164" t="s">
+      <c r="N10" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="164"/>
-      <c r="P10" s="165">
+      <c r="O10" s="169"/>
+      <c r="P10" s="170">
         <f>SUM(F7:F1006)</f>
         <v>16675000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="162"/>
+      <c r="A11" s="167"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -3088,12 +4455,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164"/>
-      <c r="P11" s="165"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="170"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="162"/>
+      <c r="A12" s="167"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -3118,17 +4485,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="166" t="s">
+      <c r="N12" s="171" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="166"/>
-      <c r="P12" s="165">
+      <c r="O12" s="171"/>
+      <c r="P12" s="170">
         <f>SUM(G7:G1006)</f>
         <v>9346000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="162"/>
+      <c r="A13" s="167"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -3153,12 +4520,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
-      <c r="P13" s="165"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="170"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162"/>
+      <c r="A14" s="167"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -3183,12 +4550,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="166"/>
-      <c r="O14" s="166"/>
-      <c r="P14" s="165"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="162"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="170"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="167"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -3213,17 +4580,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="167" t="s">
+      <c r="N15" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="167"/>
+      <c r="O15" s="172"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>9285000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="162"/>
+      <c r="A16" s="167"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -3250,7 +4617,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="162"/>
+      <c r="A17" s="167"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -3276,8 +4643,8 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="162"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="167"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3312,8 +4679,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="163"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="168"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -3336,7 +4703,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="159" t="s">
+      <c r="A20" s="164" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -3368,7 +4735,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="160"/>
+      <c r="A21" s="165"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -3401,7 +4768,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="160"/>
+      <c r="A22" s="165"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="6">B21+1</f>
         <v>3</v>
@@ -3432,7 +4799,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="160"/>
+      <c r="A23" s="165"/>
       <c r="B23" s="38">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -3455,7 +4822,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="160"/>
+      <c r="A24" s="165"/>
       <c r="B24" s="38">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -3486,7 +4853,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="160"/>
+      <c r="A25" s="165"/>
       <c r="B25" s="38">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -3518,8 +4885,8 @@
       <c r="K25" s="84"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="160"/>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="165"/>
       <c r="B26" s="38">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -3549,8 +4916,8 @@
       </c>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="160"/>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="165"/>
       <c r="B27" s="38">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -3582,8 +4949,8 @@
       <c r="K27" s="85"/>
       <c r="L27" s="76"/>
     </row>
-    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="160"/>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="165"/>
       <c r="B28" s="38">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -3615,8 +4982,8 @@
       <c r="K28" s="91"/>
       <c r="L28" s="76"/>
     </row>
-    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="160"/>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="165"/>
       <c r="B29" s="38">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -3639,7 +5006,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="160"/>
+      <c r="A30" s="165"/>
       <c r="B30" s="38">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -3669,8 +5036,8 @@
       </c>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="160"/>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="165"/>
       <c r="B31" s="38">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3702,8 +5069,8 @@
       <c r="K31" s="106"/>
       <c r="L31" s="93"/>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="160"/>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="165"/>
       <c r="B32" s="38">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -3735,8 +5102,8 @@
       <c r="K32" s="106"/>
       <c r="L32" s="93"/>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="160"/>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="165"/>
       <c r="B33" s="38">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -3762,8 +5129,8 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18" x14ac:dyDescent="0.3">
-      <c r="A34" s="160"/>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="165"/>
       <c r="B34" s="38">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -3795,8 +5162,8 @@
       <c r="K34" s="92"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18" x14ac:dyDescent="0.3">
-      <c r="A35" s="160"/>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="165"/>
       <c r="B35" s="38">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -3826,8 +5193,8 @@
       </c>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="160"/>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="165"/>
       <c r="B36" s="38">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -3859,8 +5226,8 @@
       <c r="K36" s="96"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="160"/>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="165"/>
       <c r="B37" s="38">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -3882,8 +5249,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="160"/>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="165"/>
       <c r="B38" s="38">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -3905,8 +5272,8 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A39" s="160"/>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="165"/>
       <c r="B39" s="38">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -3928,8 +5295,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A40" s="160"/>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="165"/>
       <c r="B40" s="38">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -3951,8 +5318,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A41" s="160"/>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="165"/>
       <c r="B41" s="38">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -3974,8 +5341,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="160"/>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="165"/>
       <c r="B42" s="38">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -3997,8 +5364,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A43" s="160"/>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="165"/>
       <c r="B43" s="38">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -4020,8 +5387,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A44" s="160"/>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="165"/>
       <c r="B44" s="38">
         <f t="shared" si="6"/>
         <v>25</v>
@@ -4043,8 +5410,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A45" s="160"/>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="165"/>
       <c r="B45" s="38">
         <f t="shared" si="6"/>
         <v>26</v>
@@ -4066,8 +5433,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A46" s="160"/>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="165"/>
       <c r="B46" s="38">
         <f t="shared" si="6"/>
         <v>27</v>
@@ -4089,8 +5456,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="160"/>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="165"/>
       <c r="B47" s="38">
         <f t="shared" si="6"/>
         <v>28</v>
@@ -4132,44 +5499,44 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2610A015-4E55-4C5A-A6A9-925DBA45A0C3}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
-      <c r="B3" s="155" t="s">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="160" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="155"/>
-      <c r="K3" s="155"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -4221,7 +5588,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="161" t="s">
+      <c r="A7" s="166" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -4258,7 +5625,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162"/>
+      <c r="A8" s="167"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -4294,7 +5661,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162"/>
+      <c r="A9" s="167"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -4327,7 +5694,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="162"/>
+      <c r="A10" s="167"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -4358,17 +5725,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="164" t="s">
+      <c r="N10" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="164"/>
-      <c r="P10" s="165">
+      <c r="O10" s="169"/>
+      <c r="P10" s="170">
         <f>SUM(F7:F1006)</f>
         <v>30573000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="162"/>
+      <c r="A11" s="167"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -4399,12 +5766,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164"/>
-      <c r="P11" s="165"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="170"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="162"/>
+      <c r="A12" s="167"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -4429,17 +5796,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="166" t="s">
+      <c r="N12" s="171" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="166"/>
-      <c r="P12" s="165">
+      <c r="O12" s="171"/>
+      <c r="P12" s="170">
         <f>SUM(G7:G1006)</f>
         <v>16022500</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="162"/>
+      <c r="A13" s="167"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -4464,12 +5831,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
-      <c r="P13" s="165"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="170"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162"/>
+      <c r="A14" s="167"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -4494,12 +5861,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="166"/>
-      <c r="O14" s="166"/>
-      <c r="P14" s="165"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="162"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="170"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="167"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -4524,17 +5891,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="167" t="s">
+      <c r="N15" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="167"/>
+      <c r="O15" s="172"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>15420500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="162"/>
+      <c r="A16" s="167"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -4561,7 +5928,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="162"/>
+      <c r="A17" s="167"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -4587,8 +5954,8 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="162"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="167"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -4623,8 +5990,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="163"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="168"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -4647,7 +6014,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="159" t="s">
+      <c r="A20" s="164" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -4681,7 +6048,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="160"/>
+      <c r="A21" s="165"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -4714,7 +6081,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="160"/>
+      <c r="A22" s="165"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -4747,7 +6114,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="160"/>
+      <c r="A23" s="165"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -4770,7 +6137,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="160"/>
+      <c r="A24" s="165"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -4803,7 +6170,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="160"/>
+      <c r="A25" s="165"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -4835,8 +6202,8 @@
       <c r="K25" s="84"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="160"/>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="165"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -4868,8 +6235,8 @@
       <c r="K26" s="85"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="160"/>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="165"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -4901,8 +6268,8 @@
       <c r="K27" s="85"/>
       <c r="L27" s="76"/>
     </row>
-    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="160"/>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="165"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -4934,8 +6301,8 @@
       <c r="K28" s="91"/>
       <c r="L28" s="76"/>
     </row>
-    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="160"/>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="165"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -4958,7 +6325,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="160"/>
+      <c r="A30" s="165"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -4990,8 +6357,8 @@
       <c r="K30" s="85"/>
       <c r="L30" s="80"/>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="160"/>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="165"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -5023,8 +6390,8 @@
       <c r="K31" s="106"/>
       <c r="L31" s="93"/>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="160"/>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="165"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -5056,8 +6423,8 @@
       <c r="K32" s="106"/>
       <c r="L32" s="93"/>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="160"/>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="165"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -5081,8 +6448,8 @@
       <c r="K33" s="106"/>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="18" x14ac:dyDescent="0.3">
-      <c r="A34" s="160"/>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="165"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -5114,8 +6481,8 @@
       <c r="K34" s="92"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="18" x14ac:dyDescent="0.3">
-      <c r="A35" s="160"/>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="165"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -5147,8 +6514,8 @@
       <c r="K35" s="85"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="160"/>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="165"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -5180,8 +6547,8 @@
       <c r="K36" s="96"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="160"/>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="165"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -5203,8 +6570,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="160"/>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="165"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -5226,8 +6593,8 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A39" s="160"/>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="165"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -5249,8 +6616,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A40" s="160"/>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="165"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -5272,8 +6639,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A41" s="160"/>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="165"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -5295,8 +6662,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="160"/>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="165"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -5318,8 +6685,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A43" s="160"/>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="165"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -5341,8 +6708,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A44" s="160"/>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="165"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -5364,8 +6731,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A45" s="160"/>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="165"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -5387,8 +6754,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A46" s="160"/>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="165"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -5410,8 +6777,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="160"/>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="165"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -5453,44 +6820,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF137B8B-2BBD-4D18-BE8C-6301B6B835E6}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
-      <c r="B3" s="155" t="s">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="160" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="155"/>
-      <c r="K3" s="155"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -5542,7 +6909,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="161" t="s">
+      <c r="A7" s="166" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -5579,7 +6946,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162"/>
+      <c r="A8" s="167"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -5615,7 +6982,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162"/>
+      <c r="A9" s="167"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -5644,7 +7011,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="162"/>
+      <c r="A10" s="167"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -5675,17 +7042,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="164" t="s">
+      <c r="N10" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="164"/>
-      <c r="P10" s="165">
+      <c r="O10" s="169"/>
+      <c r="P10" s="170">
         <f>SUM(F7:F1006)</f>
         <v>3545000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="162"/>
+      <c r="A11" s="167"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -5716,12 +7083,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164"/>
-      <c r="P11" s="165"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="170"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="162"/>
+      <c r="A12" s="167"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -5746,17 +7113,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="166" t="s">
+      <c r="N12" s="171" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="166"/>
-      <c r="P12" s="165">
+      <c r="O12" s="171"/>
+      <c r="P12" s="170">
         <f>SUM(G7:G1006)</f>
         <v>2127000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="162"/>
+      <c r="A13" s="167"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -5781,12 +7148,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
-      <c r="P13" s="165"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="170"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162"/>
+      <c r="A14" s="167"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -5811,12 +7178,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="166"/>
-      <c r="O14" s="166"/>
-      <c r="P14" s="165"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="162"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="170"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="167"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -5841,17 +7208,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="167" t="s">
+      <c r="N15" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="167"/>
+      <c r="O15" s="172"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>2010000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="162"/>
+      <c r="A16" s="167"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -5878,7 +7245,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="162"/>
+      <c r="A17" s="167"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -5904,8 +7271,8 @@
       <c r="K17" s="96"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="162"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="167"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -5940,8 +7307,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="163"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="168"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -5964,7 +7331,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="159" t="s">
+      <c r="A20" s="164" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -5994,7 +7361,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="160"/>
+      <c r="A21" s="165"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -6023,7 +7390,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="160"/>
+      <c r="A22" s="165"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -6052,7 +7419,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="160"/>
+      <c r="A23" s="165"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -6077,7 +7444,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="160"/>
+      <c r="A24" s="165"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -6106,7 +7473,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="160"/>
+      <c r="A25" s="165"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -6134,8 +7501,8 @@
       </c>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="160"/>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="165"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -6163,8 +7530,8 @@
       </c>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="160"/>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="165"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -6193,7 +7560,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="160"/>
+      <c r="A28" s="165"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -6222,7 +7589,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="160"/>
+      <c r="A29" s="165"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -6247,7 +7614,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="160"/>
+      <c r="A30" s="165"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -6276,7 +7643,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="160"/>
+      <c r="A31" s="165"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -6305,7 +7672,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="160"/>
+      <c r="A32" s="165"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -6334,7 +7701,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="160"/>
+      <c r="A33" s="165"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -6360,8 +7727,8 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A34" s="160"/>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="165"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -6389,8 +7756,8 @@
       </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A35" s="160"/>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="165"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -6418,8 +7785,8 @@
       </c>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="160"/>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="165"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -6447,8 +7814,8 @@
       </c>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="160"/>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="165"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -6470,8 +7837,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="160"/>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="165"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -6493,8 +7860,8 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A39" s="160"/>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="165"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -6516,8 +7883,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A40" s="160"/>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="165"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -6539,8 +7906,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A41" s="160"/>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="165"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -6562,8 +7929,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="160"/>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="165"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -6585,8 +7952,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A43" s="160"/>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="165"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -6608,8 +7975,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A44" s="160"/>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="165"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -6631,8 +7998,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A45" s="160"/>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="165"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -6654,8 +8021,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A46" s="160"/>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="165"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -6677,8 +8044,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="160"/>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="165"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -6720,44 +8087,44 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C31C35F-5774-4DEE-9905-7B7C61A41D99}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
-      <c r="B3" s="155" t="s">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="160" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="155"/>
-      <c r="K3" s="155"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -6809,7 +8176,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="161" t="s">
+      <c r="A7" s="166" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -6846,7 +8213,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162"/>
+      <c r="A8" s="167"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -6874,7 +8241,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162"/>
+      <c r="A9" s="167"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -6903,7 +8270,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="162"/>
+      <c r="A10" s="167"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -6934,17 +8301,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="164" t="s">
+      <c r="N10" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="164"/>
-      <c r="P10" s="165">
+      <c r="O10" s="169"/>
+      <c r="P10" s="170">
         <f>SUM(F7:F1006)</f>
         <v>40751000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="162"/>
+      <c r="A11" s="167"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -6975,12 +8342,12 @@
       </c>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164"/>
-      <c r="P11" s="165"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="170"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="162"/>
+      <c r="A12" s="167"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -7005,17 +8372,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="166" t="s">
+      <c r="N12" s="171" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="166"/>
-      <c r="P12" s="165">
+      <c r="O12" s="171"/>
+      <c r="P12" s="170">
         <f>SUM(G7:G1006)</f>
         <v>20907500</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="162"/>
+      <c r="A13" s="167"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -7040,12 +8407,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
-      <c r="P13" s="165"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="170"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162"/>
+      <c r="A14" s="167"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7070,12 +8437,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="166"/>
-      <c r="O14" s="166"/>
-      <c r="P14" s="165"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="162"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="170"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="167"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -7100,17 +8467,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="167" t="s">
+      <c r="N15" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="167"/>
+      <c r="O15" s="172"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>21280000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="162"/>
+      <c r="A16" s="167"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -7135,7 +8502,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="162"/>
+      <c r="A17" s="167"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -7159,8 +8526,8 @@
       <c r="K17" s="130"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="162"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="167"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -7193,8 +8560,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="163"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="168"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -7217,7 +8584,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="159" t="s">
+      <c r="A20" s="164" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -7251,7 +8618,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="160"/>
+      <c r="A21" s="165"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -7280,7 +8647,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="160"/>
+      <c r="A22" s="165"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -7313,7 +8680,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="160"/>
+      <c r="A23" s="165"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -7346,7 +8713,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="160"/>
+      <c r="A24" s="165"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -7379,7 +8746,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="160"/>
+      <c r="A25" s="165"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -7411,8 +8778,8 @@
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="160"/>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="165"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -7444,8 +8811,8 @@
       <c r="K26" s="132"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="160"/>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="165"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -7478,7 +8845,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="160"/>
+      <c r="A28" s="165"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -7513,7 +8880,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="160"/>
+      <c r="A29" s="165"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -7548,7 +8915,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="160"/>
+      <c r="A30" s="165"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -7581,7 +8948,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="160"/>
+      <c r="A31" s="165"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -7614,7 +8981,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="160"/>
+      <c r="A32" s="165"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -7647,7 +9014,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="160"/>
+      <c r="A33" s="165"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -7681,8 +9048,8 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A34" s="160"/>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="165"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -7716,8 +9083,8 @@
       </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A35" s="160"/>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="165"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -7749,8 +9116,8 @@
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="160"/>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="165"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -7782,8 +9149,8 @@
       <c r="K36" s="132"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="160"/>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="165"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -7809,8 +9176,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="160"/>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="165"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -7836,8 +9203,8 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A39" s="160"/>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="165"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -7861,8 +9228,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A40" s="160"/>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="165"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -7886,8 +9253,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A41" s="160"/>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="165"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -7911,8 +9278,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="160"/>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="165"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -7936,8 +9303,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A43" s="160"/>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="165"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -7959,8 +9326,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A44" s="160"/>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="165"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -7982,8 +9349,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A45" s="160"/>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="165"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -8005,8 +9372,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A46" s="160"/>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="165"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -8028,8 +9395,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="160"/>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="165"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -8071,44 +9438,44 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA68E37-18F4-45D2-9A8A-CA2CAECC56FB}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
-      <c r="B3" s="155" t="s">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="160" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="155"/>
-      <c r="K3" s="155"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -8160,7 +9527,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="161" t="s">
+      <c r="A7" s="166" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -8197,7 +9564,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162"/>
+      <c r="A8" s="167"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -8233,7 +9600,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162"/>
+      <c r="A9" s="167"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -8260,7 +9627,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="162"/>
+      <c r="A10" s="167"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -8291,17 +9658,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="164" t="s">
+      <c r="N10" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="164"/>
-      <c r="P10" s="165">
+      <c r="O10" s="169"/>
+      <c r="P10" s="170">
         <f>SUM(F7:F1006)</f>
         <v>32460000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="162"/>
+      <c r="A11" s="167"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -8324,12 +9691,12 @@
       <c r="J11" s="128"/>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164"/>
-      <c r="P11" s="165"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="170"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="162"/>
+      <c r="A12" s="167"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -8354,17 +9721,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="166" t="s">
+      <c r="N12" s="171" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="166"/>
-      <c r="P12" s="165">
+      <c r="O12" s="171"/>
+      <c r="P12" s="170">
         <f>SUM(G7:G1006)</f>
         <v>17157000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="162"/>
+      <c r="A13" s="167"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -8389,12 +9756,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
-      <c r="P13" s="165"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="170"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162"/>
+      <c r="A14" s="167"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -8419,12 +9786,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="166"/>
-      <c r="O14" s="166"/>
-      <c r="P14" s="165"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="162"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="170"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="167"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -8449,17 +9816,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="167" t="s">
+      <c r="N15" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="167"/>
+      <c r="O15" s="172"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>16778500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="162"/>
+      <c r="A16" s="167"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -8484,7 +9851,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="162"/>
+      <c r="A17" s="167"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -8508,8 +9875,8 @@
       <c r="K17" s="130"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="162"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="167"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -8542,8 +9909,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="163"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="168"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -8566,7 +9933,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="159" t="s">
+      <c r="A20" s="164" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -8596,7 +9963,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="160"/>
+      <c r="A21" s="165"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -8629,7 +9996,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="160"/>
+      <c r="A22" s="165"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -8664,7 +10031,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="160"/>
+      <c r="A23" s="165"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -8693,7 +10060,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="160"/>
+      <c r="A24" s="165"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -8726,7 +10093,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="160"/>
+      <c r="A25" s="165"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -8758,8 +10125,8 @@
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="160"/>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="165"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -8791,8 +10158,8 @@
       <c r="K26" s="132"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="160"/>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="165"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -8825,7 +10192,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="160"/>
+      <c r="A28" s="165"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -8858,7 +10225,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="160"/>
+      <c r="A29" s="165"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -8891,7 +10258,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="160"/>
+      <c r="A30" s="165"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -8924,7 +10291,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="160"/>
+      <c r="A31" s="165"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -8957,7 +10324,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="160"/>
+      <c r="A32" s="165"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -8990,7 +10357,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="160"/>
+      <c r="A33" s="165"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -9024,8 +10391,8 @@
       </c>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A34" s="160"/>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="165"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -9059,8 +10426,8 @@
       </c>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A35" s="160"/>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="165"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -9092,8 +10459,8 @@
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="160"/>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="165"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -9125,8 +10492,8 @@
       <c r="K36" s="132"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="160"/>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="165"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -9150,8 +10517,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="160"/>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="165"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -9185,8 +10552,8 @@
       </c>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A39" s="160"/>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="165"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -9210,8 +10577,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A40" s="160"/>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="165"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -9235,8 +10602,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A41" s="160"/>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="165"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -9260,8 +10627,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="160"/>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="165"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -9285,8 +10652,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A43" s="160"/>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="165"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -9308,8 +10675,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A44" s="160"/>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="165"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -9331,8 +10698,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A45" s="160"/>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="165"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -9354,8 +10721,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A46" s="160"/>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="165"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -9377,8 +10744,8 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="160"/>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="165"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -9419,44 +10786,44 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DDB050C-EFA5-4BA1-89FF-2BF72F913523}">
   <dimension ref="A3:Q47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="37.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="18.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" ht="28.2" x14ac:dyDescent="0.25">
-      <c r="B3" s="155" t="s">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="160" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="155"/>
-      <c r="K3" s="155"/>
-    </row>
-    <row r="4" spans="1:16" ht="30.6" x14ac:dyDescent="0.25">
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
@@ -9508,7 +10875,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="161" t="s">
+      <c r="A7" s="166" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -9545,7 +10912,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162"/>
+      <c r="A8" s="167"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -9581,7 +10948,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162"/>
+      <c r="A9" s="167"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -9610,7 +10977,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="162"/>
+      <c r="A10" s="167"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -9641,17 +11008,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="164" t="s">
+      <c r="N10" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="164"/>
-      <c r="P10" s="165">
+      <c r="O10" s="169"/>
+      <c r="P10" s="170">
         <f>SUM(F7:F1006)</f>
         <v>35340000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="162"/>
+      <c r="A11" s="167"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -9674,12 +11041,12 @@
       <c r="J11" s="128"/>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164"/>
-      <c r="P11" s="165"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="170"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="162"/>
+      <c r="A12" s="167"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -9704,17 +11071,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="166" t="s">
+      <c r="N12" s="171" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="166"/>
-      <c r="P12" s="165">
+      <c r="O12" s="171"/>
+      <c r="P12" s="170">
         <f>SUM(G7:G1006)</f>
         <v>18504400</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="162"/>
+      <c r="A13" s="167"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -9739,12 +11106,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
-      <c r="P13" s="165"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="170"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162"/>
+      <c r="A14" s="167"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -9769,12 +11136,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="166"/>
-      <c r="O14" s="166"/>
-      <c r="P14" s="165"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="162"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="170"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="167"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -9799,17 +11166,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="167" t="s">
+      <c r="N15" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="167"/>
+      <c r="O15" s="172"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>18210000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="162"/>
+      <c r="A16" s="167"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -9834,7 +11201,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="162"/>
+      <c r="A17" s="167"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -9858,8 +11225,8 @@
       <c r="K17" s="130"/>
       <c r="L17" s="46"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="162"/>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="167"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -9892,8 +11259,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="163"/>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="168"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -9916,7 +11283,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="159" t="s">
+      <c r="A20" s="164" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -9946,7 +11313,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="160"/>
+      <c r="A21" s="165"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -9979,7 +11346,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="160"/>
+      <c r="A22" s="165"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -10014,7 +11381,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="160"/>
+      <c r="A23" s="165"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -10039,7 +11406,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="160"/>
+      <c r="A24" s="165"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -10072,7 +11439,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="160"/>
+      <c r="A25" s="165"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -10104,8 +11471,8 @@
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="160"/>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="165"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -10137,8 +11504,8 @@
       <c r="K26" s="132"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="160"/>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="165"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -10171,7 +11538,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="160"/>
+      <c r="A28" s="165"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -10204,7 +11571,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="160"/>
+      <c r="A29" s="165"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -10237,7 +11604,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="160"/>
+      <c r="A30" s="165"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -10270,7 +11637,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="160"/>
+      <c r="A31" s="165"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -10305,7 +11672,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="160"/>
+      <c r="A32" s="165"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -10338,7 +11705,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="160"/>
+      <c r="A33" s="165"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -10370,8 +11737,8 @@
       <c r="K33" s="89"/>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A34" s="160"/>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="165"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -10403,8 +11770,8 @@
       <c r="K34" s="132"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A35" s="160"/>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="165"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -10436,8 +11803,8 @@
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
-    <row r="36" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="160"/>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="165"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -10469,8 +11836,8 @@
       <c r="K36" s="132"/>
       <c r="L36" s="46"/>
     </row>
-    <row r="37" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="160"/>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="165"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -10494,8 +11861,8 @@
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="160"/>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="165"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -10527,8 +11894,8 @@
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A39" s="160"/>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="165"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -10552,8 +11919,8 @@
       <c r="K39" s="98"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A40" s="160"/>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="165"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -10577,8 +11944,8 @@
       <c r="K40" s="98"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A41" s="160"/>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="165"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -10602,8 +11969,8 @@
       <c r="K41" s="98"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="160"/>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="165"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -10627,8 +11994,8 @@
       <c r="K42" s="98"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A43" s="160"/>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="165"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -10650,8 +12017,8 @@
       <c r="K43" s="98"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A44" s="160"/>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="165"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -10673,8 +12040,8 @@
       <c r="K44" s="98"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A45" s="160"/>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="165"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -10696,8 +12063,8 @@
       <c r="K45" s="98"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A46" s="160"/>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="165"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -10719,8 +12086,2658 @@
       <c r="K46" s="98"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="160"/>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="165"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C751520-0A45-4A23-A6EE-174DE0E24C5F}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="160" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="166" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="41">
+        <v>1700000</v>
+      </c>
+      <c r="G7" s="41">
+        <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
+        <v>1020000</v>
+      </c>
+      <c r="H7" s="41">
+        <v>850000</v>
+      </c>
+      <c r="I7" s="41">
+        <f>G7-H7</f>
+        <v>170000</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="129"/>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="167"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41">
+        <v>2000000</v>
+      </c>
+      <c r="G8" s="41">
+        <f t="shared" ref="G8:G18" si="0">IF(F8="",0,IF(F8&gt;1800000,F8*O$19,F8*O$18))</f>
+        <v>1000000</v>
+      </c>
+      <c r="H8" s="41">
+        <v>1000000</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="1">G8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="130"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="167"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="2">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="122" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="126"/>
+      <c r="I9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="155"/>
+      <c r="K9" s="154" t="s">
+        <v>150</v>
+      </c>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="167"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="44">
+        <v>850000</v>
+      </c>
+      <c r="G10" s="41">
+        <f t="shared" si="0"/>
+        <v>510000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>510000</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="130"/>
+      <c r="L10" s="46"/>
+      <c r="N10" s="169" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="169"/>
+      <c r="P10" s="170">
+        <f>SUM(F7:F1006)</f>
+        <v>35368000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="167"/>
+      <c r="B11" s="38">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="44"/>
+      <c r="I11" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="155"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="170"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="167"/>
+      <c r="B12" s="38">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="155"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="171" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="171"/>
+      <c r="P12" s="170">
+        <f>SUM(G7:G1006)</f>
+        <v>18197000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="167"/>
+      <c r="B13" s="38">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="155"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="170"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="167"/>
+      <c r="B14" s="38">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="170"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="167"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="172" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="172"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>17549000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="167"/>
+      <c r="B16" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="167"/>
+      <c r="B17" s="38">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="167"/>
+      <c r="B18" s="38">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="168"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="164" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="128"/>
+      <c r="K20" s="132" t="s">
+        <v>152</v>
+      </c>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="165"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="79">
+        <v>1320000</v>
+      </c>
+      <c r="G21" s="75">
+        <f t="shared" si="3"/>
+        <v>792000</v>
+      </c>
+      <c r="H21" s="79">
+        <v>660000</v>
+      </c>
+      <c r="I21" s="75">
+        <f t="shared" si="4"/>
+        <v>132000</v>
+      </c>
+      <c r="J21" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K21" s="132">
+        <v>1320</v>
+      </c>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="165"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="79"/>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="K22" s="148">
+        <v>400</v>
+      </c>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="165"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="101"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="103"/>
+      <c r="I23" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="128"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="165"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="75">
+        <v>2730000</v>
+      </c>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>1365000</v>
+      </c>
+      <c r="H24" s="79">
+        <v>1365000</v>
+      </c>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K24" s="132"/>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="165"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="75">
+        <v>1860000</v>
+      </c>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>930000</v>
+      </c>
+      <c r="H25" s="79">
+        <v>930000</v>
+      </c>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K25" s="132"/>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="165"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="75">
+        <v>3325000</v>
+      </c>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>1662500</v>
+      </c>
+      <c r="H26" s="75">
+        <v>1662000</v>
+      </c>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26" s="132"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="165"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="87"/>
+      <c r="E27" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="79">
+        <v>2213000</v>
+      </c>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>1106500</v>
+      </c>
+      <c r="H27" s="75">
+        <v>1106000</v>
+      </c>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K27" s="132"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="165"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="79">
+        <v>1870000</v>
+      </c>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>935000</v>
+      </c>
+      <c r="H28" s="79">
+        <v>935000</v>
+      </c>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K28" s="132"/>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="165"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="118">
+        <v>2700000</v>
+      </c>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>1350000</v>
+      </c>
+      <c r="H29" s="118">
+        <v>1350000</v>
+      </c>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K29" s="132"/>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="165"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="78"/>
+      <c r="E30" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="89">
+        <v>1260000</v>
+      </c>
+      <c r="G30" s="75">
+        <f t="shared" si="3"/>
+        <v>756000</v>
+      </c>
+      <c r="H30" s="119">
+        <v>756000</v>
+      </c>
+      <c r="I30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K30" s="132"/>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="165"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="89">
+        <v>1720000</v>
+      </c>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>860000</v>
+      </c>
+      <c r="H31" s="89">
+        <v>860000</v>
+      </c>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31" s="132"/>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="165"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="156" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="157"/>
+      <c r="E32" s="140" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="139"/>
+      <c r="G32" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="139"/>
+      <c r="I32" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="49"/>
+      <c r="K32" s="132" t="s">
+        <v>151</v>
+      </c>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="165"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="87"/>
+      <c r="E33" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="90">
+        <v>2180000</v>
+      </c>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>1090000</v>
+      </c>
+      <c r="H33" s="89">
+        <v>1090000</v>
+      </c>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K33" s="89"/>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="165"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="79">
+        <v>2180000</v>
+      </c>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>1090000</v>
+      </c>
+      <c r="H34" s="79">
+        <v>1090000</v>
+      </c>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K34" s="132"/>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="165"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="120"/>
+      <c r="E35" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="118">
+        <v>1820000</v>
+      </c>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>910000</v>
+      </c>
+      <c r="H35" s="118">
+        <v>910000</v>
+      </c>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K35" s="132"/>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="165"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="87" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="120"/>
+      <c r="E36" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="118">
+        <v>2750000</v>
+      </c>
+      <c r="G36" s="75">
+        <f t="shared" si="3"/>
+        <v>1375000</v>
+      </c>
+      <c r="H36" s="118">
+        <v>1375000</v>
+      </c>
+      <c r="I36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K36" s="132"/>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="165"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="149"/>
+      <c r="D37" s="150"/>
+      <c r="E37" s="151" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="152"/>
+      <c r="G37" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="153"/>
+      <c r="I37" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="83"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="165"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="43"/>
+      <c r="E38" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="90">
+        <v>2890000</v>
+      </c>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>1445000</v>
+      </c>
+      <c r="H38" s="89">
+        <v>1100000</v>
+      </c>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>345000</v>
+      </c>
+      <c r="J38" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K38" s="98" t="s">
+        <v>153</v>
+      </c>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="165"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="90"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="165"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="90"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="165"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="165"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="165"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="165"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="165"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="165"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="165"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C1EF3A-8A6D-4162-8923-BC641C12C621}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="160" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="166" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="41">
+        <v>1000000</v>
+      </c>
+      <c r="G7" s="41">
+        <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
+        <v>600000</v>
+      </c>
+      <c r="H7" s="41">
+        <v>600000</v>
+      </c>
+      <c r="I7" s="41">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="129" t="s">
+        <v>157</v>
+      </c>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="167"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41">
+        <v>1220000</v>
+      </c>
+      <c r="G8" s="41">
+        <f t="shared" ref="G8:G18" si="0">IF(F8="",0,IF(F8&gt;1800000,F8*O$19,F8*O$18))</f>
+        <v>732000</v>
+      </c>
+      <c r="H8" s="41">
+        <v>610000</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="1">G8-H8</f>
+        <v>122000</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="130"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="167"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="2">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="122"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="126"/>
+      <c r="I9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="159"/>
+      <c r="K9" s="154"/>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="167"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="44">
+        <v>1400000</v>
+      </c>
+      <c r="G10" s="41">
+        <f t="shared" si="0"/>
+        <v>840000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>840000</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="130"/>
+      <c r="L10" s="46"/>
+      <c r="N10" s="169" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="169"/>
+      <c r="P10" s="170">
+        <f>SUM(F7:F1006)</f>
+        <v>33741000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="167"/>
+      <c r="B11" s="38">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="44"/>
+      <c r="I11" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="155"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="170"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="167"/>
+      <c r="B12" s="38">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="155"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="171" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="171"/>
+      <c r="P12" s="170">
+        <f>SUM(G7:G1006)</f>
+        <v>17932800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="167"/>
+      <c r="B13" s="38">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="155"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="170"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="167"/>
+      <c r="B14" s="38">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="170"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="167"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="172" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="172"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>16981000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="167"/>
+      <c r="B16" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="167"/>
+      <c r="B17" s="38">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="167"/>
+      <c r="B18" s="38">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="168"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="164" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="139"/>
+      <c r="I20" s="75">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="128"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="165"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="79">
+        <v>1320000</v>
+      </c>
+      <c r="G21" s="75">
+        <f t="shared" si="3"/>
+        <v>792000</v>
+      </c>
+      <c r="H21" s="79">
+        <v>660000</v>
+      </c>
+      <c r="I21" s="75">
+        <f t="shared" si="4"/>
+        <v>132000</v>
+      </c>
+      <c r="J21" s="62"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="165"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75">
+        <v>1500000</v>
+      </c>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>900000</v>
+      </c>
+      <c r="H22" s="79">
+        <v>900000</v>
+      </c>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" s="158">
+        <v>1500</v>
+      </c>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="165"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="73" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="75">
+        <v>920000</v>
+      </c>
+      <c r="G23" s="75">
+        <f t="shared" si="3"/>
+        <v>552000</v>
+      </c>
+      <c r="H23" s="75">
+        <v>552000</v>
+      </c>
+      <c r="I23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K23" s="132"/>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="165"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="75">
+        <v>2900000</v>
+      </c>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>1450000</v>
+      </c>
+      <c r="H24" s="79">
+        <v>1450000</v>
+      </c>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="128"/>
+      <c r="K24" s="132"/>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="165"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="75">
+        <v>1770000</v>
+      </c>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>885000</v>
+      </c>
+      <c r="H25" s="79">
+        <v>885000</v>
+      </c>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="128"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="165"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="75">
+        <v>2730000</v>
+      </c>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>1365000</v>
+      </c>
+      <c r="H26" s="75">
+        <v>1365000</v>
+      </c>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26" s="132"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="165"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="87"/>
+      <c r="E27" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="79">
+        <v>1363000</v>
+      </c>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>817800</v>
+      </c>
+      <c r="H27" s="75">
+        <v>816000</v>
+      </c>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>1800</v>
+      </c>
+      <c r="J27" s="128"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="165"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="79">
+        <v>740000</v>
+      </c>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>444000</v>
+      </c>
+      <c r="H28" s="79">
+        <v>444000</v>
+      </c>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="128"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="165"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="118">
+        <v>3360000</v>
+      </c>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>1680000</v>
+      </c>
+      <c r="H29" s="118">
+        <v>1680000</v>
+      </c>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="128"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="165"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="78"/>
+      <c r="E30" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="89">
+        <v>1160000</v>
+      </c>
+      <c r="G30" s="75">
+        <f t="shared" si="3"/>
+        <v>696000</v>
+      </c>
+      <c r="H30" s="119"/>
+      <c r="I30" s="75">
+        <f t="shared" si="4"/>
+        <v>696000</v>
+      </c>
+      <c r="J30" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="K30" s="132" t="s">
+        <v>156</v>
+      </c>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="165"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="89">
+        <v>2060000</v>
+      </c>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>1030000</v>
+      </c>
+      <c r="H31" s="89">
+        <v>1030000</v>
+      </c>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="128"/>
+      <c r="K31" s="132"/>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="165"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="156" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="157"/>
+      <c r="E32" s="140" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="139"/>
+      <c r="G32" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="139"/>
+      <c r="I32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="128"/>
+      <c r="K32" s="132"/>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="165"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="87"/>
+      <c r="E33" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="90">
+        <v>1768000</v>
+      </c>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>884000</v>
+      </c>
+      <c r="H33" s="89">
+        <v>884000</v>
+      </c>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="128"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="165"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="79">
+        <v>2030000</v>
+      </c>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>1015000</v>
+      </c>
+      <c r="H34" s="79">
+        <v>1015000</v>
+      </c>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="128"/>
+      <c r="K34" s="132"/>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="165"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="120"/>
+      <c r="E35" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="118">
+        <v>2100000</v>
+      </c>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>1050000</v>
+      </c>
+      <c r="H35" s="118">
+        <v>1050000</v>
+      </c>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="128"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="165"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="87" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="120"/>
+      <c r="E36" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="118">
+        <v>2000000</v>
+      </c>
+      <c r="G36" s="75">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+      <c r="H36" s="118">
+        <v>1000000</v>
+      </c>
+      <c r="I36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="128"/>
+      <c r="K36" s="132"/>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="165"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="142"/>
+      <c r="D37" s="143"/>
+      <c r="E37" s="144" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="145"/>
+      <c r="G37" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="146"/>
+      <c r="I37" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="83"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="165"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="43"/>
+      <c r="E38" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="90">
+        <v>2400000</v>
+      </c>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>1200000</v>
+      </c>
+      <c r="H38" s="89">
+        <v>1200000</v>
+      </c>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="128"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="165"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="90"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="165"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="90"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="165"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="165"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="165"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="165"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="165"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="165"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="165"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>

--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924336F6-BB63-4DF0-B102-2E2CBE591715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67572DA-9B8E-4CC8-8360-D4B3CA4CA7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="168">
   <si>
     <t>STT</t>
   </si>
@@ -513,13 +513,40 @@
     <t>DOANH THU 08/02/2026</t>
   </si>
   <si>
-    <t>đi phà chưa chuyển khoản</t>
-  </si>
-  <si>
     <t>trừ vào tiền cọc xe</t>
   </si>
   <si>
     <t>DOANH THU 09/02/2026</t>
+  </si>
+  <si>
+    <t>đi chơi chưa về</t>
+  </si>
+  <si>
+    <t>Chú QUỲNH</t>
+  </si>
+  <si>
+    <t>xin bác kim nghỉ</t>
+  </si>
+  <si>
+    <t>trúng gió xin nghỉ 1 hôm</t>
+  </si>
+  <si>
+    <t>về quê</t>
+  </si>
+  <si>
+    <t>gửi bảo vệ 100k</t>
+  </si>
+  <si>
+    <t>nghỉ ăn tất niên</t>
+  </si>
+  <si>
+    <t>đang ở hòn thơm chưa về</t>
+  </si>
+  <si>
+    <t>k11425</t>
+  </si>
+  <si>
+    <t>k11327</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1044,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1459,6 +1486,21 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2065,32 +2107,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="160" t="s">
+      <c r="B2" s="165" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="161" t="s">
+      <c r="B3" s="166" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="162"/>
-      <c r="K3" s="162"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="167"/>
+      <c r="I3" s="167"/>
+      <c r="J3" s="167"/>
+      <c r="K3" s="167"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="21"/>
@@ -2748,20 +2790,20 @@
       <c r="F26" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="163" t="s">
+      <c r="H26" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="163"/>
+      <c r="I26" s="168"/>
       <c r="J26" s="5">
         <f>SUM(H7:H1001)</f>
         <v>28869000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="163" t="s">
+      <c r="H27" s="168" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="163"/>
+      <c r="I27" s="168"/>
       <c r="J27" s="5">
         <f>SUM(I7:I1001)</f>
         <v>17311000</v>
@@ -2899,25 +2941,25 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="165" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
       <c r="G4" s="58" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I4" s="59"/>
       <c r="J4" s="59"/>
@@ -2964,46 +3006,44 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="171" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
         <v>1</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="D7" s="40"/>
       <c r="E7" s="60" t="s">
         <v>76</v>
       </c>
       <c r="F7" s="41">
-        <v>1000000</v>
+        <v>350000</v>
       </c>
       <c r="G7" s="41">
         <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
-        <v>600000</v>
+        <v>210000</v>
       </c>
       <c r="H7" s="41">
-        <v>600000</v>
+        <v>175000</v>
       </c>
       <c r="I7" s="41">
         <f>G7-H7</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="129" t="s">
-        <v>157</v>
-      </c>
+        <v>35000</v>
+      </c>
+      <c r="J7" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="129"/>
       <c r="L7" s="46"/>
       <c r="N7" s="50" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167"/>
+      <c r="A8" s="172"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -3016,18 +3056,18 @@
         <v>65</v>
       </c>
       <c r="F8" s="41">
-        <v>1220000</v>
+        <v>1100000</v>
       </c>
       <c r="G8" s="41">
         <f t="shared" ref="G8:G18" si="0">IF(F8="",0,IF(F8&gt;1800000,F8*O$19,F8*O$18))</f>
-        <v>732000</v>
+        <v>660000</v>
       </c>
       <c r="H8" s="41">
-        <v>610000</v>
+        <v>550000</v>
       </c>
       <c r="I8" s="41">
         <f t="shared" ref="I8:I18" si="1">G8-H8</f>
-        <v>122000</v>
+        <v>110000</v>
       </c>
       <c r="J8" s="50" t="s">
         <v>25</v>
@@ -3039,32 +3079,32 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
+      <c r="A9" s="172"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
       </c>
-      <c r="C9" s="122"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="124" t="s">
+      <c r="C9" s="39"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125">
+      <c r="F9" s="41"/>
+      <c r="G9" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="126"/>
-      <c r="I9" s="125">
+      <c r="H9" s="44"/>
+      <c r="I9" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="159"/>
+      <c r="J9" s="155"/>
       <c r="K9" s="154"/>
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167"/>
+      <c r="A10" s="172"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -3077,14 +3117,14 @@
         <v>76</v>
       </c>
       <c r="F10" s="44">
-        <v>1400000</v>
+        <v>1000000</v>
       </c>
       <c r="G10" s="41">
         <f t="shared" si="0"/>
-        <v>840000</v>
+        <v>600000</v>
       </c>
       <c r="H10" s="44">
-        <v>840000</v>
+        <v>600000</v>
       </c>
       <c r="I10" s="41">
         <f t="shared" si="1"/>
@@ -3093,19 +3133,21 @@
       <c r="J10" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="130"/>
+      <c r="K10" s="130" t="s">
+        <v>166</v>
+      </c>
       <c r="L10" s="46"/>
-      <c r="N10" s="169" t="s">
+      <c r="N10" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170">
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
         <f>SUM(F7:F1006)</f>
-        <v>33741000</v>
+        <v>27508000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167"/>
+      <c r="A11" s="172"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -3128,12 +3170,12 @@
       <c r="J11" s="155"/>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="170"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="167"/>
+      <c r="A12" s="172"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -3158,17 +3200,17 @@
       <c r="J12" s="155"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="171" t="s">
+      <c r="N12" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="171"/>
-      <c r="P12" s="170">
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
         <f>SUM(G7:G1006)</f>
-        <v>17932800</v>
+        <v>14257000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167"/>
+      <c r="A13" s="172"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -3193,12 +3235,12 @@
       <c r="J13" s="155"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="170"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
+      <c r="A14" s="172"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -3223,12 +3265,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="170"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="167"/>
+      <c r="A15" s="172"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -3253,17 +3295,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="172" t="s">
+      <c r="N15" s="177" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="172"/>
+      <c r="O15" s="177"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
-        <v>16981000</v>
+        <v>14045000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
+      <c r="A16" s="172"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -3288,7 +3330,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="167"/>
+      <c r="A17" s="172"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -3313,7 +3355,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="167"/>
+      <c r="A18" s="172"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -3347,7 +3389,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="168"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -3370,7 +3412,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="164" t="s">
+      <c r="A20" s="169" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -3398,7 +3440,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="165"/>
+      <c r="A21" s="170"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -3411,60 +3453,56 @@
         <v>105</v>
       </c>
       <c r="F21" s="79">
-        <v>1320000</v>
+        <v>1883000</v>
       </c>
       <c r="G21" s="75">
         <f t="shared" si="3"/>
-        <v>792000</v>
+        <v>941500</v>
       </c>
       <c r="H21" s="79">
-        <v>660000</v>
+        <v>945000</v>
       </c>
       <c r="I21" s="75">
         <f t="shared" si="4"/>
-        <v>132000</v>
-      </c>
-      <c r="J21" s="62"/>
+        <v>-3500</v>
+      </c>
+      <c r="J21" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K21" s="132"/>
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="165"/>
+      <c r="A22" s="170"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
       </c>
-      <c r="C22" s="73" t="s">
+      <c r="C22" s="137" t="s">
         <v>127</v>
       </c>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81" t="s">
+      <c r="D22" s="140"/>
+      <c r="E22" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="75">
-        <v>1500000</v>
-      </c>
-      <c r="G22" s="75">
-        <f t="shared" si="3"/>
-        <v>900000</v>
-      </c>
-      <c r="H22" s="79">
-        <v>900000</v>
-      </c>
+      <c r="F22" s="139"/>
+      <c r="G22" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="160"/>
       <c r="I22" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J22" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="K22" s="158">
-        <v>1500</v>
+      <c r="J22" s="49"/>
+      <c r="K22" s="164" t="s">
+        <v>160</v>
       </c>
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="165"/>
+      <c r="A23" s="170"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -3477,14 +3515,14 @@
         <v>26</v>
       </c>
       <c r="F23" s="75">
-        <v>920000</v>
+        <v>1380000</v>
       </c>
       <c r="G23" s="75">
         <f t="shared" si="3"/>
-        <v>552000</v>
+        <v>828000</v>
       </c>
       <c r="H23" s="75">
-        <v>552000</v>
+        <v>828000</v>
       </c>
       <c r="I23" s="75">
         <f t="shared" si="4"/>
@@ -3497,38 +3535,36 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="165"/>
+      <c r="A24" s="170"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="C24" s="73" t="s">
+      <c r="C24" s="137" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81" t="s">
+      <c r="D24" s="140"/>
+      <c r="E24" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="F24" s="75">
-        <v>2900000</v>
-      </c>
-      <c r="G24" s="75">
-        <f t="shared" si="3"/>
-        <v>1450000</v>
-      </c>
-      <c r="H24" s="79">
-        <v>1450000</v>
-      </c>
+      <c r="F24" s="139"/>
+      <c r="G24" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="160"/>
       <c r="I24" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J24" s="128"/>
-      <c r="K24" s="132"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="132" t="s">
+        <v>161</v>
+      </c>
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="165"/>
+      <c r="A25" s="170"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -3541,25 +3577,27 @@
         <v>104</v>
       </c>
       <c r="F25" s="75">
-        <v>1770000</v>
+        <v>2030000</v>
       </c>
       <c r="G25" s="75">
         <f t="shared" si="3"/>
-        <v>885000</v>
+        <v>1015000</v>
       </c>
       <c r="H25" s="79">
-        <v>885000</v>
+        <v>1030000</v>
       </c>
       <c r="I25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="128"/>
+        <v>-15000</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="165"/>
+      <c r="A26" s="170"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -3571,28 +3609,22 @@
       <c r="E26" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="75">
-        <v>2730000</v>
-      </c>
+      <c r="F26" s="75"/>
       <c r="G26" s="75">
         <f t="shared" si="3"/>
-        <v>1365000</v>
-      </c>
-      <c r="H26" s="75">
-        <v>1365000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H26" s="75"/>
       <c r="I26" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="49" t="s">
-        <v>63</v>
-      </c>
+      <c r="J26" s="49"/>
       <c r="K26" s="132"/>
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="165"/>
+      <c r="A27" s="170"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -3605,25 +3637,27 @@
         <v>76</v>
       </c>
       <c r="F27" s="79">
-        <v>1363000</v>
+        <v>3380000</v>
       </c>
       <c r="G27" s="75">
         <f t="shared" si="3"/>
-        <v>817800</v>
+        <v>1690000</v>
       </c>
       <c r="H27" s="75">
-        <v>816000</v>
+        <v>1690000</v>
       </c>
       <c r="I27" s="75">
         <f t="shared" si="4"/>
-        <v>1800</v>
-      </c>
-      <c r="J27" s="128"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K27" s="132"/>
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="165"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -3636,25 +3670,27 @@
         <v>24</v>
       </c>
       <c r="F28" s="79">
-        <v>740000</v>
+        <v>3310000</v>
       </c>
       <c r="G28" s="75">
         <f t="shared" si="3"/>
-        <v>444000</v>
+        <v>1655000</v>
       </c>
       <c r="H28" s="79">
-        <v>444000</v>
+        <v>1655000</v>
       </c>
       <c r="I28" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J28" s="128"/>
+      <c r="J28" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K28" s="132"/>
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="165"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -3667,58 +3703,56 @@
         <v>106</v>
       </c>
       <c r="F29" s="118">
-        <v>3360000</v>
+        <v>1970000</v>
       </c>
       <c r="G29" s="75">
         <f t="shared" si="3"/>
-        <v>1680000</v>
+        <v>985000</v>
       </c>
       <c r="H29" s="118">
-        <v>1680000</v>
+        <v>1000000</v>
       </c>
       <c r="I29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="128"/>
+        <v>-15000</v>
+      </c>
+      <c r="J29" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K29" s="132"/>
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="165"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="C30" s="88" t="s">
+      <c r="C30" s="161" t="s">
         <v>108</v>
       </c>
-      <c r="D30" s="78"/>
-      <c r="E30" s="81" t="s">
+      <c r="D30" s="162"/>
+      <c r="E30" s="140" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="89">
-        <v>1160000</v>
-      </c>
-      <c r="G30" s="75">
-        <f t="shared" si="3"/>
-        <v>696000</v>
-      </c>
-      <c r="H30" s="119"/>
-      <c r="I30" s="75">
-        <f t="shared" si="4"/>
-        <v>696000</v>
-      </c>
-      <c r="J30" s="48" t="s">
-        <v>64</v>
-      </c>
+      <c r="F30" s="146"/>
+      <c r="G30" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="163"/>
+      <c r="I30" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="49"/>
       <c r="K30" s="132" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="165"/>
+      <c r="A31" s="170"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -3731,25 +3765,29 @@
         <v>16</v>
       </c>
       <c r="F31" s="89">
-        <v>2060000</v>
+        <v>2600000</v>
       </c>
       <c r="G31" s="75">
         <f t="shared" si="3"/>
-        <v>1030000</v>
+        <v>1300000</v>
       </c>
       <c r="H31" s="89">
-        <v>1030000</v>
+        <v>1200000</v>
       </c>
       <c r="I31" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="128"/>
-      <c r="K31" s="132"/>
+        <v>100000</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31" s="132" t="s">
+        <v>163</v>
+      </c>
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="165"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -3771,43 +3809,43 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J32" s="128"/>
-      <c r="K32" s="132"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="132" t="s">
+        <v>165</v>
+      </c>
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="165"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="C33" s="87" t="s">
+      <c r="C33" s="157" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="87"/>
-      <c r="E33" s="81" t="s">
+      <c r="D33" s="157"/>
+      <c r="E33" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="F33" s="90">
-        <v>1768000</v>
-      </c>
-      <c r="G33" s="75">
-        <f t="shared" si="3"/>
-        <v>884000</v>
-      </c>
-      <c r="H33" s="89">
-        <v>884000</v>
-      </c>
+      <c r="F33" s="145"/>
+      <c r="G33" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="146"/>
       <c r="I33" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J33" s="128"/>
-      <c r="K33" s="89"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="89" t="s">
+        <v>164</v>
+      </c>
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="165"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -3820,25 +3858,27 @@
         <v>15</v>
       </c>
       <c r="F34" s="79">
-        <v>2030000</v>
+        <v>2720000</v>
       </c>
       <c r="G34" s="75">
         <f t="shared" si="3"/>
-        <v>1015000</v>
+        <v>1360000</v>
       </c>
       <c r="H34" s="79">
-        <v>1015000</v>
+        <v>1360000</v>
       </c>
       <c r="I34" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J34" s="128"/>
+      <c r="J34" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K34" s="132"/>
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="165"/>
+      <c r="A35" s="170"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -3851,25 +3891,27 @@
         <v>76</v>
       </c>
       <c r="F35" s="118">
-        <v>2100000</v>
+        <v>1850000</v>
       </c>
       <c r="G35" s="75">
         <f t="shared" si="3"/>
-        <v>1050000</v>
+        <v>925000</v>
       </c>
       <c r="H35" s="118">
-        <v>1050000</v>
+        <v>925000</v>
       </c>
       <c r="I35" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J35" s="128"/>
+      <c r="J35" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="165"/>
+      <c r="A36" s="170"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -3882,25 +3924,29 @@
         <v>76</v>
       </c>
       <c r="F36" s="118">
-        <v>2000000</v>
+        <v>1200000</v>
       </c>
       <c r="G36" s="75">
         <f t="shared" si="3"/>
-        <v>1000000</v>
+        <v>720000</v>
       </c>
       <c r="H36" s="118">
-        <v>1000000</v>
+        <v>720000</v>
       </c>
       <c r="I36" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J36" s="128"/>
-      <c r="K36" s="132"/>
+      <c r="J36" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K36" s="132" t="s">
+        <v>167</v>
+      </c>
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="165"/>
+      <c r="A37" s="170"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -3920,12 +3966,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J37" s="83"/>
+      <c r="J37" s="49"/>
       <c r="K37" s="98"/>
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="165"/>
+      <c r="A38" s="170"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -3938,25 +3984,27 @@
         <v>76</v>
       </c>
       <c r="F38" s="90">
-        <v>2400000</v>
+        <v>2735000</v>
       </c>
       <c r="G38" s="75">
         <f t="shared" si="3"/>
-        <v>1200000</v>
+        <v>1367500</v>
       </c>
       <c r="H38" s="89">
-        <v>1200000</v>
+        <v>1367000</v>
       </c>
       <c r="I38" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="128"/>
+        <v>500</v>
+      </c>
+      <c r="J38" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="165"/>
+      <c r="A39" s="170"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -3981,7 +4029,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="165"/>
+      <c r="A40" s="170"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -4006,7 +4054,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="165"/>
+      <c r="A41" s="170"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -4031,7 +4079,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="165"/>
+      <c r="A42" s="170"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -4056,7 +4104,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="165"/>
+      <c r="A43" s="170"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -4079,7 +4127,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="165"/>
+      <c r="A44" s="170"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -4102,7 +4150,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="165"/>
+      <c r="A45" s="170"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -4125,7 +4173,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="165"/>
+      <c r="A46" s="170"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -4148,7 +4196,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="165"/>
+      <c r="A47" s="170"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -4213,18 +4261,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="165" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -4278,7 +4326,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="171" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -4315,7 +4363,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167"/>
+      <c r="A8" s="172"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -4351,7 +4399,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
+      <c r="A9" s="172"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -4383,7 +4431,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167"/>
+      <c r="A10" s="172"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -4414,17 +4462,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="169" t="s">
+      <c r="N10" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170">
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
         <f>SUM(F7:F1006)</f>
         <v>16675000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167"/>
+      <c r="A11" s="172"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -4455,12 +4503,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="170"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="167"/>
+      <c r="A12" s="172"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -4485,17 +4533,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="171" t="s">
+      <c r="N12" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="171"/>
-      <c r="P12" s="170">
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
         <f>SUM(G7:G1006)</f>
         <v>9346000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167"/>
+      <c r="A13" s="172"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -4520,12 +4568,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="170"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
+      <c r="A14" s="172"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -4550,12 +4598,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="170"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="167"/>
+      <c r="A15" s="172"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -4580,17 +4628,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="172" t="s">
+      <c r="N15" s="177" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="172"/>
+      <c r="O15" s="177"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>9285000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
+      <c r="A16" s="172"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -4617,7 +4665,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="167"/>
+      <c r="A17" s="172"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -4644,7 +4692,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="167"/>
+      <c r="A18" s="172"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -4680,7 +4728,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="168"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -4703,7 +4751,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="164" t="s">
+      <c r="A20" s="169" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -4735,7 +4783,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="165"/>
+      <c r="A21" s="170"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -4768,7 +4816,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="165"/>
+      <c r="A22" s="170"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="6">B21+1</f>
         <v>3</v>
@@ -4799,7 +4847,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="165"/>
+      <c r="A23" s="170"/>
       <c r="B23" s="38">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -4822,7 +4870,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="165"/>
+      <c r="A24" s="170"/>
       <c r="B24" s="38">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -4853,7 +4901,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="165"/>
+      <c r="A25" s="170"/>
       <c r="B25" s="38">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -4886,7 +4934,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="165"/>
+      <c r="A26" s="170"/>
       <c r="B26" s="38">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -4917,7 +4965,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="165"/>
+      <c r="A27" s="170"/>
       <c r="B27" s="38">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -4950,7 +4998,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="165"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="38">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -4983,7 +5031,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="165"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="38">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -5006,7 +5054,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="165"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="38">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -5037,7 +5085,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="165"/>
+      <c r="A31" s="170"/>
       <c r="B31" s="38">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -5070,7 +5118,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="165"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="38">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -5103,7 +5151,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="165"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="38">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -5130,7 +5178,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="165"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="38">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -5163,7 +5211,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="165"/>
+      <c r="A35" s="170"/>
       <c r="B35" s="38">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -5194,7 +5242,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="165"/>
+      <c r="A36" s="170"/>
       <c r="B36" s="38">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -5227,7 +5275,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="165"/>
+      <c r="A37" s="170"/>
       <c r="B37" s="38">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -5250,7 +5298,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="165"/>
+      <c r="A38" s="170"/>
       <c r="B38" s="38">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -5273,7 +5321,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="165"/>
+      <c r="A39" s="170"/>
       <c r="B39" s="38">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -5296,7 +5344,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="165"/>
+      <c r="A40" s="170"/>
       <c r="B40" s="38">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -5319,7 +5367,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="165"/>
+      <c r="A41" s="170"/>
       <c r="B41" s="38">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -5342,7 +5390,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="165"/>
+      <c r="A42" s="170"/>
       <c r="B42" s="38">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -5365,7 +5413,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="165"/>
+      <c r="A43" s="170"/>
       <c r="B43" s="38">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -5388,7 +5436,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="165"/>
+      <c r="A44" s="170"/>
       <c r="B44" s="38">
         <f t="shared" si="6"/>
         <v>25</v>
@@ -5411,7 +5459,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="165"/>
+      <c r="A45" s="170"/>
       <c r="B45" s="38">
         <f t="shared" si="6"/>
         <v>26</v>
@@ -5434,7 +5482,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="165"/>
+      <c r="A46" s="170"/>
       <c r="B46" s="38">
         <f t="shared" si="6"/>
         <v>27</v>
@@ -5457,7 +5505,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="165"/>
+      <c r="A47" s="170"/>
       <c r="B47" s="38">
         <f t="shared" si="6"/>
         <v>28</v>
@@ -5523,18 +5571,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="165" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -5588,7 +5636,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="171" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -5625,7 +5673,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167"/>
+      <c r="A8" s="172"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -5661,7 +5709,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
+      <c r="A9" s="172"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -5694,7 +5742,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167"/>
+      <c r="A10" s="172"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -5725,17 +5773,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="169" t="s">
+      <c r="N10" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170">
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
         <f>SUM(F7:F1006)</f>
         <v>30573000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167"/>
+      <c r="A11" s="172"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -5766,12 +5814,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="170"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="167"/>
+      <c r="A12" s="172"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -5796,17 +5844,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="171" t="s">
+      <c r="N12" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="171"/>
-      <c r="P12" s="170">
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
         <f>SUM(G7:G1006)</f>
         <v>16022500</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167"/>
+      <c r="A13" s="172"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -5831,12 +5879,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="170"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
+      <c r="A14" s="172"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -5861,12 +5909,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="170"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="167"/>
+      <c r="A15" s="172"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -5891,17 +5939,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="172" t="s">
+      <c r="N15" s="177" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="172"/>
+      <c r="O15" s="177"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>15420500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
+      <c r="A16" s="172"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -5928,7 +5976,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="167"/>
+      <c r="A17" s="172"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -5955,7 +6003,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="167"/>
+      <c r="A18" s="172"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -5991,7 +6039,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="168"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -6014,7 +6062,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="164" t="s">
+      <c r="A20" s="169" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -6048,7 +6096,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="165"/>
+      <c r="A21" s="170"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -6081,7 +6129,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="165"/>
+      <c r="A22" s="170"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -6114,7 +6162,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="165"/>
+      <c r="A23" s="170"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -6137,7 +6185,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="165"/>
+      <c r="A24" s="170"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -6170,7 +6218,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="165"/>
+      <c r="A25" s="170"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -6203,7 +6251,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="165"/>
+      <c r="A26" s="170"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -6236,7 +6284,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="165"/>
+      <c r="A27" s="170"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -6269,7 +6317,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="165"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -6302,7 +6350,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="165"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -6325,7 +6373,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="165"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -6358,7 +6406,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="165"/>
+      <c r="A31" s="170"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -6391,7 +6439,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="165"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -6424,7 +6472,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="165"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -6449,7 +6497,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="165"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -6482,7 +6530,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="165"/>
+      <c r="A35" s="170"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -6515,7 +6563,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="165"/>
+      <c r="A36" s="170"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -6548,7 +6596,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="165"/>
+      <c r="A37" s="170"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -6571,7 +6619,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="165"/>
+      <c r="A38" s="170"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -6594,7 +6642,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="165"/>
+      <c r="A39" s="170"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -6617,7 +6665,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="165"/>
+      <c r="A40" s="170"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -6640,7 +6688,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="165"/>
+      <c r="A41" s="170"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -6663,7 +6711,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="165"/>
+      <c r="A42" s="170"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -6686,7 +6734,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="165"/>
+      <c r="A43" s="170"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -6709,7 +6757,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="165"/>
+      <c r="A44" s="170"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -6732,7 +6780,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="165"/>
+      <c r="A45" s="170"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -6755,7 +6803,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="165"/>
+      <c r="A46" s="170"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -6778,7 +6826,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="165"/>
+      <c r="A47" s="170"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -6844,18 +6892,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="165" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -6909,7 +6957,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="171" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -6946,7 +6994,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167"/>
+      <c r="A8" s="172"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -6982,7 +7030,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
+      <c r="A9" s="172"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="1">B8+1</f>
         <v>3</v>
@@ -7011,7 +7059,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167"/>
+      <c r="A10" s="172"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -7042,17 +7090,17 @@
       </c>
       <c r="K10" s="96"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="169" t="s">
+      <c r="N10" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170">
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
         <f>SUM(F7:F1006)</f>
         <v>3545000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167"/>
+      <c r="A11" s="172"/>
       <c r="B11" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -7083,12 +7131,12 @@
       </c>
       <c r="K11" s="96"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="170"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="167"/>
+      <c r="A12" s="172"/>
       <c r="B12" s="38">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -7113,17 +7161,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="96"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="171" t="s">
+      <c r="N12" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="171"/>
-      <c r="P12" s="170">
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
         <f>SUM(G7:G1006)</f>
         <v>2127000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167"/>
+      <c r="A13" s="172"/>
       <c r="B13" s="38">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -7148,12 +7196,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="96"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="170"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
+      <c r="A14" s="172"/>
       <c r="B14" s="38">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -7178,12 +7226,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="96"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="170"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="167"/>
+      <c r="A15" s="172"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -7208,17 +7256,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="96"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="172" t="s">
+      <c r="N15" s="177" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="172"/>
+      <c r="O15" s="177"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>2010000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
+      <c r="A16" s="172"/>
       <c r="B16" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -7245,7 +7293,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="167"/>
+      <c r="A17" s="172"/>
       <c r="B17" s="38">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -7272,7 +7320,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="167"/>
+      <c r="A18" s="172"/>
       <c r="B18" s="38">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -7308,7 +7356,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="168"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -7331,7 +7379,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="164" t="s">
+      <c r="A20" s="169" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -7361,7 +7409,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="165"/>
+      <c r="A21" s="170"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -7390,7 +7438,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="165"/>
+      <c r="A22" s="170"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -7419,7 +7467,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="165"/>
+      <c r="A23" s="170"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -7444,7 +7492,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="165"/>
+      <c r="A24" s="170"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -7473,7 +7521,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="165"/>
+      <c r="A25" s="170"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -7502,7 +7550,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="165"/>
+      <c r="A26" s="170"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -7531,7 +7579,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="165"/>
+      <c r="A27" s="170"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -7560,7 +7608,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="165"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -7589,7 +7637,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="165"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -7614,7 +7662,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="165"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -7643,7 +7691,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="165"/>
+      <c r="A31" s="170"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -7672,7 +7720,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="165"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -7701,7 +7749,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="165"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -7728,7 +7776,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="165"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -7757,7 +7805,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="165"/>
+      <c r="A35" s="170"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -7786,7 +7834,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="165"/>
+      <c r="A36" s="170"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -7815,7 +7863,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="165"/>
+      <c r="A37" s="170"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -7838,7 +7886,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="165"/>
+      <c r="A38" s="170"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -7861,7 +7909,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="165"/>
+      <c r="A39" s="170"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -7884,7 +7932,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="165"/>
+      <c r="A40" s="170"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -7907,7 +7955,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="165"/>
+      <c r="A41" s="170"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -7930,7 +7978,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="165"/>
+      <c r="A42" s="170"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -7953,7 +8001,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="165"/>
+      <c r="A43" s="170"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -7976,7 +8024,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="165"/>
+      <c r="A44" s="170"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -7999,7 +8047,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="165"/>
+      <c r="A45" s="170"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -8022,7 +8070,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="165"/>
+      <c r="A46" s="170"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -8045,7 +8093,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="165"/>
+      <c r="A47" s="170"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -8111,18 +8159,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="165" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -8176,7 +8224,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="171" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -8213,7 +8261,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167"/>
+      <c r="A8" s="172"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -8241,7 +8289,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
+      <c r="A9" s="172"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -8270,7 +8318,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167"/>
+      <c r="A10" s="172"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -8301,17 +8349,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="169" t="s">
+      <c r="N10" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170">
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
         <f>SUM(F7:F1006)</f>
         <v>40751000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167"/>
+      <c r="A11" s="172"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -8342,12 +8390,12 @@
       </c>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="170"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="167"/>
+      <c r="A12" s="172"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -8372,17 +8420,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="171" t="s">
+      <c r="N12" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="171"/>
-      <c r="P12" s="170">
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
         <f>SUM(G7:G1006)</f>
         <v>20907500</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167"/>
+      <c r="A13" s="172"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -8407,12 +8455,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="170"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
+      <c r="A14" s="172"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -8437,12 +8485,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="170"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="167"/>
+      <c r="A15" s="172"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -8467,17 +8515,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="172" t="s">
+      <c r="N15" s="177" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="172"/>
+      <c r="O15" s="177"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>21280000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
+      <c r="A16" s="172"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -8502,7 +8550,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="167"/>
+      <c r="A17" s="172"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -8527,7 +8575,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="167"/>
+      <c r="A18" s="172"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -8561,7 +8609,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="168"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -8584,7 +8632,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="164" t="s">
+      <c r="A20" s="169" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -8618,7 +8666,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="165"/>
+      <c r="A21" s="170"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -8647,7 +8695,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="165"/>
+      <c r="A22" s="170"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -8680,7 +8728,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="165"/>
+      <c r="A23" s="170"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -8713,7 +8761,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="165"/>
+      <c r="A24" s="170"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -8746,7 +8794,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="165"/>
+      <c r="A25" s="170"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -8779,7 +8827,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="165"/>
+      <c r="A26" s="170"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -8812,7 +8860,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="165"/>
+      <c r="A27" s="170"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -8845,7 +8893,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="165"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -8880,7 +8928,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="165"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -8915,7 +8963,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="165"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -8948,7 +8996,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="165"/>
+      <c r="A31" s="170"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -8981,7 +9029,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="165"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -9014,7 +9062,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="165"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -9049,7 +9097,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="165"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -9084,7 +9132,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="165"/>
+      <c r="A35" s="170"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -9117,7 +9165,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="165"/>
+      <c r="A36" s="170"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -9150,7 +9198,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="165"/>
+      <c r="A37" s="170"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -9177,7 +9225,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="165"/>
+      <c r="A38" s="170"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -9204,7 +9252,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="165"/>
+      <c r="A39" s="170"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -9229,7 +9277,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="165"/>
+      <c r="A40" s="170"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -9254,7 +9302,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="165"/>
+      <c r="A41" s="170"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -9279,7 +9327,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="165"/>
+      <c r="A42" s="170"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -9304,7 +9352,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="165"/>
+      <c r="A43" s="170"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -9327,7 +9375,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="165"/>
+      <c r="A44" s="170"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -9350,7 +9398,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="165"/>
+      <c r="A45" s="170"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -9373,7 +9421,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="165"/>
+      <c r="A46" s="170"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -9396,7 +9444,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="165"/>
+      <c r="A47" s="170"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -9462,18 +9510,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="165" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -9527,7 +9575,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="171" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -9564,7 +9612,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167"/>
+      <c r="A8" s="172"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -9600,7 +9648,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
+      <c r="A9" s="172"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -9627,7 +9675,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167"/>
+      <c r="A10" s="172"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -9658,17 +9706,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="169" t="s">
+      <c r="N10" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170">
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
         <f>SUM(F7:F1006)</f>
         <v>32460000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167"/>
+      <c r="A11" s="172"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -9691,12 +9739,12 @@
       <c r="J11" s="128"/>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="170"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="167"/>
+      <c r="A12" s="172"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -9721,17 +9769,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="171" t="s">
+      <c r="N12" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="171"/>
-      <c r="P12" s="170">
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
         <f>SUM(G7:G1006)</f>
         <v>17157000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167"/>
+      <c r="A13" s="172"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -9756,12 +9804,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="170"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
+      <c r="A14" s="172"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -9786,12 +9834,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="170"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="167"/>
+      <c r="A15" s="172"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -9816,17 +9864,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="172" t="s">
+      <c r="N15" s="177" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="172"/>
+      <c r="O15" s="177"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>16778500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
+      <c r="A16" s="172"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -9851,7 +9899,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="167"/>
+      <c r="A17" s="172"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -9876,7 +9924,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="167"/>
+      <c r="A18" s="172"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -9910,7 +9958,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="168"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -9933,7 +9981,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="164" t="s">
+      <c r="A20" s="169" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -9963,7 +10011,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="165"/>
+      <c r="A21" s="170"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -9996,7 +10044,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="165"/>
+      <c r="A22" s="170"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -10031,7 +10079,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="165"/>
+      <c r="A23" s="170"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -10060,7 +10108,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="165"/>
+      <c r="A24" s="170"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -10093,7 +10141,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="165"/>
+      <c r="A25" s="170"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -10126,7 +10174,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="165"/>
+      <c r="A26" s="170"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -10159,7 +10207,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="165"/>
+      <c r="A27" s="170"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -10192,7 +10240,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="165"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -10225,7 +10273,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="165"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -10258,7 +10306,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="165"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -10291,7 +10339,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="165"/>
+      <c r="A31" s="170"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -10324,7 +10372,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="165"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -10357,7 +10405,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="165"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -10392,7 +10440,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="165"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -10427,7 +10475,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="165"/>
+      <c r="A35" s="170"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -10460,7 +10508,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="165"/>
+      <c r="A36" s="170"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -10493,7 +10541,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="165"/>
+      <c r="A37" s="170"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -10518,7 +10566,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="165"/>
+      <c r="A38" s="170"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -10553,7 +10601,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="165"/>
+      <c r="A39" s="170"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -10578,7 +10626,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="165"/>
+      <c r="A40" s="170"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -10603,7 +10651,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="165"/>
+      <c r="A41" s="170"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -10628,7 +10676,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="165"/>
+      <c r="A42" s="170"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -10653,7 +10701,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="165"/>
+      <c r="A43" s="170"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -10676,7 +10724,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="165"/>
+      <c r="A44" s="170"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -10699,7 +10747,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="165"/>
+      <c r="A45" s="170"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -10722,7 +10770,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="165"/>
+      <c r="A46" s="170"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -10745,7 +10793,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="165"/>
+      <c r="A47" s="170"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -10810,18 +10858,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="165" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -10875,7 +10923,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="171" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -10912,7 +10960,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167"/>
+      <c r="A8" s="172"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -10948,7 +10996,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
+      <c r="A9" s="172"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -10977,7 +11025,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167"/>
+      <c r="A10" s="172"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -11008,17 +11056,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="169" t="s">
+      <c r="N10" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170">
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
         <f>SUM(F7:F1006)</f>
         <v>35340000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167"/>
+      <c r="A11" s="172"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -11041,12 +11089,12 @@
       <c r="J11" s="128"/>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="170"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="167"/>
+      <c r="A12" s="172"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -11071,17 +11119,17 @@
       <c r="J12" s="62"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="171" t="s">
+      <c r="N12" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="171"/>
-      <c r="P12" s="170">
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
         <f>SUM(G7:G1006)</f>
         <v>18504400</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167"/>
+      <c r="A13" s="172"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -11106,12 +11154,12 @@
       <c r="J13" s="62"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="170"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
+      <c r="A14" s="172"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -11136,12 +11184,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="170"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="167"/>
+      <c r="A15" s="172"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -11166,17 +11214,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="172" t="s">
+      <c r="N15" s="177" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="172"/>
+      <c r="O15" s="177"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>18210000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
+      <c r="A16" s="172"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -11201,7 +11249,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="167"/>
+      <c r="A17" s="172"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -11226,7 +11274,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="167"/>
+      <c r="A18" s="172"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -11260,7 +11308,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="168"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -11283,7 +11331,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="164" t="s">
+      <c r="A20" s="169" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -11313,7 +11361,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="165"/>
+      <c r="A21" s="170"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -11346,7 +11394,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="165"/>
+      <c r="A22" s="170"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -11381,7 +11429,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="165"/>
+      <c r="A23" s="170"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -11406,7 +11454,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="165"/>
+      <c r="A24" s="170"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -11439,7 +11487,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="165"/>
+      <c r="A25" s="170"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -11472,7 +11520,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="165"/>
+      <c r="A26" s="170"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -11505,7 +11553,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="165"/>
+      <c r="A27" s="170"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -11538,7 +11586,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="165"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -11571,7 +11619,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="165"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -11604,7 +11652,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="165"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -11637,7 +11685,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="165"/>
+      <c r="A31" s="170"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -11672,7 +11720,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="165"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -11705,7 +11753,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="165"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -11738,7 +11786,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="165"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -11771,7 +11819,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="165"/>
+      <c r="A35" s="170"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -11804,7 +11852,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="165"/>
+      <c r="A36" s="170"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -11837,7 +11885,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="165"/>
+      <c r="A37" s="170"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -11862,7 +11910,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="165"/>
+      <c r="A38" s="170"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -11895,7 +11943,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="165"/>
+      <c r="A39" s="170"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -11920,7 +11968,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="165"/>
+      <c r="A40" s="170"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -11945,7 +11993,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="165"/>
+      <c r="A41" s="170"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -11970,7 +12018,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="165"/>
+      <c r="A42" s="170"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -11995,7 +12043,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="165"/>
+      <c r="A43" s="170"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -12018,7 +12066,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="165"/>
+      <c r="A44" s="170"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -12041,7 +12089,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="165"/>
+      <c r="A45" s="170"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -12064,7 +12112,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="165"/>
+      <c r="A46" s="170"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -12087,7 +12135,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="165"/>
+      <c r="A47" s="170"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -12152,18 +12200,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="165" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -12217,7 +12265,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="171" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -12254,7 +12302,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167"/>
+      <c r="A8" s="172"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -12290,7 +12338,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
+      <c r="A9" s="172"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -12319,7 +12367,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167"/>
+      <c r="A10" s="172"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -12350,17 +12398,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="169" t="s">
+      <c r="N10" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170">
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
         <f>SUM(F7:F1006)</f>
         <v>35368000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167"/>
+      <c r="A11" s="172"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -12383,12 +12431,12 @@
       <c r="J11" s="155"/>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="170"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="167"/>
+      <c r="A12" s="172"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -12413,17 +12461,17 @@
       <c r="J12" s="155"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="171" t="s">
+      <c r="N12" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="171"/>
-      <c r="P12" s="170">
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
         <f>SUM(G7:G1006)</f>
         <v>18197000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167"/>
+      <c r="A13" s="172"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -12448,12 +12496,12 @@
       <c r="J13" s="155"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="170"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
+      <c r="A14" s="172"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -12478,12 +12526,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="170"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="167"/>
+      <c r="A15" s="172"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -12508,17 +12556,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="172" t="s">
+      <c r="N15" s="177" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="172"/>
+      <c r="O15" s="177"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
         <v>17549000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
+      <c r="A16" s="172"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -12543,7 +12591,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="167"/>
+      <c r="A17" s="172"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -12568,7 +12616,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="167"/>
+      <c r="A18" s="172"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -12602,7 +12650,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="168"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -12625,7 +12673,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="164" t="s">
+      <c r="A20" s="169" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -12655,7 +12703,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="165"/>
+      <c r="A21" s="170"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -12690,7 +12738,7 @@
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="165"/>
+      <c r="A22" s="170"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -12721,7 +12769,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="165"/>
+      <c r="A23" s="170"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -12746,7 +12794,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="165"/>
+      <c r="A24" s="170"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -12779,7 +12827,7 @@
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="165"/>
+      <c r="A25" s="170"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -12812,7 +12860,7 @@
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="165"/>
+      <c r="A26" s="170"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -12845,7 +12893,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="165"/>
+      <c r="A27" s="170"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -12878,7 +12926,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="165"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -12911,7 +12959,7 @@
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="165"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -12944,7 +12992,7 @@
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="165"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -12977,7 +13025,7 @@
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="165"/>
+      <c r="A31" s="170"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -13010,7 +13058,7 @@
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="165"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -13039,7 +13087,7 @@
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="165"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -13072,7 +13120,7 @@
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="165"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -13105,7 +13153,7 @@
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="165"/>
+      <c r="A35" s="170"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -13138,7 +13186,7 @@
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="165"/>
+      <c r="A36" s="170"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -13171,7 +13219,7 @@
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="165"/>
+      <c r="A37" s="170"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -13196,7 +13244,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="165"/>
+      <c r="A38" s="170"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -13231,7 +13279,7 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="165"/>
+      <c r="A39" s="170"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -13256,7 +13304,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="165"/>
+      <c r="A40" s="170"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -13281,7 +13329,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="165"/>
+      <c r="A41" s="170"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -13306,7 +13354,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="165"/>
+      <c r="A42" s="170"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -13331,7 +13379,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="165"/>
+      <c r="A43" s="170"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -13354,7 +13402,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="165"/>
+      <c r="A44" s="170"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -13377,7 +13425,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="165"/>
+      <c r="A45" s="170"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -13400,7 +13448,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="165"/>
+      <c r="A46" s="170"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -13423,7 +13471,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="165"/>
+      <c r="A47" s="170"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -13488,18 +13536,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="165" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="59"/>
@@ -13553,7 +13601,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="171" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="38">
@@ -13584,7 +13632,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="129" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L7" s="46"/>
       <c r="N7" s="50" t="s">
@@ -13592,7 +13640,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167"/>
+      <c r="A8" s="172"/>
       <c r="B8" s="38">
         <f>B7+1</f>
         <v>2</v>
@@ -13628,7 +13676,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
+      <c r="A9" s="172"/>
       <c r="B9" s="38">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>3</v>
@@ -13653,7 +13701,7 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167"/>
+      <c r="A10" s="172"/>
       <c r="B10" s="38">
         <f>B9+1</f>
         <v>4</v>
@@ -13684,17 +13732,17 @@
       </c>
       <c r="K10" s="130"/>
       <c r="L10" s="46"/>
-      <c r="N10" s="169" t="s">
+      <c r="N10" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170">
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
         <f>SUM(F7:F1006)</f>
         <v>33741000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167"/>
+      <c r="A11" s="172"/>
       <c r="B11" s="38">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -13717,12 +13765,12 @@
       <c r="J11" s="155"/>
       <c r="K11" s="130"/>
       <c r="L11" s="46"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="170"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="167"/>
+      <c r="A12" s="172"/>
       <c r="B12" s="38">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -13747,17 +13795,17 @@
       <c r="J12" s="155"/>
       <c r="K12" s="130"/>
       <c r="L12" s="46"/>
-      <c r="N12" s="171" t="s">
+      <c r="N12" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="171"/>
-      <c r="P12" s="170">
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
         <f>SUM(G7:G1006)</f>
         <v>17932800</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167"/>
+      <c r="A13" s="172"/>
       <c r="B13" s="38">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -13782,12 +13830,12 @@
       <c r="J13" s="155"/>
       <c r="K13" s="130"/>
       <c r="L13" s="46"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="170"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
+      <c r="A14" s="172"/>
       <c r="B14" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -13812,12 +13860,12 @@
       <c r="J14" s="62"/>
       <c r="K14" s="130"/>
       <c r="L14" s="46"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="170"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="167"/>
+      <c r="A15" s="172"/>
       <c r="B15" s="38">
         <f>B14+1</f>
         <v>9</v>
@@ -13842,17 +13890,17 @@
       <c r="J15" s="62"/>
       <c r="K15" s="130"/>
       <c r="L15" s="46"/>
-      <c r="N15" s="172" t="s">
+      <c r="N15" s="177" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="172"/>
+      <c r="O15" s="177"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
-        <v>16981000</v>
+        <v>17677000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
+      <c r="A16" s="172"/>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -13877,7 +13925,7 @@
       <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="167"/>
+      <c r="A17" s="172"/>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -13902,7 +13950,7 @@
       <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="167"/>
+      <c r="A18" s="172"/>
       <c r="B18" s="38">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -13936,7 +13984,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="168"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="51"/>
@@ -13959,7 +14007,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="164" t="s">
+      <c r="A20" s="169" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="38">
@@ -13987,7 +14035,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="165"/>
+      <c r="A21" s="170"/>
       <c r="B21" s="38">
         <f>B20+1</f>
         <v>2</v>
@@ -14013,12 +14061,14 @@
         <f t="shared" si="4"/>
         <v>132000</v>
       </c>
-      <c r="J21" s="62"/>
+      <c r="J21" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K21" s="132"/>
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="165"/>
+      <c r="A22" s="170"/>
       <c r="B22" s="38">
         <f t="shared" ref="B22:B47" si="5">B21+1</f>
         <v>3</v>
@@ -14053,7 +14103,7 @@
       <c r="L22" s="82"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="165"/>
+      <c r="A23" s="170"/>
       <c r="B23" s="38">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -14086,7 +14136,7 @@
       <c r="L23" s="76"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="165"/>
+      <c r="A24" s="170"/>
       <c r="B24" s="38">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -14112,12 +14162,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J24" s="128"/>
+      <c r="J24" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K24" s="132"/>
       <c r="L24" s="82"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="165"/>
+      <c r="A25" s="170"/>
       <c r="B25" s="38">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -14143,12 +14195,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J25" s="128"/>
+      <c r="J25" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K25" s="132"/>
       <c r="L25" s="76"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="165"/>
+      <c r="A26" s="170"/>
       <c r="B26" s="38">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -14181,7 +14235,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="165"/>
+      <c r="A27" s="170"/>
       <c r="B27" s="38">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -14207,12 +14261,14 @@
         <f t="shared" si="4"/>
         <v>1800</v>
       </c>
-      <c r="J27" s="128"/>
+      <c r="J27" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K27" s="132"/>
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="165"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="38">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -14238,12 +14294,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J28" s="128"/>
+      <c r="J28" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K28" s="132"/>
       <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="165"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="38">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -14269,12 +14327,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J29" s="128"/>
+      <c r="J29" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K29" s="132"/>
       <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="165"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="38">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -14293,21 +14353,21 @@
         <f t="shared" si="3"/>
         <v>696000</v>
       </c>
-      <c r="H30" s="119"/>
+      <c r="H30" s="119">
+        <v>696000</v>
+      </c>
       <c r="I30" s="75">
         <f t="shared" si="4"/>
-        <v>696000</v>
-      </c>
-      <c r="J30" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="K30" s="132" t="s">
-        <v>156</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J30" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K30" s="132"/>
       <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="165"/>
+      <c r="A31" s="170"/>
       <c r="B31" s="38">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -14333,12 +14393,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J31" s="128"/>
+      <c r="J31" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K31" s="132"/>
       <c r="L31" s="93"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="165"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="38">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -14361,11 +14423,13 @@
         <v>0</v>
       </c>
       <c r="J32" s="128"/>
-      <c r="K32" s="132"/>
+      <c r="K32" s="132" t="s">
+        <v>158</v>
+      </c>
       <c r="L32" s="93"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="165"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="38">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -14391,12 +14455,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J33" s="128"/>
+      <c r="J33" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K33" s="89"/>
       <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="165"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="38">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -14422,12 +14488,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J34" s="128"/>
+      <c r="J34" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K34" s="132"/>
       <c r="L34" s="76"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="165"/>
+      <c r="A35" s="170"/>
       <c r="B35" s="38">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -14453,12 +14521,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J35" s="128"/>
+      <c r="J35" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K35" s="132"/>
       <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="165"/>
+      <c r="A36" s="170"/>
       <c r="B36" s="38">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -14484,12 +14554,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J36" s="128"/>
+      <c r="J36" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K36" s="132"/>
       <c r="L36" s="46"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="165"/>
+      <c r="A37" s="170"/>
       <c r="B37" s="38">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -14514,7 +14586,7 @@
       <c r="L37" s="47"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="165"/>
+      <c r="A38" s="170"/>
       <c r="B38" s="38">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -14540,12 +14612,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J38" s="128"/>
+      <c r="J38" s="49" t="s">
+        <v>63</v>
+      </c>
       <c r="K38" s="98"/>
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="165"/>
+      <c r="A39" s="170"/>
       <c r="B39" s="38">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -14570,7 +14644,7 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="165"/>
+      <c r="A40" s="170"/>
       <c r="B40" s="38">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -14595,7 +14669,7 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="165"/>
+      <c r="A41" s="170"/>
       <c r="B41" s="38">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -14620,7 +14694,7 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="165"/>
+      <c r="A42" s="170"/>
       <c r="B42" s="38">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -14645,7 +14719,7 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="165"/>
+      <c r="A43" s="170"/>
       <c r="B43" s="38">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -14668,7 +14742,7 @@
       <c r="L43" s="47"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="165"/>
+      <c r="A44" s="170"/>
       <c r="B44" s="38">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -14691,7 +14765,7 @@
       <c r="L44" s="47"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="165"/>
+      <c r="A45" s="170"/>
       <c r="B45" s="38">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -14714,7 +14788,7 @@
       <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="165"/>
+      <c r="A46" s="170"/>
       <c r="B46" s="38">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -14737,7 +14811,7 @@
       <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="165"/>
+      <c r="A47" s="170"/>
       <c r="B47" s="38">
         <f t="shared" si="5"/>
         <v>28</v>

--- a/Theo dõi/T2 2026.xlsx
+++ b/Theo dõi/T2 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67572DA-9B8E-4CC8-8360-D4B3CA4CA7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828F5582-67C0-4ADA-906E-D406FFC9D2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10-01" sheetId="14" state="hidden" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <sheet name="07-02" sheetId="43" r:id="rId8"/>
     <sheet name="08-02" sheetId="44" r:id="rId9"/>
     <sheet name="09-02" sheetId="45" r:id="rId10"/>
+    <sheet name="10-02" sheetId="47" r:id="rId11"/>
+    <sheet name="11-02" sheetId="46" r:id="rId12"/>
+    <sheet name="12-02" sheetId="48" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="177">
   <si>
     <t>STT</t>
   </si>
@@ -548,6 +551,33 @@
   <si>
     <t>k11327</t>
   </si>
+  <si>
+    <t>LÊ THÀNH LẬP</t>
+  </si>
+  <si>
+    <t>XIN NGHỈ LUÔN</t>
+  </si>
+  <si>
+    <t>DOANH THU 10/02/2026</t>
+  </si>
+  <si>
+    <t>k11425, thạo đi ăn cưới nên ngày 12 nộp doanh thu</t>
+  </si>
+  <si>
+    <t>gộp doanh thu 2 ngày</t>
+  </si>
+  <si>
+    <t>doanh thu 10 - 11</t>
+  </si>
+  <si>
+    <t>DOANH THU 11/02/2026</t>
+  </si>
+  <si>
+    <t>k11327, nghỉ qua xe đỏ chạy nhưng bị công an bắt</t>
+  </si>
+  <si>
+    <t>DOANH THU 12/02/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -1044,7 +1074,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1540,6 +1570,19 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="27" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3143,7 +3186,7 @@
       <c r="O10" s="174"/>
       <c r="P10" s="175">
         <f>SUM(F7:F1006)</f>
-        <v>27508000</v>
+        <v>30628000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3206,7 +3249,7 @@
       <c r="O12" s="176"/>
       <c r="P12" s="175">
         <f>SUM(G7:G1006)</f>
-        <v>14257000</v>
+        <v>15817000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3301,7 +3344,7 @@
       <c r="O15" s="177"/>
       <c r="P15" s="67">
         <f>SUM(H7:H1006)</f>
-        <v>14045000</v>
+        <v>15605000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3609,12 +3652,16 @@
       <c r="E26" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="75"/>
+      <c r="F26" s="75">
+        <v>3120000</v>
+      </c>
       <c r="G26" s="75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="75"/>
+        <v>1560000</v>
+      </c>
+      <c r="H26" s="75">
+        <v>1560000</v>
+      </c>
       <c r="I26" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -4065,6 +4112,3796 @@
         <v>76</v>
       </c>
       <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="170"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="170"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="170"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="170"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="170"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="170"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84438330-29DE-4F90-AE31-C18EEE9AE32B}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="165" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="171" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="122" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="123"/>
+      <c r="E7" s="178" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125">
+        <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="K7" s="129" t="s">
+        <v>172</v>
+      </c>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="172"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41">
+        <v>1820000</v>
+      </c>
+      <c r="G8" s="41">
+        <f>IF(F8="",0,IF(F8&gt;=1800000,F8*O$19,F8*O$18))</f>
+        <v>910000</v>
+      </c>
+      <c r="H8" s="41">
+        <v>910000</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="0">G8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="130"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="172"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="1">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41">
+        <f t="shared" ref="G9:G18" si="2">IF(F9="",0,IF(F9&gt;1800000,F9*O$19,F9*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="44"/>
+      <c r="I9" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="155"/>
+      <c r="K9" s="154"/>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="172"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="44">
+        <v>800000</v>
+      </c>
+      <c r="G10" s="41">
+        <f t="shared" si="2"/>
+        <v>480000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>480000</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="130" t="s">
+        <v>171</v>
+      </c>
+      <c r="L10" s="46"/>
+      <c r="N10" s="174" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
+        <f>SUM(F7:F1006)</f>
+        <v>25741000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="172"/>
+      <c r="B11" s="38">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="44"/>
+      <c r="I11" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="155"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="172"/>
+      <c r="B12" s="38">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="155"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="176" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
+        <f>SUM(G7:G1006)</f>
+        <v>13126500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="172"/>
+      <c r="B13" s="38">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="155"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="172"/>
+      <c r="B14" s="38">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="172"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="177" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="177"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>13138000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="172"/>
+      <c r="B16" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="172"/>
+      <c r="B17" s="38">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="172"/>
+      <c r="B18" s="38">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="173"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="169" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="139"/>
+      <c r="I20" s="75">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="128"/>
+      <c r="K20" s="132" t="s">
+        <v>139</v>
+      </c>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="170"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="156" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" s="162"/>
+      <c r="E21" s="162" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="160"/>
+      <c r="G21" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="160"/>
+      <c r="I21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="49"/>
+      <c r="K21" s="132" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="170"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="79"/>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="49"/>
+      <c r="K22" s="164" t="s">
+        <v>160</v>
+      </c>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="170"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="137" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" s="140"/>
+      <c r="E23" s="140" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="139"/>
+      <c r="G23" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="139"/>
+      <c r="I23" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="49"/>
+      <c r="K23" s="132" t="s">
+        <v>114</v>
+      </c>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="170"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="75">
+        <v>460000</v>
+      </c>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>276000</v>
+      </c>
+      <c r="H24" s="79">
+        <v>276000</v>
+      </c>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="49"/>
+      <c r="K24" s="132" t="s">
+        <v>169</v>
+      </c>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="170"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="75">
+        <v>2070000</v>
+      </c>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>1035000</v>
+      </c>
+      <c r="H25" s="79">
+        <v>1035000</v>
+      </c>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K25" s="132"/>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="170"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="K26" s="132"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="170"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="87"/>
+      <c r="E27" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="79">
+        <v>1880000</v>
+      </c>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>940000</v>
+      </c>
+      <c r="H27" s="75">
+        <v>940000</v>
+      </c>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K27" s="132"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="170"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="79">
+        <v>1300000</v>
+      </c>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>780000</v>
+      </c>
+      <c r="H28" s="79">
+        <v>780000</v>
+      </c>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K28" s="132"/>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="170"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="118">
+        <v>2550000</v>
+      </c>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>1275000</v>
+      </c>
+      <c r="H29" s="118">
+        <v>1275000</v>
+      </c>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K29" s="132"/>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="170"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="161" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="162"/>
+      <c r="E30" s="140" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="146"/>
+      <c r="G30" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="163"/>
+      <c r="I30" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="49"/>
+      <c r="K30" s="132" t="s">
+        <v>162</v>
+      </c>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="170"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="89">
+        <v>2430000</v>
+      </c>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>1215000</v>
+      </c>
+      <c r="H31" s="89">
+        <v>1215000</v>
+      </c>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31" s="132"/>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="170"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="156" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="157"/>
+      <c r="E32" s="140" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="139"/>
+      <c r="G32" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="139"/>
+      <c r="I32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="49"/>
+      <c r="K32" s="132" t="s">
+        <v>165</v>
+      </c>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="170"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="87"/>
+      <c r="E33" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="90">
+        <v>3312000</v>
+      </c>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>1656000</v>
+      </c>
+      <c r="H33" s="89">
+        <v>1656000</v>
+      </c>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="49"/>
+      <c r="K33" s="89" t="s">
+        <v>164</v>
+      </c>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="170"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="79">
+        <v>3166000</v>
+      </c>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>1583000</v>
+      </c>
+      <c r="H34" s="79">
+        <v>1583000</v>
+      </c>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K34" s="132"/>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="170"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="120"/>
+      <c r="E35" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="118">
+        <v>1736000</v>
+      </c>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>868000</v>
+      </c>
+      <c r="H35" s="118">
+        <v>880000</v>
+      </c>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>-12000</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K35" s="132"/>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="170"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="87" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="120"/>
+      <c r="E36" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="118">
+        <v>1950000</v>
+      </c>
+      <c r="G36" s="75">
+        <f t="shared" si="3"/>
+        <v>975000</v>
+      </c>
+      <c r="H36" s="118">
+        <v>975000</v>
+      </c>
+      <c r="I36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K36" s="132" t="s">
+        <v>167</v>
+      </c>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="170"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="142"/>
+      <c r="D37" s="143"/>
+      <c r="E37" s="144" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="145"/>
+      <c r="G37" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="146"/>
+      <c r="I37" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="49"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="170"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="43"/>
+      <c r="E38" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="90">
+        <v>2267000</v>
+      </c>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>1133500</v>
+      </c>
+      <c r="H38" s="89">
+        <v>1133000</v>
+      </c>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="J38" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K38" s="98"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="170"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="90"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="170"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="90"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="170"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="170"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="170"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="170"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="170"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="170"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="170"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F27CF0A-12D9-4118-9B99-1186D3F9D7B5}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="47.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="165" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="171" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="41">
+        <v>2140000</v>
+      </c>
+      <c r="G7" s="41">
+        <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
+        <v>1070000</v>
+      </c>
+      <c r="H7" s="41">
+        <v>1070000</v>
+      </c>
+      <c r="I7" s="41">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="129" t="s">
+        <v>172</v>
+      </c>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="172"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41">
+        <v>1000000</v>
+      </c>
+      <c r="G8" s="41">
+        <f>IF(F8="",0,IF(F8&gt;=1800000,F8*O$19,F8*O$18))</f>
+        <v>600000</v>
+      </c>
+      <c r="H8" s="41">
+        <v>500000</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="0">G8-H8</f>
+        <v>100000</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="130"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="172"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="1">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41">
+        <f t="shared" ref="G9:G18" si="2">IF(F9="",0,IF(F9&gt;1800000,F9*O$19,F9*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="44"/>
+      <c r="I9" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="155"/>
+      <c r="K9" s="154"/>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="172"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="179" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="143"/>
+      <c r="E10" s="178" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="126"/>
+      <c r="G10" s="125">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="126"/>
+      <c r="I10" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="141"/>
+      <c r="K10" s="130" t="s">
+        <v>171</v>
+      </c>
+      <c r="L10" s="46"/>
+      <c r="N10" s="174" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
+        <f>SUM(F7:F1006)</f>
+        <v>23391000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="172"/>
+      <c r="B11" s="38">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="44"/>
+      <c r="I11" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="155"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="172"/>
+      <c r="B12" s="38">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="155"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="176" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
+        <f>SUM(G7:G1006)</f>
+        <v>11795500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="172"/>
+      <c r="B13" s="38">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="155"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="172"/>
+      <c r="B14" s="38">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="172"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="177" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="177"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>11695000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="172"/>
+      <c r="B16" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="172"/>
+      <c r="B17" s="38">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="172"/>
+      <c r="B18" s="38">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="173"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="169" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="141"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="170"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="77"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="79"/>
+      <c r="G21" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="79"/>
+      <c r="I21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="49"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="170"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="79"/>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="49"/>
+      <c r="K22" s="164"/>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="170"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="73"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="49"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="170"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="79"/>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="49"/>
+      <c r="K24" s="132"/>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="170"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="75">
+        <v>2070000</v>
+      </c>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>1035000</v>
+      </c>
+      <c r="H25" s="79">
+        <v>1035000</v>
+      </c>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K25" s="132"/>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="170"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="75">
+        <v>8646000</v>
+      </c>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>4323000</v>
+      </c>
+      <c r="H26" s="75">
+        <v>4323000</v>
+      </c>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26" s="132" t="s">
+        <v>173</v>
+      </c>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="170"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="79"/>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="49"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="170"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="79">
+        <v>2750000</v>
+      </c>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>1375000</v>
+      </c>
+      <c r="H28" s="79">
+        <v>1375000</v>
+      </c>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K28" s="132"/>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="170"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="118">
+        <v>2950000</v>
+      </c>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>1475000</v>
+      </c>
+      <c r="H29" s="118">
+        <v>1475000</v>
+      </c>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K29" s="132"/>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="170"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="78"/>
+      <c r="E30" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="89"/>
+      <c r="G30" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="119"/>
+      <c r="I30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="49"/>
+      <c r="K30" s="132"/>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="170"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="89">
+        <v>1790000</v>
+      </c>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>895000</v>
+      </c>
+      <c r="H31" s="89">
+        <v>895000</v>
+      </c>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31" s="132">
+        <v>1790000</v>
+      </c>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="170"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="156" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="157"/>
+      <c r="E32" s="140" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="139"/>
+      <c r="G32" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="139"/>
+      <c r="I32" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="141"/>
+      <c r="K32" s="132"/>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="170"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="90"/>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="89"/>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="49"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="170"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="87"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="79"/>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="79"/>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="49"/>
+      <c r="K34" s="132"/>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="170"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="87"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="118"/>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="118"/>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="49"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="170"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="157" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="180"/>
+      <c r="E36" s="144" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="181"/>
+      <c r="G36" s="139">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="181"/>
+      <c r="I36" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="141"/>
+      <c r="K36" s="182" t="s">
+        <v>175</v>
+      </c>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="170"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="99"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="90"/>
+      <c r="G37" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="89"/>
+      <c r="I37" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="49"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="170"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="43"/>
+      <c r="E38" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="90">
+        <v>2045000</v>
+      </c>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>1022500</v>
+      </c>
+      <c r="H38" s="89">
+        <v>1022000</v>
+      </c>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="J38" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K38" s="98"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="170"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="90"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="170"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="90"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="170"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="100"/>
+      <c r="G41" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="89"/>
+      <c r="I41" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="83"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="47"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="170"/>
+      <c r="B42" s="38">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="100"/>
+      <c r="G42" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="89"/>
+      <c r="I42" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="170"/>
+      <c r="B43" s="38">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="89"/>
+      <c r="I43" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="83"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="170"/>
+      <c r="B44" s="38">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="89"/>
+      <c r="I44" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="83"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="170"/>
+      <c r="B45" s="38">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="89"/>
+      <c r="I45" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="83"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="47"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="170"/>
+      <c r="B46" s="38">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="99"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="89"/>
+      <c r="I46" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="83"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="47"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="170"/>
+      <c r="B47" s="38">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="99"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="89"/>
+      <c r="I47" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="83"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D055C60D-576A-4818-AE7C-59570D5C3B4B}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="47.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="165" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="G4" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+      <c r="B6" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="171" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38">
+        <v>1</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="40"/>
+      <c r="E7" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41">
+        <f>IF(F7="",0,IF(F7&gt;1800000,F7*O$19,F7*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="128"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="46"/>
+      <c r="N7" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="172"/>
+      <c r="B8" s="38">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41">
+        <f>IF(F8="",0,IF(F8&gt;=1800000,F8*O$19,F8*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I18" si="0">G8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="128"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="172"/>
+      <c r="B9" s="38">
+        <f t="shared" ref="B9:B18" si="1">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41">
+        <f t="shared" ref="G9:G18" si="2">IF(F9="",0,IF(F9&gt;1800000,F9*O$19,F9*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="44"/>
+      <c r="I9" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="155"/>
+      <c r="K9" s="154"/>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="172"/>
+      <c r="B10" s="38">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="41">
+        <v>550000</v>
+      </c>
+      <c r="G10" s="41">
+        <f t="shared" si="2"/>
+        <v>330000</v>
+      </c>
+      <c r="H10" s="44">
+        <v>330000</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="130"/>
+      <c r="L10" s="46"/>
+      <c r="N10" s="174" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="174"/>
+      <c r="P10" s="175">
+        <f>SUM(F7:F1006)</f>
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="172"/>
+      <c r="B11" s="38">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="44"/>
+      <c r="I11" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="155"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="46"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="172"/>
+      <c r="B12" s="38">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="155"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="46"/>
+      <c r="N12" s="176" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="176"/>
+      <c r="P12" s="175">
+        <f>SUM(G7:G1006)</f>
+        <v>330000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="172"/>
+      <c r="B13" s="38">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="155"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="46"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="175"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="172"/>
+      <c r="B14" s="38">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="46"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="175"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="172"/>
+      <c r="B15" s="38">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="46"/>
+      <c r="N15" s="177" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="177"/>
+      <c r="P15" s="67">
+        <f>SUM(H7:H1006)</f>
+        <v>330000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="172"/>
+      <c r="B16" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="62"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="46"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="172"/>
+      <c r="B17" s="38">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="62"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="172"/>
+      <c r="B18" s="38">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="62"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="46"/>
+      <c r="N18" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="68">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="173"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="56"/>
+      <c r="N19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="169" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="38">
+        <v>1</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75">
+        <f t="shared" ref="G20:G47" si="3">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="75"/>
+      <c r="I20" s="75">
+        <f t="shared" ref="I20:I47" si="4">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="128"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="170"/>
+      <c r="B21" s="38">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="77"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="79"/>
+      <c r="G21" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="79"/>
+      <c r="I21" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="128"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="170"/>
+      <c r="B22" s="38">
+        <f t="shared" ref="B22:B47" si="5">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="73"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="79"/>
+      <c r="I22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="128"/>
+      <c r="K22" s="164"/>
+      <c r="L22" s="82"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="170"/>
+      <c r="B23" s="38">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="73"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="128"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="76"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="170"/>
+      <c r="B24" s="38">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="73"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="79"/>
+      <c r="I24" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="128"/>
+      <c r="K24" s="132"/>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="170"/>
+      <c r="B25" s="38">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="79"/>
+      <c r="I25" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="128"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="76"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="170"/>
+      <c r="B26" s="38">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="128"/>
+      <c r="K26" s="132"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="170"/>
+      <c r="B27" s="38">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="77"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="79"/>
+      <c r="G27" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="128"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="170"/>
+      <c r="B28" s="38">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="79"/>
+      <c r="G28" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="79"/>
+      <c r="I28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="128"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="76"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="170"/>
+      <c r="B29" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="118"/>
+      <c r="G29" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="118"/>
+      <c r="I29" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="128"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="93"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="170"/>
+      <c r="B30" s="38">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="78"/>
+      <c r="E30" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="89"/>
+      <c r="G30" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="119"/>
+      <c r="I30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="128"/>
+      <c r="K30" s="132"/>
+      <c r="L30" s="80"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="170"/>
+      <c r="B31" s="38">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="89"/>
+      <c r="G31" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="89"/>
+      <c r="I31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="128"/>
+      <c r="K31" s="132"/>
+      <c r="L31" s="93"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="170"/>
+      <c r="B32" s="38">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="87"/>
+      <c r="E32" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="128"/>
+      <c r="K32" s="132"/>
+      <c r="L32" s="93"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="170"/>
+      <c r="B33" s="38">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="90"/>
+      <c r="G33" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="89"/>
+      <c r="I33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="128"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="76"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="170"/>
+      <c r="B34" s="38">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="87"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="79"/>
+      <c r="G34" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="79"/>
+      <c r="I34" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="128"/>
+      <c r="K34" s="132"/>
+      <c r="L34" s="76"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="170"/>
+      <c r="B35" s="38">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="87"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="118"/>
+      <c r="G35" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="118"/>
+      <c r="I35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="128"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="80"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="170"/>
+      <c r="B36" s="38">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="87" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="120"/>
+      <c r="E36" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="118"/>
+      <c r="G36" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="118"/>
+      <c r="I36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="128"/>
+      <c r="K36" s="182"/>
+      <c r="L36" s="46"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="170"/>
+      <c r="B37" s="38">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="99"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="90"/>
+      <c r="G37" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="89"/>
+      <c r="I37" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="128"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="47"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="170"/>
+      <c r="B38" s="38">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="43"/>
+      <c r="E38" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="90"/>
+      <c r="G38" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="89"/>
+      <c r="I38" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="128"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="47"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="170"/>
+      <c r="B39" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="99"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="90"/>
+      <c r="G39" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="89"/>
+      <c r="I39" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="83"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="47"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="170"/>
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="90"/>
+      <c r="G40" s="75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="89"/>
+      <c r="I40" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="83"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="47"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="170"/>
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="90"/>
       <c r="G41" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
